--- a/Assets/StreamingAssets/DataTable.xlsx
+++ b/Assets/StreamingAssets/DataTable.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SWProject\My project\Assets\StreamingAssets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C1FBBE6C-38E2-4FA4-901B-4822D246DBA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{334DFBCC-6313-46CC-9629-71224C7178D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="15435" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="암모니아 실험 개요" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="754" uniqueCount="360">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="755" uniqueCount="361">
   <si>
     <t>개요</t>
   </si>
@@ -75,9 +75,6 @@
   </si>
   <si>
     <t>실험절차</t>
-  </si>
-  <si>
-    <t>NO</t>
   </si>
   <si>
     <t>Tag</t>
@@ -1173,6 +1170,14 @@
   </si>
   <si>
     <t>폐수처리, 부지사용, 인건비 총괄</t>
+  </si>
+  <si>
+    <t>A</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NO</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1643,7 +1648,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="67">
+  <cellXfs count="68">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1786,7 +1791,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1835,6 +1839,10 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="2" xr:uid="{00000000-000B-0000-0000-000008000000}"/>
@@ -1852,10 +1860,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2178,7 +2182,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C485614-A5BE-4FB7-B2E6-807540769775}">
-  <dimension ref="A1:R50"/>
+  <dimension ref="A1:R56"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="6.375" style="1" bestFit="1" customWidth="1"/>
@@ -2204,58 +2208,58 @@
   <sheetData>
     <row r="1" spans="1:18">
       <c r="A1" s="14" t="s">
+        <v>360</v>
+      </c>
+      <c r="B1" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="C1" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="D1" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="E1" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="F1" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="F1" s="14" t="s">
+      <c r="G1" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="G1" s="14" t="s">
+      <c r="H1" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="H1" s="14" t="s">
+      <c r="I1" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="I1" s="14" t="s">
+      <c r="J1" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="J1" s="14" t="s">
+      <c r="K1" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="K1" s="14" t="s">
+      <c r="L1" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="L1" s="14" t="s">
+      <c r="M1" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="M1" s="14" t="s">
+      <c r="N1" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="N1" s="14" t="s">
+      <c r="O1" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="O1" s="14" t="s">
+      <c r="P1" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="P1" s="14" t="s">
+      <c r="Q1" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="Q1" s="14" t="s">
+      <c r="R1" s="14" t="s">
         <v>26</v>
-      </c>
-      <c r="R1" s="14" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:18">
@@ -2263,31 +2267,31 @@
         <v>1</v>
       </c>
       <c r="B2" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="C2" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="C2" s="15" t="s">
+      <c r="D2" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="D2" s="15" t="s">
+      <c r="E2" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="E2" s="15" t="s">
+      <c r="F2" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="F2" s="15" t="s">
+      <c r="G2" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="G2" s="15" t="s">
+      <c r="H2" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="I2" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="H2" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="I2" s="15" t="s">
+      <c r="J2" s="15" t="s">
         <v>34</v>
-      </c>
-      <c r="J2" s="15" t="s">
-        <v>35</v>
       </c>
       <c r="K2" s="15">
         <v>0</v>
@@ -2308,7 +2312,7 @@
         <v>1</v>
       </c>
       <c r="Q2" s="15" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="R2" s="15"/>
     </row>
@@ -2317,31 +2321,31 @@
         <v>2</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C3" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="D3" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="D3" s="15" t="s">
+      <c r="E3" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="E3" s="15" t="s">
+      <c r="F3" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="F3" s="15" t="s">
+      <c r="G3" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="G3" s="15" t="s">
+      <c r="H3" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="I3" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="H3" s="15" t="s">
-        <v>37</v>
-      </c>
-      <c r="I3" s="15" t="s">
+      <c r="J3" s="15" t="s">
         <v>34</v>
-      </c>
-      <c r="J3" s="15" t="s">
-        <v>35</v>
       </c>
       <c r="K3" s="15">
         <v>0</v>
@@ -2362,7 +2366,7 @@
         <v>1</v>
       </c>
       <c r="Q3" s="15" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="R3" s="15"/>
     </row>
@@ -2371,31 +2375,31 @@
         <v>3</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C4" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="D4" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="D4" s="15" t="s">
+      <c r="E4" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="E4" s="15" t="s">
+      <c r="F4" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="F4" s="15" t="s">
+      <c r="G4" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="G4" s="15" t="s">
+      <c r="H4" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="I4" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="H4" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="I4" s="15" t="s">
+      <c r="J4" s="15" t="s">
         <v>34</v>
-      </c>
-      <c r="J4" s="15" t="s">
-        <v>35</v>
       </c>
       <c r="K4" s="15">
         <v>0</v>
@@ -2416,7 +2420,7 @@
         <v>1</v>
       </c>
       <c r="Q4" s="15" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="R4" s="15"/>
     </row>
@@ -2425,31 +2429,31 @@
         <v>4</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C5" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="D5" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="D5" s="15" t="s">
+      <c r="E5" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="E5" s="15" t="s">
+      <c r="F5" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="F5" s="15" t="s">
+      <c r="G5" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="G5" s="15" t="s">
+      <c r="H5" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="I5" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="H5" s="15" t="s">
-        <v>41</v>
-      </c>
-      <c r="I5" s="15" t="s">
+      <c r="J5" s="15" t="s">
         <v>34</v>
-      </c>
-      <c r="J5" s="15" t="s">
-        <v>35</v>
       </c>
       <c r="K5" s="15">
         <v>0</v>
@@ -2470,7 +2474,7 @@
         <v>1</v>
       </c>
       <c r="Q5" s="15" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R5" s="15"/>
     </row>
@@ -2479,31 +2483,31 @@
         <v>5</v>
       </c>
       <c r="B6" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="C6" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="D6" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="E6" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="F6" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="C6" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="D6" s="15" t="s">
-        <v>30</v>
-      </c>
-      <c r="E6" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="F6" s="15" t="s">
-        <v>44</v>
-      </c>
       <c r="G6" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="H6" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="I6" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="H6" s="15" t="s">
-        <v>43</v>
-      </c>
-      <c r="I6" s="15" t="s">
+      <c r="J6" s="15" t="s">
         <v>34</v>
-      </c>
-      <c r="J6" s="15" t="s">
-        <v>35</v>
       </c>
       <c r="K6" s="15">
         <v>0</v>
@@ -2524,7 +2528,7 @@
         <v>1</v>
       </c>
       <c r="Q6" s="15" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="R6" s="15"/>
     </row>
@@ -2533,31 +2537,31 @@
         <v>6</v>
       </c>
       <c r="B7" s="15" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C7" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="D7" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="D7" s="15" t="s">
+      <c r="E7" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="E7" s="15" t="s">
-        <v>31</v>
-      </c>
       <c r="F7" s="15" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G7" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="H7" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="I7" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="H7" s="15" t="s">
-        <v>46</v>
-      </c>
-      <c r="I7" s="15" t="s">
+      <c r="J7" s="15" t="s">
         <v>34</v>
-      </c>
-      <c r="J7" s="15" t="s">
-        <v>35</v>
       </c>
       <c r="K7" s="15">
         <v>0</v>
@@ -2578,7 +2582,7 @@
         <v>1</v>
       </c>
       <c r="Q7" s="15" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="R7" s="15"/>
     </row>
@@ -2587,31 +2591,31 @@
         <v>7</v>
       </c>
       <c r="B8" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="C8" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="D8" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="E8" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="F8" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="G8" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="H8" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="I8" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="C8" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="D8" s="15" t="s">
-        <v>30</v>
-      </c>
-      <c r="E8" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="F8" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="G8" s="15" t="s">
-        <v>33</v>
-      </c>
-      <c r="H8" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="I8" s="15" t="s">
-        <v>49</v>
-      </c>
       <c r="J8" s="15" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K8" s="15">
         <v>0</v>
@@ -2632,7 +2636,7 @@
         <v>1</v>
       </c>
       <c r="Q8" s="15" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="R8" s="15"/>
     </row>
@@ -2641,31 +2645,31 @@
         <v>8</v>
       </c>
       <c r="B9" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="C9" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="D9" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="E9" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="F9" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="G9" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="H9" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="I9" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="C9" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="D9" s="15" t="s">
-        <v>30</v>
-      </c>
-      <c r="E9" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="F9" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="G9" s="15" t="s">
-        <v>33</v>
-      </c>
-      <c r="H9" s="15" t="s">
-        <v>51</v>
-      </c>
-      <c r="I9" s="15" t="s">
-        <v>52</v>
-      </c>
       <c r="J9" s="15" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K9" s="15">
         <v>0</v>
@@ -2686,7 +2690,7 @@
         <v>1</v>
       </c>
       <c r="Q9" s="15" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="R9" s="15"/>
     </row>
@@ -2695,31 +2699,31 @@
         <v>9</v>
       </c>
       <c r="B10" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="C10" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="D10" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="E10" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="F10" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="C10" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="D10" s="15" t="s">
-        <v>30</v>
-      </c>
-      <c r="E10" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="F10" s="15" t="s">
-        <v>55</v>
-      </c>
       <c r="G10" s="15" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H10" s="15" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="I10" s="15" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="J10" s="15" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K10" s="15">
         <v>0</v>
@@ -2740,7 +2744,7 @@
         <v>1</v>
       </c>
       <c r="Q10" s="15" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="R10" s="15"/>
     </row>
@@ -2749,31 +2753,31 @@
         <v>10</v>
       </c>
       <c r="B11" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="C11" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="D11" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="E11" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="F11" s="15" t="s">
         <v>57</v>
       </c>
-      <c r="C11" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="D11" s="15" t="s">
-        <v>30</v>
-      </c>
-      <c r="E11" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="F11" s="15" t="s">
+      <c r="G11" s="15" t="s">
         <v>58</v>
       </c>
-      <c r="G11" s="15" t="s">
-        <v>59</v>
-      </c>
       <c r="H11" s="15" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="I11" s="15" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="J11" s="15" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K11" s="15">
         <v>0</v>
@@ -2794,7 +2798,7 @@
         <v>1</v>
       </c>
       <c r="Q11" s="15" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="R11" s="15"/>
     </row>
@@ -2803,31 +2807,31 @@
         <v>11</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C12" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="D12" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="D12" s="15" t="s">
+      <c r="E12" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="E12" s="15" t="s">
-        <v>31</v>
-      </c>
       <c r="F12" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="G12" s="15" t="s">
         <v>58</v>
       </c>
-      <c r="G12" s="15" t="s">
-        <v>59</v>
-      </c>
       <c r="H12" s="15" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I12" s="15" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="J12" s="15" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K12" s="15">
         <v>0</v>
@@ -2848,7 +2852,7 @@
         <v>1</v>
       </c>
       <c r="Q12" s="15" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="R12" s="15"/>
     </row>
@@ -2857,31 +2861,31 @@
         <v>12</v>
       </c>
       <c r="B13" s="15" t="s">
+        <v>62</v>
+      </c>
+      <c r="C13" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="D13" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="E13" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="F13" s="15" t="s">
         <v>63</v>
       </c>
-      <c r="C13" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="D13" s="15" t="s">
-        <v>30</v>
-      </c>
-      <c r="E13" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="F13" s="15" t="s">
-        <v>64</v>
-      </c>
       <c r="G13" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="H13" s="15" t="s">
+        <v>62</v>
+      </c>
+      <c r="I13" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="H13" s="15" t="s">
-        <v>63</v>
-      </c>
-      <c r="I13" s="15" t="s">
+      <c r="J13" s="15" t="s">
         <v>34</v>
-      </c>
-      <c r="J13" s="15" t="s">
-        <v>35</v>
       </c>
       <c r="K13" s="15">
         <v>0</v>
@@ -2902,248 +2906,230 @@
         <v>1</v>
       </c>
       <c r="Q13" s="15" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="R13" s="15"/>
     </row>
     <row r="14" spans="1:18">
       <c r="A14" s="15">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>66</v>
+        <v>132</v>
       </c>
       <c r="C14" s="15" t="s">
-        <v>67</v>
+        <v>28</v>
       </c>
       <c r="D14" s="15" t="s">
-        <v>30</v>
-      </c>
-      <c r="E14" s="15" t="s">
-        <v>68</v>
-      </c>
+        <v>133</v>
+      </c>
+      <c r="E14" s="15"/>
       <c r="F14" s="15" t="s">
-        <v>69</v>
+        <v>134</v>
       </c>
       <c r="G14" s="15" t="s">
-        <v>70</v>
+        <v>135</v>
       </c>
       <c r="H14" s="15" t="s">
-        <v>71</v>
+        <v>136</v>
       </c>
       <c r="I14" s="15" t="s">
-        <v>49</v>
+        <v>137</v>
       </c>
       <c r="J14" s="15" t="s">
-        <v>35</v>
+        <v>138</v>
       </c>
       <c r="K14" s="15">
         <v>0</v>
       </c>
       <c r="L14" s="15">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="M14" s="15">
         <v>0</v>
       </c>
       <c r="N14" s="15">
-        <v>16000</v>
+        <v>1</v>
       </c>
       <c r="O14" s="15">
-        <v>13</v>
+        <v>250</v>
       </c>
       <c r="P14" s="15" t="b">
         <v>1</v>
       </c>
-      <c r="Q14" s="15"/>
+      <c r="Q14" s="15" t="s">
+        <v>139</v>
+      </c>
       <c r="R14" s="15"/>
     </row>
     <row r="15" spans="1:18">
       <c r="A15" s="15">
+        <v>14</v>
+      </c>
+      <c r="B15" s="15" t="s">
+        <v>140</v>
+      </c>
+      <c r="C15" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="B15" s="15" t="s">
-        <v>72</v>
-      </c>
-      <c r="C15" s="15" t="s">
-        <v>67</v>
-      </c>
       <c r="D15" s="15" t="s">
-        <v>30</v>
-      </c>
-      <c r="E15" s="15" t="s">
-        <v>31</v>
-      </c>
+        <v>133</v>
+      </c>
+      <c r="E15" s="15"/>
       <c r="F15" s="15" t="s">
-        <v>58</v>
+        <v>141</v>
       </c>
       <c r="G15" s="15" t="s">
-        <v>70</v>
+        <v>135</v>
       </c>
       <c r="H15" s="15" t="s">
-        <v>71</v>
+        <v>136</v>
       </c>
       <c r="I15" s="15" t="s">
-        <v>49</v>
+        <v>137</v>
       </c>
       <c r="J15" s="15" t="s">
-        <v>35</v>
+        <v>138</v>
       </c>
       <c r="K15" s="15">
         <v>0</v>
       </c>
       <c r="L15" s="15">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="M15" s="15">
         <v>0</v>
       </c>
       <c r="N15" s="15">
-        <v>16000</v>
+        <v>1</v>
       </c>
       <c r="O15" s="15">
-        <v>14</v>
+        <v>251</v>
       </c>
       <c r="P15" s="15" t="b">
         <v>1</v>
       </c>
-      <c r="Q15" s="15"/>
+      <c r="Q15" s="15" t="s">
+        <v>142</v>
+      </c>
       <c r="R15" s="15"/>
     </row>
     <row r="16" spans="1:18">
       <c r="A16" s="15">
-        <v>29</v>
-      </c>
-      <c r="B16" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="C16" s="15" t="s">
-        <v>67</v>
-      </c>
-      <c r="D16" s="15" t="s">
-        <v>30</v>
-      </c>
-      <c r="E16" s="15" t="s">
-        <v>74</v>
-      </c>
-      <c r="F16" s="15" t="s">
-        <v>75</v>
-      </c>
-      <c r="G16" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="H16" s="15" t="s">
-        <v>71</v>
-      </c>
-      <c r="I16" s="15" t="s">
-        <v>49</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="B16" s="15"/>
+      <c r="C16" s="15"/>
+      <c r="D16" s="15"/>
+      <c r="E16" s="15"/>
+      <c r="F16" s="15"/>
+      <c r="G16" s="15"/>
+      <c r="H16" s="15"/>
+      <c r="I16" s="15"/>
       <c r="J16" s="15" t="s">
-        <v>35</v>
+        <v>138</v>
       </c>
       <c r="K16" s="15">
         <v>0</v>
       </c>
       <c r="L16" s="15">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="M16" s="15">
         <v>0</v>
       </c>
       <c r="N16" s="15">
-        <v>16000</v>
+        <v>1</v>
       </c>
       <c r="O16" s="15">
-        <v>15</v>
+        <v>452</v>
       </c>
       <c r="P16" s="15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q16" s="15"/>
       <c r="R16" s="15"/>
     </row>
     <row r="17" spans="1:18">
       <c r="A17" s="15">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="B17" s="15" t="s">
-        <v>76</v>
+        <v>165</v>
       </c>
       <c r="C17" s="15" t="s">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="D17" s="15" t="s">
-        <v>30</v>
-      </c>
-      <c r="E17" s="15" t="s">
-        <v>74</v>
-      </c>
+        <v>160</v>
+      </c>
+      <c r="E17" s="15"/>
       <c r="F17" s="15" t="s">
-        <v>78</v>
+        <v>166</v>
       </c>
       <c r="G17" s="15" t="s">
-        <v>59</v>
+        <v>146</v>
       </c>
       <c r="H17" s="15" t="s">
-        <v>57</v>
+        <v>165</v>
       </c>
       <c r="I17" s="15" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="J17" s="15" t="s">
-        <v>35</v>
+        <v>138</v>
       </c>
       <c r="K17" s="15">
         <v>0</v>
       </c>
       <c r="L17" s="15">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="M17" s="15">
         <v>0</v>
       </c>
       <c r="N17" s="15">
-        <v>16000</v>
+        <v>1</v>
       </c>
       <c r="O17" s="15">
-        <v>17</v>
+        <v>453</v>
       </c>
       <c r="P17" s="15" t="b">
         <v>1</v>
       </c>
       <c r="Q17" s="15" t="s">
-        <v>79</v>
+        <v>167</v>
       </c>
       <c r="R17" s="15"/>
     </row>
     <row r="18" spans="1:18">
       <c r="A18" s="15">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="B18" s="15" t="s">
-        <v>80</v>
+        <v>147</v>
       </c>
       <c r="C18" s="15" t="s">
-        <v>81</v>
+        <v>66</v>
       </c>
       <c r="D18" s="15" t="s">
-        <v>30</v>
+        <v>160</v>
       </c>
       <c r="E18" s="15"/>
       <c r="F18" s="15" t="s">
-        <v>82</v>
+        <v>166</v>
       </c>
       <c r="G18" s="15" t="s">
-        <v>83</v>
+        <v>146</v>
       </c>
       <c r="H18" s="15" t="s">
-        <v>84</v>
+        <v>147</v>
       </c>
       <c r="I18" s="15" t="s">
-        <v>81</v>
+        <v>51</v>
       </c>
       <c r="J18" s="15" t="s">
-        <v>35</v>
+        <v>138</v>
       </c>
       <c r="K18" s="15">
         <v>0</v>
@@ -3158,44 +3144,30 @@
         <v>1</v>
       </c>
       <c r="O18" s="15">
-        <v>18</v>
+        <v>454</v>
       </c>
       <c r="P18" s="15" t="b">
         <v>1</v>
       </c>
       <c r="Q18" s="15" t="s">
-        <v>85</v>
+        <v>168</v>
       </c>
       <c r="R18" s="15"/>
     </row>
     <row r="19" spans="1:18">
       <c r="A19" s="15">
-        <v>38</v>
-      </c>
-      <c r="B19" s="15" t="s">
-        <v>86</v>
-      </c>
-      <c r="C19" s="15" t="s">
-        <v>81</v>
-      </c>
-      <c r="D19" s="15" t="s">
-        <v>30</v>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="B19" s="15"/>
+      <c r="C19" s="15"/>
+      <c r="D19" s="15"/>
       <c r="E19" s="15"/>
-      <c r="F19" s="15" t="s">
-        <v>87</v>
-      </c>
-      <c r="G19" s="15" t="s">
-        <v>83</v>
-      </c>
-      <c r="H19" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="I19" s="15" t="s">
-        <v>81</v>
-      </c>
+      <c r="F19" s="15"/>
+      <c r="G19" s="15"/>
+      <c r="H19" s="15"/>
+      <c r="I19" s="15"/>
       <c r="J19" s="15" t="s">
-        <v>35</v>
+        <v>138</v>
       </c>
       <c r="K19" s="15">
         <v>0</v>
@@ -3210,44 +3182,44 @@
         <v>1</v>
       </c>
       <c r="O19" s="15">
-        <v>19</v>
+        <v>252</v>
       </c>
       <c r="P19" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q19" s="15" t="s">
-        <v>89</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q19" s="15"/>
       <c r="R19" s="15"/>
     </row>
     <row r="20" spans="1:18">
       <c r="A20" s="15">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>90</v>
+        <v>143</v>
       </c>
       <c r="C20" s="15" t="s">
-        <v>81</v>
+        <v>66</v>
       </c>
       <c r="D20" s="15" t="s">
-        <v>30</v>
-      </c>
-      <c r="E20" s="15"/>
+        <v>133</v>
+      </c>
+      <c r="E20" s="66" t="s">
+        <v>144</v>
+      </c>
       <c r="F20" s="15" t="s">
-        <v>91</v>
+        <v>145</v>
       </c>
       <c r="G20" s="15" t="s">
-        <v>83</v>
+        <v>146</v>
       </c>
       <c r="H20" s="15" t="s">
-        <v>92</v>
+        <v>147</v>
       </c>
       <c r="I20" s="15" t="s">
-        <v>81</v>
+        <v>51</v>
       </c>
       <c r="J20" s="15" t="s">
-        <v>35</v>
+        <v>138</v>
       </c>
       <c r="K20" s="15">
         <v>0</v>
@@ -3262,44 +3234,46 @@
         <v>1</v>
       </c>
       <c r="O20" s="15">
-        <v>20</v>
+        <v>253</v>
       </c>
       <c r="P20" s="15" t="b">
         <v>1</v>
       </c>
       <c r="Q20" s="15" t="s">
-        <v>93</v>
+        <v>148</v>
       </c>
       <c r="R20" s="15"/>
     </row>
     <row r="21" spans="1:18">
       <c r="A21" s="15">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="B21" s="15" t="s">
-        <v>94</v>
+        <v>149</v>
       </c>
       <c r="C21" s="15" t="s">
-        <v>81</v>
+        <v>66</v>
       </c>
       <c r="D21" s="15" t="s">
-        <v>30</v>
-      </c>
-      <c r="E21" s="15"/>
+        <v>133</v>
+      </c>
+      <c r="E21" s="66" t="s">
+        <v>144</v>
+      </c>
       <c r="F21" s="15" t="s">
-        <v>95</v>
+        <v>145</v>
       </c>
       <c r="G21" s="15" t="s">
-        <v>83</v>
+        <v>146</v>
       </c>
       <c r="H21" s="15" t="s">
-        <v>96</v>
+        <v>150</v>
       </c>
       <c r="I21" s="15" t="s">
-        <v>81</v>
+        <v>51</v>
       </c>
       <c r="J21" s="15" t="s">
-        <v>35</v>
+        <v>138</v>
       </c>
       <c r="K21" s="15">
         <v>0</v>
@@ -3314,13 +3288,13 @@
         <v>1</v>
       </c>
       <c r="O21" s="15">
-        <v>21</v>
+        <v>254</v>
       </c>
       <c r="P21" s="15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q21" s="15" t="s">
-        <v>97</v>
+        <v>151</v>
       </c>
       <c r="R21" s="15"/>
     </row>
@@ -3329,29 +3303,29 @@
         <v>21</v>
       </c>
       <c r="B22" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="C22" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="D22" s="15" t="s">
         <v>98</v>
-      </c>
-      <c r="C22" s="15" t="s">
-        <v>67</v>
-      </c>
-      <c r="D22" s="15" t="s">
-        <v>99</v>
       </c>
       <c r="E22" s="15"/>
       <c r="F22" s="15" t="s">
+        <v>99</v>
+      </c>
+      <c r="G22" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="H22" s="15" t="s">
         <v>100</v>
       </c>
-      <c r="G22" s="15" t="s">
-        <v>59</v>
-      </c>
-      <c r="H22" s="15" t="s">
-        <v>101</v>
-      </c>
       <c r="I22" s="15" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="J22" s="15" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K22" s="15">
         <v>0</v>
@@ -3372,7 +3346,7 @@
         <v>0</v>
       </c>
       <c r="Q22" s="15" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="R22" s="15"/>
     </row>
@@ -3381,29 +3355,29 @@
         <v>22</v>
       </c>
       <c r="B23" s="15" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C23" s="15" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D23" s="15" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E23" s="15"/>
       <c r="F23" s="15" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G23" s="15" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H23" s="15" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I23" s="15" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="J23" s="15" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K23" s="15">
         <v>0</v>
@@ -3424,90 +3398,90 @@
         <v>0</v>
       </c>
       <c r="Q23" s="15" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="R23" s="15"/>
     </row>
     <row r="24" spans="1:18">
       <c r="A24" s="15">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B24" s="15" t="s">
-        <v>106</v>
+        <v>154</v>
       </c>
       <c r="C24" s="15" t="s">
-        <v>67</v>
+        <v>153</v>
       </c>
       <c r="D24" s="15" t="s">
-        <v>99</v>
+        <v>160</v>
       </c>
       <c r="E24" s="15"/>
       <c r="F24" s="15" t="s">
-        <v>100</v>
+        <v>166</v>
       </c>
       <c r="G24" s="15" t="s">
-        <v>107</v>
+        <v>146</v>
       </c>
       <c r="H24" s="15" t="s">
-        <v>108</v>
+        <v>154</v>
       </c>
       <c r="I24" s="15" t="s">
-        <v>34</v>
+        <v>137</v>
       </c>
       <c r="J24" s="15" t="s">
-        <v>35</v>
+        <v>138</v>
       </c>
       <c r="K24" s="15">
         <v>0</v>
       </c>
       <c r="L24" s="15">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="M24" s="15">
         <v>0</v>
       </c>
       <c r="N24" s="15">
-        <v>16000</v>
+        <v>1</v>
       </c>
       <c r="O24" s="15">
-        <v>32</v>
+        <v>455</v>
       </c>
       <c r="P24" s="15" t="b">
         <v>1</v>
       </c>
       <c r="Q24" s="15" t="s">
-        <v>109</v>
+        <v>169</v>
       </c>
       <c r="R24" s="15"/>
     </row>
     <row r="25" spans="1:18" ht="32.25" customHeight="1">
       <c r="A25" s="15">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="B25" s="15" t="s">
-        <v>110</v>
+        <v>152</v>
       </c>
       <c r="C25" s="15" t="s">
-        <v>81</v>
+        <v>153</v>
       </c>
       <c r="D25" s="15" t="s">
-        <v>111</v>
+        <v>133</v>
       </c>
       <c r="E25" s="15"/>
       <c r="F25" s="15" t="s">
-        <v>112</v>
+        <v>145</v>
       </c>
       <c r="G25" s="15" t="s">
-        <v>83</v>
+        <v>146</v>
       </c>
       <c r="H25" s="15" t="s">
-        <v>81</v>
+        <v>154</v>
       </c>
       <c r="I25" s="15" t="s">
-        <v>81</v>
+        <v>137</v>
       </c>
       <c r="J25" s="15" t="s">
-        <v>35</v>
+        <v>138</v>
       </c>
       <c r="K25" s="15">
         <v>0</v>
@@ -3522,154 +3496,150 @@
         <v>1</v>
       </c>
       <c r="O25" s="15">
-        <v>34</v>
+        <v>255</v>
       </c>
       <c r="P25" s="15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q25" s="15" t="s">
-        <v>113</v>
-      </c>
-      <c r="R25" s="15" t="s">
-        <v>114</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="R25" s="15"/>
     </row>
     <row r="26" spans="1:18">
       <c r="A26" s="15">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="B26" s="15" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="C26" s="15" t="s">
-        <v>81</v>
+        <v>66</v>
       </c>
       <c r="D26" s="15" t="s">
-        <v>111</v>
+        <v>98</v>
       </c>
       <c r="E26" s="15"/>
       <c r="F26" s="15" t="s">
-        <v>116</v>
+        <v>99</v>
       </c>
       <c r="G26" s="15" t="s">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="H26" s="15" t="s">
-        <v>81</v>
+        <v>107</v>
       </c>
       <c r="I26" s="15" t="s">
-        <v>81</v>
+        <v>33</v>
       </c>
       <c r="J26" s="15" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K26" s="15">
         <v>0</v>
       </c>
       <c r="L26" s="15">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="M26" s="15">
         <v>0</v>
       </c>
       <c r="N26" s="15">
-        <v>1</v>
+        <v>16000</v>
       </c>
       <c r="O26" s="15">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="P26" s="15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q26" s="15" t="s">
-        <v>117</v>
-      </c>
-      <c r="R26" s="15" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="27" spans="1:18">
+        <v>108</v>
+      </c>
+      <c r="R26" s="15"/>
+    </row>
+    <row r="27" spans="1:18" ht="33">
       <c r="A27" s="15">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="B27" s="15" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C27" s="15" t="s">
-        <v>81</v>
+        <v>66</v>
       </c>
       <c r="D27" s="15" t="s">
-        <v>111</v>
+        <v>98</v>
       </c>
       <c r="E27" s="15"/>
       <c r="F27" s="15" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="G27" s="15" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="H27" s="15" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="I27" s="15" t="s">
-        <v>81</v>
+        <v>48</v>
       </c>
       <c r="J27" s="15" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K27" s="15">
         <v>0</v>
       </c>
       <c r="L27" s="15">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="M27" s="15">
         <v>0</v>
       </c>
       <c r="N27" s="15">
-        <v>1</v>
+        <v>16000</v>
       </c>
       <c r="O27" s="15">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="P27" s="15" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q27" s="15" t="s">
-        <v>120</v>
-      </c>
-      <c r="R27" s="15" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="28" spans="1:18" ht="33">
+        <v>1</v>
+      </c>
+      <c r="Q27" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="R27" s="15"/>
+    </row>
+    <row r="28" spans="1:18">
       <c r="A28" s="15">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B28" s="15" t="s">
-        <v>121</v>
+        <v>65</v>
       </c>
       <c r="C28" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="D28" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="E28" s="15" t="s">
         <v>67</v>
       </c>
-      <c r="D28" s="15" t="s">
-        <v>99</v>
-      </c>
-      <c r="E28" s="15"/>
       <c r="F28" s="15" t="s">
-        <v>122</v>
+        <v>68</v>
       </c>
       <c r="G28" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="H28" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="H28" s="15" t="s">
-        <v>71</v>
-      </c>
       <c r="I28" s="15" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J28" s="15" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K28" s="15">
         <v>0</v>
@@ -3684,206 +3654,200 @@
         <v>16000</v>
       </c>
       <c r="O28" s="15">
-        <v>37</v>
+        <v>13</v>
       </c>
       <c r="P28" s="15" t="b">
         <v>1</v>
       </c>
-      <c r="Q28" s="16" t="s">
-        <v>123</v>
-      </c>
+      <c r="Q28" s="15"/>
       <c r="R28" s="15"/>
     </row>
     <row r="29" spans="1:18">
       <c r="A29" s="15">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="B29" s="15" t="s">
-        <v>124</v>
+        <v>71</v>
       </c>
       <c r="C29" s="15" t="s">
-        <v>81</v>
+        <v>66</v>
       </c>
       <c r="D29" s="15" t="s">
-        <v>111</v>
-      </c>
-      <c r="E29" s="15"/>
+        <v>29</v>
+      </c>
+      <c r="E29" s="15" t="s">
+        <v>30</v>
+      </c>
       <c r="F29" s="15" t="s">
-        <v>125</v>
+        <v>57</v>
       </c>
       <c r="G29" s="15" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="H29" s="15" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="I29" s="15" t="s">
-        <v>81</v>
+        <v>48</v>
       </c>
       <c r="J29" s="15" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K29" s="15">
         <v>0</v>
       </c>
       <c r="L29" s="15">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="M29" s="15">
         <v>0</v>
       </c>
       <c r="N29" s="15">
-        <v>1</v>
+        <v>16000</v>
       </c>
       <c r="O29" s="15">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="P29" s="15" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q29" s="15" t="s">
-        <v>126</v>
-      </c>
-      <c r="R29" s="15" t="s">
-        <v>114</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="Q29" s="15"/>
+      <c r="R29" s="15"/>
     </row>
     <row r="30" spans="1:18">
       <c r="A30" s="15">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="B30" s="15" t="s">
-        <v>127</v>
+        <v>72</v>
       </c>
       <c r="C30" s="15" t="s">
-        <v>81</v>
+        <v>66</v>
       </c>
       <c r="D30" s="15" t="s">
-        <v>111</v>
-      </c>
-      <c r="E30" s="15"/>
+        <v>29</v>
+      </c>
+      <c r="E30" s="15" t="s">
+        <v>73</v>
+      </c>
       <c r="F30" s="15" t="s">
-        <v>128</v>
+        <v>74</v>
       </c>
       <c r="G30" s="15" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="H30" s="15" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="I30" s="15" t="s">
-        <v>81</v>
+        <v>48</v>
       </c>
       <c r="J30" s="15" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K30" s="15">
         <v>0</v>
       </c>
       <c r="L30" s="15">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="M30" s="15">
         <v>0</v>
       </c>
       <c r="N30" s="15">
-        <v>1</v>
+        <v>16000</v>
       </c>
       <c r="O30" s="15">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="P30" s="15" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q30" s="15" t="s">
-        <v>129</v>
-      </c>
-      <c r="R30" s="15" t="s">
-        <v>114</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="Q30" s="15"/>
+      <c r="R30" s="15"/>
     </row>
     <row r="31" spans="1:18">
       <c r="A31" s="15">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="B31" s="15" t="s">
-        <v>130</v>
+        <v>75</v>
       </c>
       <c r="C31" s="15" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="D31" s="15" t="s">
-        <v>111</v>
-      </c>
-      <c r="E31" s="15"/>
+        <v>29</v>
+      </c>
+      <c r="E31" s="15" t="s">
+        <v>73</v>
+      </c>
       <c r="F31" s="15" t="s">
-        <v>131</v>
+        <v>77</v>
       </c>
       <c r="G31" s="15" t="s">
-        <v>83</v>
+        <v>58</v>
       </c>
       <c r="H31" s="15" t="s">
-        <v>81</v>
+        <v>56</v>
       </c>
       <c r="I31" s="15" t="s">
-        <v>81</v>
+        <v>51</v>
       </c>
       <c r="J31" s="15" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K31" s="15">
         <v>0</v>
       </c>
       <c r="L31" s="15">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="M31" s="15">
         <v>0</v>
       </c>
       <c r="N31" s="15">
-        <v>1</v>
+        <v>16000</v>
       </c>
       <c r="O31" s="15">
-        <v>42</v>
+        <v>17</v>
       </c>
       <c r="P31" s="15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q31" s="15" t="s">
-        <v>132</v>
-      </c>
-      <c r="R31" s="15" t="s">
-        <v>114</v>
-      </c>
+        <v>78</v>
+      </c>
+      <c r="R31" s="15"/>
     </row>
     <row r="32" spans="1:18">
       <c r="A32" s="15">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="B32" s="15" t="s">
-        <v>133</v>
+        <v>159</v>
       </c>
       <c r="C32" s="15" t="s">
-        <v>29</v>
+        <v>80</v>
       </c>
       <c r="D32" s="15" t="s">
-        <v>134</v>
+        <v>160</v>
       </c>
       <c r="E32" s="15"/>
       <c r="F32" s="15" t="s">
-        <v>135</v>
+        <v>82</v>
       </c>
       <c r="G32" s="15" t="s">
-        <v>136</v>
+        <v>82</v>
       </c>
       <c r="H32" s="15" t="s">
-        <v>137</v>
+        <v>80</v>
       </c>
       <c r="I32" s="15" t="s">
-        <v>138</v>
+        <v>80</v>
       </c>
       <c r="J32" s="15" t="s">
-        <v>139</v>
+        <v>157</v>
       </c>
       <c r="K32" s="15">
         <v>0</v>
@@ -3898,44 +3862,44 @@
         <v>1</v>
       </c>
       <c r="O32" s="15">
-        <v>250</v>
+        <v>450</v>
       </c>
       <c r="P32" s="15" t="b">
         <v>1</v>
       </c>
       <c r="Q32" s="15" t="s">
-        <v>140</v>
+        <v>161</v>
       </c>
       <c r="R32" s="15"/>
     </row>
     <row r="33" spans="1:18">
       <c r="A33" s="15">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="B33" s="15" t="s">
-        <v>141</v>
+        <v>156</v>
       </c>
       <c r="C33" s="15" t="s">
-        <v>29</v>
+        <v>80</v>
       </c>
       <c r="D33" s="15" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E33" s="15"/>
       <c r="F33" s="15" t="s">
-        <v>142</v>
+        <v>82</v>
       </c>
       <c r="G33" s="15" t="s">
-        <v>136</v>
+        <v>82</v>
       </c>
       <c r="H33" s="15" t="s">
-        <v>137</v>
+        <v>80</v>
       </c>
       <c r="I33" s="15" t="s">
-        <v>138</v>
+        <v>80</v>
       </c>
       <c r="J33" s="15" t="s">
-        <v>139</v>
+        <v>157</v>
       </c>
       <c r="K33" s="15">
         <v>0</v>
@@ -3949,31 +3913,45 @@
       <c r="N33" s="15">
         <v>1</v>
       </c>
-      <c r="O33" s="15">
-        <v>251</v>
+      <c r="O33" s="17">
+        <v>256</v>
       </c>
       <c r="P33" s="15" t="b">
         <v>1</v>
       </c>
       <c r="Q33" s="15" t="s">
-        <v>143</v>
+        <v>158</v>
       </c>
       <c r="R33" s="15"/>
     </row>
     <row r="34" spans="1:18">
       <c r="A34" s="15">
-        <v>18</v>
-      </c>
-      <c r="B34" s="15"/>
-      <c r="C34" s="15"/>
-      <c r="D34" s="15"/>
+        <v>33</v>
+      </c>
+      <c r="B34" s="15" t="s">
+        <v>162</v>
+      </c>
+      <c r="C34" s="15" t="s">
+        <v>80</v>
+      </c>
+      <c r="D34" s="15" t="s">
+        <v>163</v>
+      </c>
       <c r="E34" s="15"/>
-      <c r="F34" s="15"/>
-      <c r="G34" s="15"/>
-      <c r="H34" s="15"/>
-      <c r="I34" s="15"/>
+      <c r="F34" s="15" t="s">
+        <v>82</v>
+      </c>
+      <c r="G34" s="15" t="s">
+        <v>82</v>
+      </c>
+      <c r="H34" s="15" t="s">
+        <v>80</v>
+      </c>
+      <c r="I34" s="15" t="s">
+        <v>80</v>
+      </c>
       <c r="J34" s="15" t="s">
-        <v>139</v>
+        <v>157</v>
       </c>
       <c r="K34" s="15">
         <v>0</v>
@@ -3988,44 +3966,44 @@
         <v>1</v>
       </c>
       <c r="O34" s="15">
-        <v>252</v>
+        <v>451</v>
       </c>
       <c r="P34" s="15" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q34" s="15"/>
+        <v>1</v>
+      </c>
+      <c r="Q34" s="15" t="s">
+        <v>164</v>
+      </c>
       <c r="R34" s="15"/>
     </row>
     <row r="35" spans="1:18">
       <c r="A35" s="15">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="B35" s="15" t="s">
-        <v>144</v>
+        <v>172</v>
       </c>
       <c r="C35" s="15" t="s">
-        <v>67</v>
+        <v>80</v>
       </c>
       <c r="D35" s="15" t="s">
-        <v>134</v>
-      </c>
-      <c r="E35" s="50" t="s">
-        <v>145</v>
-      </c>
+        <v>160</v>
+      </c>
+      <c r="E35" s="67"/>
       <c r="F35" s="15" t="s">
-        <v>146</v>
+        <v>173</v>
       </c>
       <c r="G35" s="15" t="s">
-        <v>147</v>
+        <v>82</v>
       </c>
       <c r="H35" s="15" t="s">
-        <v>148</v>
+        <v>83</v>
       </c>
       <c r="I35" s="15" t="s">
-        <v>52</v>
+        <v>80</v>
       </c>
       <c r="J35" s="15" t="s">
-        <v>139</v>
+        <v>157</v>
       </c>
       <c r="K35" s="15">
         <v>0</v>
@@ -4040,46 +4018,44 @@
         <v>1</v>
       </c>
       <c r="O35" s="15">
-        <v>253</v>
+        <v>460</v>
       </c>
       <c r="P35" s="15" t="b">
         <v>1</v>
       </c>
-      <c r="Q35" s="15" t="s">
-        <v>149</v>
+      <c r="Q35" s="16" t="s">
+        <v>174</v>
       </c>
       <c r="R35" s="15"/>
     </row>
     <row r="36" spans="1:18">
       <c r="A36" s="15">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="B36" s="15" t="s">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="C36" s="15" t="s">
-        <v>67</v>
+        <v>80</v>
       </c>
       <c r="D36" s="15" t="s">
-        <v>134</v>
-      </c>
-      <c r="E36" s="50" t="s">
-        <v>145</v>
-      </c>
+        <v>160</v>
+      </c>
+      <c r="E36" s="67"/>
       <c r="F36" s="15" t="s">
-        <v>146</v>
+        <v>176</v>
       </c>
       <c r="G36" s="15" t="s">
-        <v>147</v>
+        <v>82</v>
       </c>
       <c r="H36" s="15" t="s">
-        <v>151</v>
+        <v>87</v>
       </c>
       <c r="I36" s="15" t="s">
-        <v>52</v>
+        <v>80</v>
       </c>
       <c r="J36" s="15" t="s">
-        <v>139</v>
+        <v>157</v>
       </c>
       <c r="K36" s="15">
         <v>0</v>
@@ -4094,44 +4070,44 @@
         <v>1</v>
       </c>
       <c r="O36" s="15">
-        <v>254</v>
+        <v>461</v>
       </c>
       <c r="P36" s="15" t="b">
         <v>1</v>
       </c>
-      <c r="Q36" s="15" t="s">
-        <v>152</v>
+      <c r="Q36" s="16" t="s">
+        <v>177</v>
       </c>
       <c r="R36" s="15"/>
     </row>
     <row r="37" spans="1:18">
       <c r="A37" s="15">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="B37" s="15" t="s">
-        <v>153</v>
+        <v>178</v>
       </c>
       <c r="C37" s="15" t="s">
-        <v>154</v>
+        <v>80</v>
       </c>
       <c r="D37" s="15" t="s">
-        <v>134</v>
+        <v>160</v>
       </c>
       <c r="E37" s="15"/>
       <c r="F37" s="15" t="s">
-        <v>146</v>
+        <v>179</v>
       </c>
       <c r="G37" s="15" t="s">
-        <v>147</v>
+        <v>82</v>
       </c>
       <c r="H37" s="15" t="s">
-        <v>155</v>
+        <v>91</v>
       </c>
       <c r="I37" s="15" t="s">
-        <v>138</v>
+        <v>80</v>
       </c>
       <c r="J37" s="15" t="s">
-        <v>139</v>
+        <v>157</v>
       </c>
       <c r="K37" s="15">
         <v>0</v>
@@ -4146,44 +4122,44 @@
         <v>1</v>
       </c>
       <c r="O37" s="15">
-        <v>255</v>
+        <v>462</v>
       </c>
       <c r="P37" s="15" t="b">
         <v>1</v>
       </c>
-      <c r="Q37" s="15" t="s">
-        <v>156</v>
+      <c r="Q37" s="16" t="s">
+        <v>180</v>
       </c>
       <c r="R37" s="15"/>
     </row>
     <row r="38" spans="1:18">
       <c r="A38" s="15">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="B38" s="15" t="s">
-        <v>157</v>
+        <v>79</v>
       </c>
       <c r="C38" s="15" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D38" s="15" t="s">
-        <v>134</v>
+        <v>29</v>
       </c>
       <c r="E38" s="15"/>
       <c r="F38" s="15" t="s">
+        <v>81</v>
+      </c>
+      <c r="G38" s="15" t="s">
+        <v>82</v>
+      </c>
+      <c r="H38" s="15" t="s">
         <v>83</v>
       </c>
-      <c r="G38" s="15" t="s">
-        <v>83</v>
-      </c>
-      <c r="H38" s="15" t="s">
-        <v>81</v>
-      </c>
       <c r="I38" s="15" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="J38" s="15" t="s">
-        <v>158</v>
+        <v>34</v>
       </c>
       <c r="K38" s="15">
         <v>0</v>
@@ -4197,45 +4173,45 @@
       <c r="N38" s="15">
         <v>1</v>
       </c>
-      <c r="O38" s="17">
-        <v>256</v>
+      <c r="O38" s="15">
+        <v>18</v>
       </c>
       <c r="P38" s="15" t="b">
         <v>1</v>
       </c>
       <c r="Q38" s="15" t="s">
-        <v>159</v>
+        <v>84</v>
       </c>
       <c r="R38" s="15"/>
     </row>
     <row r="39" spans="1:18">
       <c r="A39" s="15">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="B39" s="15" t="s">
-        <v>160</v>
+        <v>85</v>
       </c>
       <c r="C39" s="15" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D39" s="15" t="s">
-        <v>161</v>
+        <v>29</v>
       </c>
       <c r="E39" s="15"/>
       <c r="F39" s="15" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="G39" s="15" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H39" s="15" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="I39" s="15" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="J39" s="15" t="s">
-        <v>158</v>
+        <v>34</v>
       </c>
       <c r="K39" s="15">
         <v>0</v>
@@ -4250,44 +4226,44 @@
         <v>1</v>
       </c>
       <c r="O39" s="15">
-        <v>450</v>
+        <v>19</v>
       </c>
       <c r="P39" s="15" t="b">
         <v>1</v>
       </c>
       <c r="Q39" s="15" t="s">
-        <v>162</v>
+        <v>88</v>
       </c>
       <c r="R39" s="15"/>
     </row>
     <row r="40" spans="1:18">
       <c r="A40" s="15">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="B40" s="15" t="s">
-        <v>163</v>
+        <v>89</v>
       </c>
       <c r="C40" s="15" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D40" s="15" t="s">
-        <v>164</v>
+        <v>29</v>
       </c>
       <c r="E40" s="15"/>
       <c r="F40" s="15" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="G40" s="15" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H40" s="15" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="I40" s="15" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="J40" s="15" t="s">
-        <v>158</v>
+        <v>34</v>
       </c>
       <c r="K40" s="15">
         <v>0</v>
@@ -4302,30 +4278,44 @@
         <v>1</v>
       </c>
       <c r="O40" s="15">
-        <v>451</v>
+        <v>20</v>
       </c>
       <c r="P40" s="15" t="b">
         <v>1</v>
       </c>
       <c r="Q40" s="15" t="s">
-        <v>165</v>
+        <v>92</v>
       </c>
       <c r="R40" s="15"/>
     </row>
     <row r="41" spans="1:18">
       <c r="A41" s="15">
-        <v>15</v>
-      </c>
-      <c r="B41" s="15"/>
-      <c r="C41" s="15"/>
-      <c r="D41" s="15"/>
+        <v>40</v>
+      </c>
+      <c r="B41" s="15" t="s">
+        <v>93</v>
+      </c>
+      <c r="C41" s="15" t="s">
+        <v>80</v>
+      </c>
+      <c r="D41" s="15" t="s">
+        <v>29</v>
+      </c>
       <c r="E41" s="15"/>
-      <c r="F41" s="15"/>
-      <c r="G41" s="15"/>
-      <c r="H41" s="15"/>
-      <c r="I41" s="15"/>
+      <c r="F41" s="15" t="s">
+        <v>94</v>
+      </c>
+      <c r="G41" s="15" t="s">
+        <v>82</v>
+      </c>
+      <c r="H41" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="I41" s="15" t="s">
+        <v>80</v>
+      </c>
       <c r="J41" s="15" t="s">
-        <v>139</v>
+        <v>34</v>
       </c>
       <c r="K41" s="15">
         <v>0</v>
@@ -4340,42 +4330,44 @@
         <v>1</v>
       </c>
       <c r="O41" s="15">
-        <v>452</v>
+        <v>21</v>
       </c>
       <c r="P41" s="15" t="b">
         <v>0</v>
       </c>
-      <c r="Q41" s="15"/>
+      <c r="Q41" s="15" t="s">
+        <v>96</v>
+      </c>
       <c r="R41" s="15"/>
     </row>
     <row r="42" spans="1:18">
       <c r="A42" s="15">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="B42" s="15" t="s">
-        <v>166</v>
+        <v>109</v>
       </c>
       <c r="C42" s="15" t="s">
-        <v>67</v>
+        <v>80</v>
       </c>
       <c r="D42" s="15" t="s">
-        <v>161</v>
+        <v>110</v>
       </c>
       <c r="E42" s="15"/>
       <c r="F42" s="15" t="s">
-        <v>167</v>
+        <v>111</v>
       </c>
       <c r="G42" s="15" t="s">
-        <v>147</v>
+        <v>82</v>
       </c>
       <c r="H42" s="15" t="s">
-        <v>166</v>
+        <v>80</v>
       </c>
       <c r="I42" s="15" t="s">
-        <v>52</v>
+        <v>80</v>
       </c>
       <c r="J42" s="15" t="s">
-        <v>139</v>
+        <v>34</v>
       </c>
       <c r="K42" s="15">
         <v>0</v>
@@ -4390,44 +4382,46 @@
         <v>1</v>
       </c>
       <c r="O42" s="15">
-        <v>453</v>
+        <v>34</v>
       </c>
       <c r="P42" s="15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q42" s="15" t="s">
-        <v>168</v>
-      </c>
-      <c r="R42" s="15"/>
+        <v>112</v>
+      </c>
+      <c r="R42" s="15" t="s">
+        <v>113</v>
+      </c>
     </row>
     <row r="43" spans="1:18">
       <c r="A43" s="15">
-        <v>17</v>
+        <v>42</v>
       </c>
       <c r="B43" s="15" t="s">
-        <v>148</v>
+        <v>114</v>
       </c>
       <c r="C43" s="15" t="s">
-        <v>67</v>
+        <v>80</v>
       </c>
       <c r="D43" s="15" t="s">
-        <v>161</v>
+        <v>110</v>
       </c>
       <c r="E43" s="15"/>
       <c r="F43" s="15" t="s">
-        <v>167</v>
+        <v>115</v>
       </c>
       <c r="G43" s="15" t="s">
-        <v>147</v>
+        <v>82</v>
       </c>
       <c r="H43" s="15" t="s">
-        <v>148</v>
+        <v>80</v>
       </c>
       <c r="I43" s="15" t="s">
-        <v>52</v>
+        <v>80</v>
       </c>
       <c r="J43" s="15" t="s">
-        <v>139</v>
+        <v>34</v>
       </c>
       <c r="K43" s="15">
         <v>0</v>
@@ -4442,44 +4436,46 @@
         <v>1</v>
       </c>
       <c r="O43" s="15">
-        <v>454</v>
+        <v>35</v>
       </c>
       <c r="P43" s="15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q43" s="15" t="s">
-        <v>169</v>
-      </c>
-      <c r="R43" s="15"/>
+        <v>116</v>
+      </c>
+      <c r="R43" s="15" t="s">
+        <v>113</v>
+      </c>
     </row>
     <row r="44" spans="1:18">
       <c r="A44" s="15">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="B44" s="15" t="s">
-        <v>155</v>
+        <v>117</v>
       </c>
       <c r="C44" s="15" t="s">
-        <v>154</v>
+        <v>80</v>
       </c>
       <c r="D44" s="15" t="s">
-        <v>161</v>
+        <v>110</v>
       </c>
       <c r="E44" s="15"/>
       <c r="F44" s="15" t="s">
-        <v>167</v>
+        <v>118</v>
       </c>
       <c r="G44" s="15" t="s">
-        <v>147</v>
+        <v>82</v>
       </c>
       <c r="H44" s="15" t="s">
-        <v>155</v>
+        <v>80</v>
       </c>
       <c r="I44" s="15" t="s">
-        <v>138</v>
+        <v>80</v>
       </c>
       <c r="J44" s="15" t="s">
-        <v>139</v>
+        <v>34</v>
       </c>
       <c r="K44" s="15">
         <v>0</v>
@@ -4494,42 +4490,46 @@
         <v>1</v>
       </c>
       <c r="O44" s="15">
-        <v>455</v>
+        <v>36</v>
       </c>
       <c r="P44" s="15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q44" s="15" t="s">
-        <v>170</v>
-      </c>
-      <c r="R44" s="15"/>
+        <v>119</v>
+      </c>
+      <c r="R44" s="15" t="s">
+        <v>113</v>
+      </c>
     </row>
     <row r="45" spans="1:18">
       <c r="A45" s="15">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="B45" s="15" t="s">
-        <v>171</v>
+        <v>123</v>
       </c>
       <c r="C45" s="15" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D45" s="15" t="s">
-        <v>164</v>
+        <v>110</v>
       </c>
       <c r="E45" s="15"/>
-      <c r="F45" s="15"/>
+      <c r="F45" s="15" t="s">
+        <v>124</v>
+      </c>
       <c r="G45" s="15" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H45" s="15" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="I45" s="15" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="J45" s="15" t="s">
-        <v>158</v>
+        <v>34</v>
       </c>
       <c r="K45" s="15">
         <v>0</v>
@@ -4544,44 +4544,46 @@
         <v>1</v>
       </c>
       <c r="O45" s="15">
-        <v>456</v>
+        <v>40</v>
       </c>
       <c r="P45" s="15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q45" s="15" t="s">
-        <v>172</v>
-      </c>
-      <c r="R45" s="15"/>
+        <v>125</v>
+      </c>
+      <c r="R45" s="15" t="s">
+        <v>113</v>
+      </c>
     </row>
     <row r="46" spans="1:18">
       <c r="A46" s="15">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="B46" s="15" t="s">
-        <v>173</v>
+        <v>126</v>
       </c>
       <c r="C46" s="15" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D46" s="15" t="s">
-        <v>161</v>
+        <v>110</v>
       </c>
       <c r="E46" s="15"/>
       <c r="F46" s="15" t="s">
-        <v>174</v>
+        <v>127</v>
       </c>
       <c r="G46" s="15" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H46" s="15" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="I46" s="15" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="J46" s="15" t="s">
-        <v>158</v>
+        <v>34</v>
       </c>
       <c r="K46" s="15">
         <v>0</v>
@@ -4596,44 +4598,46 @@
         <v>1</v>
       </c>
       <c r="O46" s="15">
-        <v>460</v>
+        <v>41</v>
       </c>
       <c r="P46" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q46" s="16" t="s">
-        <v>175</v>
-      </c>
-      <c r="R46" s="15"/>
+        <v>0</v>
+      </c>
+      <c r="Q46" s="15" t="s">
+        <v>128</v>
+      </c>
+      <c r="R46" s="15" t="s">
+        <v>113</v>
+      </c>
     </row>
     <row r="47" spans="1:18">
       <c r="A47" s="15">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="B47" s="15" t="s">
-        <v>176</v>
+        <v>129</v>
       </c>
       <c r="C47" s="15" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D47" s="15" t="s">
-        <v>161</v>
+        <v>110</v>
       </c>
       <c r="E47" s="15"/>
       <c r="F47" s="15" t="s">
-        <v>177</v>
+        <v>130</v>
       </c>
       <c r="G47" s="15" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H47" s="15" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="I47" s="15" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="J47" s="15" t="s">
-        <v>158</v>
+        <v>34</v>
       </c>
       <c r="K47" s="15">
         <v>0</v>
@@ -4648,44 +4652,46 @@
         <v>1</v>
       </c>
       <c r="O47" s="15">
-        <v>461</v>
+        <v>42</v>
       </c>
       <c r="P47" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q47" s="16" t="s">
-        <v>178</v>
-      </c>
-      <c r="R47" s="15"/>
+        <v>0</v>
+      </c>
+      <c r="Q47" s="15" t="s">
+        <v>131</v>
+      </c>
+      <c r="R47" s="15" t="s">
+        <v>113</v>
+      </c>
     </row>
     <row r="48" spans="1:18">
       <c r="A48" s="15">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="B48" s="15" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C48" s="15" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D48" s="15" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E48" s="15"/>
       <c r="F48" s="15" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="G48" s="15" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H48" s="15" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="I48" s="15" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="J48" s="15" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="K48" s="15">
         <v>0</v>
@@ -4700,44 +4706,46 @@
         <v>1</v>
       </c>
       <c r="O48" s="15">
-        <v>462</v>
+        <v>470</v>
       </c>
       <c r="P48" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q48" s="16" t="s">
-        <v>181</v>
-      </c>
-      <c r="R48" s="15"/>
+        <v>0</v>
+      </c>
+      <c r="Q48" s="15" t="s">
+        <v>183</v>
+      </c>
+      <c r="R48" s="15" t="s">
+        <v>184</v>
+      </c>
     </row>
     <row r="49" spans="1:18">
       <c r="A49" s="15">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B49" s="15" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="C49" s="15" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D49" s="15" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E49" s="15"/>
       <c r="F49" s="15" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="G49" s="15" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H49" s="15" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="I49" s="15" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="J49" s="15" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="K49" s="15">
         <v>0</v>
@@ -4752,46 +4760,44 @@
         <v>1</v>
       </c>
       <c r="O49" s="15">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="P49" s="15" t="b">
         <v>0</v>
       </c>
       <c r="Q49" s="15" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="R49" s="15" t="s">
-        <v>185</v>
+        <v>113</v>
       </c>
     </row>
     <row r="50" spans="1:18">
       <c r="A50" s="15">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B50" s="15" t="s">
-        <v>186</v>
+        <v>170</v>
       </c>
       <c r="C50" s="15" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D50" s="15" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E50" s="15"/>
-      <c r="F50" s="15" t="s">
-        <v>187</v>
-      </c>
+      <c r="F50" s="15"/>
       <c r="G50" s="15" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H50" s="15" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="I50" s="15" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="J50" s="15" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="K50" s="15">
         <v>0</v>
@@ -4806,22 +4812,25 @@
         <v>1</v>
       </c>
       <c r="O50" s="15">
-        <v>471</v>
+        <v>456</v>
       </c>
       <c r="P50" s="15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q50" s="15" t="s">
-        <v>188</v>
-      </c>
-      <c r="R50" s="15" t="s">
-        <v>114</v>
+        <v>171</v>
+      </c>
+      <c r="R50" s="15"/>
+    </row>
+    <row r="56" spans="1:18">
+      <c r="G56" s="1" t="s">
+        <v>359</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:R1" xr:uid="{7C485614-A5BE-4FB7-B2E6-807540769775}">
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:R50">
-      <sortCondition ref="O1"/>
+      <sortCondition ref="A1"/>
     </sortState>
   </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -4840,15 +4849,15 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B2">
         <v>1000</v>
@@ -4856,7 +4865,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B3">
         <v>1000</v>
@@ -4864,7 +4873,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B4">
         <v>1000</v>
@@ -4872,7 +4881,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B5">
         <v>1000</v>
@@ -4900,28 +4909,28 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>192</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>193</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -4929,19 +4938,19 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="F2" s="11" t="s">
         <v>195</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="F2" s="11" t="s">
-        <v>196</v>
       </c>
       <c r="G2" s="1">
         <v>16000</v>
@@ -4955,19 +4964,19 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="D3" s="1" t="s">
+      <c r="E3" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>198</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>199</v>
       </c>
       <c r="G3" s="1">
         <v>100</v>
@@ -4981,19 +4990,19 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="D4" s="1" t="s">
+      <c r="E4" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>201</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>202</v>
       </c>
       <c r="G4" s="1">
         <v>100</v>
@@ -5007,19 +5016,19 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>204</v>
-      </c>
       <c r="E5" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="G5" s="1">
         <v>100</v>
@@ -5033,16 +5042,16 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="G6" s="1">
         <v>100</v>
@@ -5056,16 +5065,16 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="C7" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="E7" s="1" t="s">
+      <c r="F7" s="1" t="s">
         <v>207</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>208</v>
       </c>
       <c r="G7" s="1">
         <v>3</v>
@@ -5079,16 +5088,16 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G8" s="1">
         <v>10000</v>
@@ -5102,13 +5111,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H9" s="1">
         <v>8</v>
@@ -5119,16 +5128,16 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="D10" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="C10" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>212</v>
-      </c>
       <c r="E10" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H10" s="1">
         <v>1</v>
@@ -5139,16 +5148,16 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="D11" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="C11" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>214</v>
-      </c>
       <c r="E11" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H11" s="1">
         <v>2</v>
@@ -5159,19 +5168,19 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G12" s="1">
         <v>1000</v>
@@ -5185,19 +5194,19 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="D13" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="C13" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>217</v>
-      </c>
       <c r="E13" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="F13" s="1" t="s">
         <v>207</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>208</v>
       </c>
       <c r="G13" s="1">
         <v>3</v>
@@ -5211,19 +5220,19 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="D14" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="C14" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>219</v>
-      </c>
       <c r="E14" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="G14" s="1">
         <v>1000</v>
@@ -5237,19 +5246,19 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="D15" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="C15" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>221</v>
-      </c>
       <c r="E15" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="F15" s="1" t="s">
         <v>207</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>208</v>
       </c>
       <c r="G15" s="1">
         <v>0</v>
@@ -5263,19 +5272,19 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="D16" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="C16" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>223</v>
-      </c>
       <c r="E16" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="H16" s="1">
         <v>7</v>
@@ -5286,13 +5295,13 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H17" s="1">
         <v>8</v>
@@ -5318,16 +5327,16 @@
   <sheetData>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D2" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
   </sheetData>
@@ -5351,389 +5360,389 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>226</v>
       </c>
-      <c r="B1" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C1" s="3" t="s">
+      <c r="D1" s="3" t="s">
         <v>227</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>228</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="5" t="s">
         <v>229</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="G1" s="3" t="s">
         <v>230</v>
       </c>
-      <c r="G1" s="3" t="s">
-        <v>231</v>
-      </c>
       <c r="H1" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="I1" s="3" t="s">
         <v>26</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="C2" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>235</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>236</v>
       </c>
       <c r="F2" s="6">
         <f>175241*4</f>
         <v>700964</v>
       </c>
       <c r="G2" s="7" t="s">
+        <v>236</v>
+      </c>
+      <c r="H2" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>238</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>240</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>241</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>242</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>243</v>
       </c>
       <c r="F3" s="6">
         <v>237420</v>
       </c>
       <c r="G3" s="8" t="s">
+        <v>243</v>
+      </c>
+      <c r="H3" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="H3" s="1" t="s">
-        <v>245</v>
-      </c>
       <c r="I3" s="1" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="1" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>233</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>234</v>
       </c>
       <c r="D4" s="1"/>
       <c r="E4" s="1" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="F4" s="6">
         <v>509000</v>
       </c>
       <c r="G4" s="8" t="s">
+        <v>247</v>
+      </c>
+      <c r="H4" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="H4" s="1" t="s">
-        <v>249</v>
-      </c>
       <c r="I4" s="1" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>233</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>234</v>
       </c>
       <c r="D5" s="1"/>
       <c r="E5" s="1" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="F5" s="6"/>
       <c r="G5" s="1"/>
       <c r="H5" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="I5" s="1" t="s">
         <v>251</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>252</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="33">
       <c r="A6" s="1" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B6" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>233</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>234</v>
       </c>
       <c r="D6" s="1"/>
       <c r="E6" s="1" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="F6" s="6"/>
       <c r="G6" s="1"/>
       <c r="H6" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="I6" s="2" t="s">
         <v>255</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>256</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="1" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B7" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>233</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>234</v>
       </c>
       <c r="D7" s="1"/>
       <c r="E7" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="F7" s="6"/>
       <c r="G7" s="1"/>
       <c r="H7" s="1" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="I7" s="1"/>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="1" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B8" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="C8" s="1" t="s">
         <v>233</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>234</v>
       </c>
       <c r="D8" s="1"/>
       <c r="E8" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="F8" s="6">
         <v>85000</v>
       </c>
       <c r="G8" s="9" t="s">
+        <v>260</v>
+      </c>
+      <c r="H8" s="1" t="s">
         <v>261</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>262</v>
       </c>
       <c r="I8" s="1"/>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="1" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B9" s="1"/>
       <c r="C9" s="1" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D9" s="1"/>
       <c r="E9" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="F9" s="6">
         <v>55200</v>
       </c>
       <c r="G9" s="8" t="s">
+        <v>264</v>
+      </c>
+      <c r="H9" s="1" t="s">
         <v>265</v>
-      </c>
-      <c r="H9" s="1" t="s">
-        <v>266</v>
       </c>
       <c r="I9" s="1"/>
     </row>
     <row r="10" spans="1:9" ht="33">
       <c r="A10" s="1" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
       <c r="E10" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="F10" s="6"/>
       <c r="G10" s="1"/>
       <c r="H10" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="I10" s="2" t="s">
         <v>268</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>269</v>
       </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="C11" s="1" t="s">
         <v>271</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="D11" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="D11" s="1" t="s">
-        <v>273</v>
-      </c>
       <c r="E11" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="F11" s="6"/>
       <c r="G11" s="8" t="s">
+        <v>273</v>
+      </c>
+      <c r="H11" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="H11" s="1" t="s">
+      <c r="I11" s="1" t="s">
         <v>275</v>
-      </c>
-      <c r="I11" s="1" t="s">
-        <v>276</v>
       </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="B12" s="10" t="s">
         <v>277</v>
       </c>
-      <c r="B12" s="10" t="s">
+      <c r="C12" s="1" t="s">
         <v>278</v>
       </c>
-      <c r="C12" s="1" t="s">
+      <c r="D12" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="D12" s="1" t="s">
-        <v>280</v>
-      </c>
       <c r="E12" s="1" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="F12" s="6">
         <f>6700*4</f>
         <v>26800</v>
       </c>
       <c r="G12" s="7" t="s">
+        <v>280</v>
+      </c>
+      <c r="H12" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="H12" s="1" t="s">
-        <v>282</v>
-      </c>
       <c r="I12" s="1" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="B13" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="C13" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="D13" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="D13" s="1" t="s">
-        <v>286</v>
-      </c>
       <c r="E13" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="F13" s="6">
         <v>2464000</v>
       </c>
       <c r="G13" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="H13" s="1" t="s">
         <v>287</v>
-      </c>
-      <c r="H13" s="1" t="s">
-        <v>288</v>
       </c>
       <c r="I13" s="1"/>
     </row>
     <row r="14" spans="1:9" ht="33">
       <c r="A14" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="B14" s="2" t="s">
         <v>289</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>290</v>
       </c>
       <c r="C14" s="1"/>
       <c r="D14" s="1" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="F14" s="6">
         <v>230989</v>
       </c>
       <c r="G14" s="8" t="s">
+        <v>291</v>
+      </c>
+      <c r="H14" s="1" t="s">
         <v>292</v>
-      </c>
-      <c r="H14" s="1" t="s">
-        <v>293</v>
       </c>
       <c r="I14" s="1"/>
     </row>
     <row r="16" spans="1:9">
       <c r="D16" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="18" spans="1:9">
       <c r="A18" t="s">
+        <v>294</v>
+      </c>
+      <c r="C18" t="s">
         <v>295</v>
       </c>
-      <c r="C18" t="s">
+      <c r="D18" s="12" t="s">
         <v>296</v>
       </c>
-      <c r="D18" s="12" t="s">
-        <v>297</v>
-      </c>
       <c r="E18" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="F18" s="4">
         <v>311300</v>
       </c>
       <c r="G18" s="13" t="s">
+        <v>297</v>
+      </c>
+      <c r="H18" t="s">
         <v>298</v>
       </c>
-      <c r="H18" t="s">
+      <c r="I18" t="s">
         <v>299</v>
-      </c>
-      <c r="I18" t="s">
-        <v>300</v>
       </c>
     </row>
   </sheetData>
@@ -5766,505 +5775,505 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="45" t="s">
+        <v>300</v>
+      </c>
+      <c r="B1" s="46" t="s">
         <v>301</v>
       </c>
-      <c r="B1" s="46" t="s">
+      <c r="C1" s="47" t="s">
         <v>302</v>
       </c>
-      <c r="C1" s="47" t="s">
+      <c r="D1" s="48" t="s">
         <v>303</v>
       </c>
-      <c r="D1" s="48" t="s">
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="52" t="s">
         <v>304</v>
       </c>
-    </row>
-    <row r="2" spans="1:4">
-      <c r="A2" s="53" t="s">
+      <c r="B2" s="18" t="s">
         <v>305</v>
-      </c>
-      <c r="B2" s="18" t="s">
-        <v>306</v>
       </c>
       <c r="C2" s="19">
         <v>10000000</v>
       </c>
-      <c r="D2" s="54">
+      <c r="D2" s="53">
         <v>18960000</v>
       </c>
     </row>
     <row r="3" spans="1:4">
-      <c r="A3" s="53"/>
+      <c r="A3" s="52"/>
       <c r="B3" s="20" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C3" s="21">
         <v>2000000</v>
       </c>
-      <c r="D3" s="55"/>
+      <c r="D3" s="54"/>
     </row>
     <row r="4" spans="1:4">
-      <c r="A4" s="53"/>
+      <c r="A4" s="52"/>
       <c r="B4" s="20" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C4" s="21">
         <v>1200000</v>
       </c>
-      <c r="D4" s="55"/>
+      <c r="D4" s="54"/>
     </row>
     <row r="5" spans="1:4">
-      <c r="A5" s="53"/>
+      <c r="A5" s="52"/>
       <c r="B5" s="20" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C5" s="21">
         <v>800000</v>
       </c>
-      <c r="D5" s="55"/>
+      <c r="D5" s="54"/>
     </row>
     <row r="6" spans="1:4">
-      <c r="A6" s="53"/>
+      <c r="A6" s="52"/>
       <c r="B6" s="20" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C6" s="21">
         <v>400000</v>
       </c>
-      <c r="D6" s="55"/>
+      <c r="D6" s="54"/>
     </row>
     <row r="7" spans="1:4">
-      <c r="A7" s="53"/>
+      <c r="A7" s="52"/>
       <c r="B7" s="20" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C7" s="21">
         <v>1000000</v>
       </c>
-      <c r="D7" s="55"/>
+      <c r="D7" s="54"/>
     </row>
     <row r="8" spans="1:4">
-      <c r="A8" s="53"/>
+      <c r="A8" s="52"/>
       <c r="B8" s="20" t="s">
+        <v>311</v>
+      </c>
+      <c r="C8" s="22" t="s">
         <v>312</v>
       </c>
-      <c r="C8" s="22" t="s">
+      <c r="D8" s="54"/>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="52"/>
+      <c r="B9" s="20" t="s">
         <v>313</v>
-      </c>
-      <c r="D8" s="55"/>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9" s="53"/>
-      <c r="B9" s="20" t="s">
-        <v>314</v>
       </c>
       <c r="C9" s="21">
         <v>3500000</v>
       </c>
-      <c r="D9" s="55"/>
+      <c r="D9" s="54"/>
     </row>
     <row r="10" spans="1:4">
-      <c r="A10" s="53"/>
+      <c r="A10" s="52"/>
       <c r="B10" s="20" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C10" s="21">
         <v>60000</v>
       </c>
-      <c r="D10" s="55"/>
+      <c r="D10" s="54"/>
     </row>
     <row r="11" spans="1:4">
-      <c r="A11" s="56" t="s">
+      <c r="A11" s="55" t="s">
+        <v>315</v>
+      </c>
+      <c r="B11" s="18" t="s">
         <v>316</v>
-      </c>
-      <c r="B11" s="18" t="s">
-        <v>317</v>
       </c>
       <c r="C11" s="23">
         <v>200000</v>
       </c>
-      <c r="D11" s="54">
+      <c r="D11" s="53">
         <v>4380000</v>
       </c>
     </row>
     <row r="12" spans="1:4">
-      <c r="A12" s="53"/>
+      <c r="A12" s="52"/>
       <c r="B12" s="20" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C12" s="21">
         <v>200000</v>
       </c>
-      <c r="D12" s="55"/>
+      <c r="D12" s="54"/>
     </row>
     <row r="13" spans="1:4">
-      <c r="A13" s="53"/>
+      <c r="A13" s="52"/>
       <c r="B13" s="20" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C13" s="21">
         <v>500000</v>
       </c>
-      <c r="D13" s="55"/>
+      <c r="D13" s="54"/>
     </row>
     <row r="14" spans="1:4">
-      <c r="A14" s="53"/>
+      <c r="A14" s="52"/>
       <c r="B14" s="20" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C14" s="24">
         <v>500000</v>
       </c>
-      <c r="D14" s="55"/>
+      <c r="D14" s="54"/>
     </row>
     <row r="15" spans="1:4">
-      <c r="A15" s="53"/>
+      <c r="A15" s="52"/>
       <c r="B15" s="20" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C15" s="24">
         <v>1000000</v>
       </c>
-      <c r="D15" s="55"/>
+      <c r="D15" s="54"/>
     </row>
     <row r="16" spans="1:4">
-      <c r="A16" s="53"/>
+      <c r="A16" s="52"/>
       <c r="B16" s="20" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C16" s="24">
         <v>1000000</v>
       </c>
-      <c r="D16" s="55"/>
+      <c r="D16" s="54"/>
     </row>
     <row r="17" spans="1:4">
-      <c r="A17" s="53"/>
+      <c r="A17" s="52"/>
       <c r="B17" s="20" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C17" s="24">
         <v>1850000</v>
       </c>
-      <c r="D17" s="55"/>
+      <c r="D17" s="54"/>
     </row>
     <row r="18" spans="1:4">
-      <c r="A18" s="53"/>
+      <c r="A18" s="52"/>
       <c r="B18" s="20" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C18" s="24">
         <v>300000</v>
       </c>
-      <c r="D18" s="55"/>
+      <c r="D18" s="54"/>
     </row>
     <row r="19" spans="1:4">
-      <c r="A19" s="53"/>
+      <c r="A19" s="52"/>
       <c r="B19" s="20" t="s">
+        <v>324</v>
+      </c>
+      <c r="C19" s="25" t="s">
         <v>325</v>
       </c>
-      <c r="C19" s="25" t="s">
+      <c r="D19" s="54"/>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20" s="52"/>
+      <c r="B20" s="20" t="s">
         <v>326</v>
-      </c>
-      <c r="D19" s="55"/>
-    </row>
-    <row r="20" spans="1:4">
-      <c r="A20" s="53"/>
-      <c r="B20" s="20" t="s">
-        <v>327</v>
       </c>
       <c r="C20" s="21">
         <v>200000</v>
       </c>
-      <c r="D20" s="55"/>
+      <c r="D20" s="54"/>
     </row>
     <row r="21" spans="1:4">
-      <c r="A21" s="53"/>
+      <c r="A21" s="52"/>
       <c r="B21" s="20" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C21" s="21">
         <v>1200000</v>
       </c>
-      <c r="D21" s="55"/>
+      <c r="D21" s="54"/>
     </row>
     <row r="22" spans="1:4">
-      <c r="A22" s="53"/>
+      <c r="A22" s="52"/>
       <c r="B22" s="20" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C22" s="21">
         <v>30000</v>
       </c>
-      <c r="D22" s="55"/>
+      <c r="D22" s="54"/>
     </row>
     <row r="23" spans="1:4">
-      <c r="A23" s="53"/>
+      <c r="A23" s="52"/>
       <c r="B23" s="20" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C23" s="21">
         <v>450000</v>
       </c>
-      <c r="D23" s="55"/>
+      <c r="D23" s="54"/>
     </row>
     <row r="24" spans="1:4">
-      <c r="A24" s="53"/>
+      <c r="A24" s="52"/>
       <c r="B24" s="20" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C24" s="21">
         <v>450000</v>
       </c>
-      <c r="D24" s="55"/>
+      <c r="D24" s="54"/>
     </row>
     <row r="25" spans="1:4">
-      <c r="A25" s="53"/>
+      <c r="A25" s="52"/>
       <c r="B25" s="20" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C25" s="21">
         <v>50000</v>
       </c>
-      <c r="D25" s="55"/>
+      <c r="D25" s="54"/>
     </row>
     <row r="26" spans="1:4">
-      <c r="A26" s="53"/>
+      <c r="A26" s="52"/>
       <c r="B26" s="20" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C26" s="21">
         <v>100000</v>
       </c>
-      <c r="D26" s="55"/>
+      <c r="D26" s="54"/>
     </row>
     <row r="27" spans="1:4">
-      <c r="A27" s="53"/>
+      <c r="A27" s="52"/>
       <c r="B27" s="20" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C27" s="21">
         <v>500000</v>
       </c>
-      <c r="D27" s="55"/>
+      <c r="D27" s="54"/>
     </row>
     <row r="28" spans="1:4">
-      <c r="A28" s="57"/>
+      <c r="A28" s="56"/>
       <c r="B28" s="26" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C28" s="27">
         <v>700000</v>
       </c>
-      <c r="D28" s="58"/>
+      <c r="D28" s="57"/>
     </row>
     <row r="29" spans="1:4">
-      <c r="A29" s="56" t="s">
+      <c r="A29" s="55" t="s">
+        <v>335</v>
+      </c>
+      <c r="B29" s="20" t="s">
         <v>336</v>
-      </c>
-      <c r="B29" s="20" t="s">
-        <v>337</v>
       </c>
       <c r="C29" s="21">
         <v>1200000</v>
       </c>
-      <c r="D29" s="59">
+      <c r="D29" s="58">
         <v>6900000</v>
       </c>
     </row>
     <row r="30" spans="1:4">
-      <c r="A30" s="53"/>
+      <c r="A30" s="52"/>
       <c r="B30" s="20" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C30" s="21">
         <v>550000</v>
       </c>
-      <c r="D30" s="55"/>
+      <c r="D30" s="54"/>
     </row>
     <row r="31" spans="1:4">
-      <c r="A31" s="53"/>
+      <c r="A31" s="52"/>
       <c r="B31" s="20" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C31" s="21">
         <v>1200000</v>
       </c>
-      <c r="D31" s="55"/>
+      <c r="D31" s="54"/>
     </row>
     <row r="32" spans="1:4">
-      <c r="A32" s="53"/>
+      <c r="A32" s="52"/>
       <c r="B32" s="20" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C32" s="21">
         <v>450000</v>
       </c>
-      <c r="D32" s="55"/>
+      <c r="D32" s="54"/>
     </row>
     <row r="33" spans="1:8">
-      <c r="A33" s="53"/>
+      <c r="A33" s="52"/>
       <c r="B33" s="20" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C33" s="21">
         <v>3500000</v>
       </c>
-      <c r="D33" s="55"/>
+      <c r="D33" s="54"/>
     </row>
     <row r="34" spans="1:8">
-      <c r="A34" s="53"/>
+      <c r="A34" s="52"/>
       <c r="B34" s="20" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C34" s="28">
         <v>300000</v>
       </c>
-      <c r="D34" s="55"/>
+      <c r="D34" s="54"/>
     </row>
     <row r="35" spans="1:8">
-      <c r="A35" s="53"/>
+      <c r="A35" s="52"/>
       <c r="B35" s="20" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C35" s="28">
         <v>30000</v>
       </c>
-      <c r="D35" s="55"/>
+      <c r="D35" s="54"/>
     </row>
     <row r="36" spans="1:8">
-      <c r="A36" s="57"/>
+      <c r="A36" s="56"/>
       <c r="B36" s="26" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C36" s="29" t="s">
-        <v>326</v>
-      </c>
-      <c r="D36" s="58"/>
+        <v>325</v>
+      </c>
+      <c r="D36" s="57"/>
     </row>
     <row r="37" spans="1:8">
-      <c r="A37" s="60" t="s">
-        <v>343</v>
+      <c r="A37" s="59" t="s">
+        <v>342</v>
       </c>
       <c r="B37" s="30" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C37" s="31" t="s">
-        <v>326</v>
-      </c>
-      <c r="D37" s="63" t="s">
-        <v>326</v>
+        <v>325</v>
+      </c>
+      <c r="D37" s="62" t="s">
+        <v>325</v>
       </c>
     </row>
     <row r="38" spans="1:8">
-      <c r="A38" s="61"/>
+      <c r="A38" s="60"/>
       <c r="B38" s="30"/>
       <c r="C38" s="31" t="s">
-        <v>326</v>
-      </c>
-      <c r="D38" s="63"/>
+        <v>325</v>
+      </c>
+      <c r="D38" s="62"/>
     </row>
     <row r="39" spans="1:8">
-      <c r="A39" s="61"/>
+      <c r="A39" s="60"/>
       <c r="B39" s="30"/>
       <c r="C39" s="31" t="s">
-        <v>326</v>
-      </c>
-      <c r="D39" s="63"/>
+        <v>325</v>
+      </c>
+      <c r="D39" s="62"/>
     </row>
     <row r="40" spans="1:8">
-      <c r="A40" s="61"/>
+      <c r="A40" s="60"/>
       <c r="B40" s="30"/>
       <c r="C40" s="31" t="s">
-        <v>326</v>
-      </c>
-      <c r="D40" s="63"/>
+        <v>325</v>
+      </c>
+      <c r="D40" s="62"/>
     </row>
     <row r="41" spans="1:8">
-      <c r="A41" s="61"/>
+      <c r="A41" s="60"/>
       <c r="B41" s="30"/>
       <c r="C41" s="31" t="s">
-        <v>326</v>
-      </c>
-      <c r="D41" s="63"/>
+        <v>325</v>
+      </c>
+      <c r="D41" s="62"/>
     </row>
     <row r="42" spans="1:8">
-      <c r="A42" s="62"/>
+      <c r="A42" s="61"/>
       <c r="B42" s="32" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C42" s="33" t="s">
-        <v>326</v>
-      </c>
-      <c r="D42" s="64"/>
+        <v>325</v>
+      </c>
+      <c r="D42" s="63"/>
     </row>
     <row r="43" spans="1:8">
-      <c r="A43" s="56" t="s">
+      <c r="A43" s="55" t="s">
+        <v>343</v>
+      </c>
+      <c r="B43" s="20" t="s">
         <v>344</v>
       </c>
-      <c r="B43" s="20" t="s">
+      <c r="C43" s="22" t="s">
+        <v>325</v>
+      </c>
+      <c r="D43" s="58">
+        <v>7630000</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8">
+      <c r="A44" s="52"/>
+      <c r="B44" s="30" t="s">
         <v>345</v>
-      </c>
-      <c r="C43" s="22" t="s">
-        <v>326</v>
-      </c>
-      <c r="D43" s="59">
-        <v>7630000</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8">
-      <c r="A44" s="53"/>
-      <c r="B44" s="30" t="s">
-        <v>346</v>
       </c>
       <c r="C44" s="21">
         <v>1600000</v>
       </c>
-      <c r="D44" s="55"/>
+      <c r="D44" s="54"/>
     </row>
     <row r="45" spans="1:8">
-      <c r="A45" s="53"/>
+      <c r="A45" s="52"/>
       <c r="B45" s="30" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C45" s="34">
         <v>5000000</v>
       </c>
-      <c r="D45" s="55"/>
+      <c r="D45" s="54"/>
     </row>
     <row r="46" spans="1:8">
-      <c r="A46" s="53"/>
+      <c r="A46" s="52"/>
       <c r="B46" s="20" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C46" s="21">
         <v>1000000</v>
       </c>
-      <c r="D46" s="55"/>
+      <c r="D46" s="54"/>
       <c r="F46" t="s">
+        <v>347</v>
+      </c>
+      <c r="H46" s="49" t="s">
         <v>348</v>
       </c>
-      <c r="H46" s="49" t="s">
-        <v>349</v>
-      </c>
     </row>
     <row r="47" spans="1:8">
-      <c r="A47" s="57"/>
+      <c r="A47" s="56"/>
       <c r="B47" s="26" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C47" s="27">
         <v>30000</v>
       </c>
-      <c r="D47" s="58"/>
+      <c r="D47" s="57"/>
       <c r="H47" s="49" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="48" spans="1:8">
       <c r="A48" s="35" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B48" s="26" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C48" s="27">
         <v>1000000</v>
@@ -6273,94 +6282,94 @@
         <v>1000000</v>
       </c>
       <c r="H48" s="49" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="49" spans="1:4">
       <c r="A49" s="35" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B49" s="26" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C49" s="37" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="D49" s="38" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="50" spans="1:4">
       <c r="A50" s="35" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B50" s="26" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C50" s="29" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="D50" s="38" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="51" spans="1:4">
       <c r="A51" s="35" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B51" s="26" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C51" s="29" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="D51" s="38" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="52" spans="1:4">
       <c r="A52" s="35" t="s">
+        <v>355</v>
+      </c>
+      <c r="B52" s="26" t="s">
+        <v>325</v>
+      </c>
+      <c r="C52" s="39" t="s">
+        <v>325</v>
+      </c>
+      <c r="D52" s="38" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4">
+      <c r="A53" s="50" t="s">
+        <v>325</v>
+      </c>
+      <c r="B53" s="64"/>
+      <c r="C53" s="64"/>
+      <c r="D53" s="65"/>
+    </row>
+    <row r="54" spans="1:4">
+      <c r="A54" s="50" t="s">
+        <v>325</v>
+      </c>
+      <c r="B54" s="40" t="s">
         <v>356</v>
       </c>
-      <c r="B52" s="26" t="s">
-        <v>326</v>
-      </c>
-      <c r="C52" s="39" t="s">
-        <v>326</v>
-      </c>
-      <c r="D52" s="38" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4">
-      <c r="A53" s="51" t="s">
-        <v>326</v>
-      </c>
-      <c r="B53" s="65"/>
-      <c r="C53" s="65"/>
-      <c r="D53" s="66"/>
-    </row>
-    <row r="54" spans="1:4">
-      <c r="A54" s="51" t="s">
-        <v>326</v>
-      </c>
-      <c r="B54" s="40" t="s">
+      <c r="C54" s="18" t="s">
         <v>357</v>
-      </c>
-      <c r="C54" s="18" t="s">
-        <v>358</v>
       </c>
       <c r="D54" s="41">
         <v>38870000</v>
       </c>
     </row>
     <row r="55" spans="1:4">
-      <c r="A55" s="52"/>
+      <c r="A55" s="51"/>
       <c r="B55" s="42" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C55" s="43" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="D55" s="44">
         <v>38870000</v>
@@ -6392,6 +6401,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="문서" ma:contentTypeID="0x01010001DD19DE52280940B3AAA5F241D6761B" ma:contentTypeVersion="4" ma:contentTypeDescription="새 문서를 만듭니다." ma:contentTypeScope="" ma:versionID="e9eb13fb4618761134bcbf92bbe04a85">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="68c09c20-cf94-447c-8c86-a27e8b975351" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="39da59c9f0b9e3f02c0d4affa15a324d" ns2:_="">
     <xsd:import namespace="68c09c20-cf94-447c-8c86-a27e8b975351"/>
@@ -6535,12 +6550,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -6551,6 +6560,22 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0ECA5C0A-123A-482D-9740-A5FEEB670C26}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="68c09c20-cf94-447c-8c86-a27e8b975351"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{96212AED-2B2E-4A37-B17B-B5E79697714B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -6568,22 +6593,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0ECA5C0A-123A-482D-9740-A5FEEB670C26}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="68c09c20-cf94-447c-8c86-a27e8b975351"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{21529231-6B89-4ED0-BD3A-09A6E1C3C7BC}">
   <ds:schemaRefs>

--- a/Assets/StreamingAssets/DataTable.xlsx
+++ b/Assets/StreamingAssets/DataTable.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SWProject\My project\Assets\StreamingAssets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F7902180-9301-47E2-A36A-ED01B8E6CE85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB2AAA6A-47EA-4A30-8F50-DE4BFB7952AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="845" uniqueCount="396">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="845" uniqueCount="397">
   <si>
     <t>개요</t>
   </si>
@@ -521,9 +521,6 @@
     <t>SV302_Status</t>
   </si>
   <si>
-    <t>SV303</t>
-  </si>
-  <si>
     <t>SV102 밸브 상태</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1285,6 +1282,14 @@
   </si>
   <si>
     <t>Set RPM</t>
+  </si>
+  <si>
+    <t>SV301</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SV302</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1884,6 +1889,44 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1932,44 +1975,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="2" xr:uid="{00000000-000B-0000-0000-000008000000}"/>
@@ -1987,10 +1992,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2323,468 +2324,468 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="64" t="s">
-        <v>223</v>
-      </c>
-      <c r="B1" s="64" t="s">
+      <c r="A1" s="48" t="s">
+        <v>222</v>
+      </c>
+      <c r="B1" s="48" t="s">
         <v>11</v>
       </c>
-      <c r="C1" s="64" t="s">
+      <c r="C1" s="48" t="s">
+        <v>357</v>
+      </c>
+      <c r="D1" s="48" t="s">
+        <v>359</v>
+      </c>
+      <c r="E1" s="48" t="s">
+        <v>362</v>
+      </c>
+      <c r="F1" s="48" t="s">
+        <v>360</v>
+      </c>
+      <c r="G1" s="48" t="s">
         <v>358</v>
       </c>
-      <c r="D1" s="64" t="s">
-        <v>360</v>
-      </c>
-      <c r="E1" s="64" t="s">
-        <v>363</v>
-      </c>
-      <c r="F1" s="64" t="s">
+      <c r="H1" s="48" t="s">
         <v>361</v>
       </c>
-      <c r="G1" s="64" t="s">
-        <v>359</v>
-      </c>
-      <c r="H1" s="64" t="s">
-        <v>362</v>
-      </c>
-      <c r="I1" s="62" t="s">
+      <c r="I1" s="46" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="68">
+      <c r="A2" s="49">
         <v>1</v>
       </c>
       <c r="B2" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="C2" s="64"/>
-      <c r="D2" s="64"/>
-      <c r="E2" s="64" t="s">
+      <c r="C2" s="48"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="48" t="s">
         <v>36</v>
       </c>
-      <c r="F2" s="64"/>
-      <c r="G2" s="64"/>
-      <c r="H2" s="64"/>
-      <c r="I2" s="62"/>
+      <c r="F2" s="48"/>
+      <c r="G2" s="48"/>
+      <c r="H2" s="48"/>
+      <c r="I2" s="46"/>
     </row>
     <row r="3" spans="1:9">
-      <c r="A3" s="68">
+      <c r="A3" s="49">
         <v>2</v>
       </c>
       <c r="B3" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="C3" s="64"/>
-      <c r="D3" s="64"/>
-      <c r="E3" s="64" t="s">
-        <v>364</v>
-      </c>
-      <c r="F3" s="64"/>
-      <c r="G3" s="64"/>
-      <c r="H3" s="64"/>
-      <c r="I3" s="62"/>
+      <c r="C3" s="48"/>
+      <c r="D3" s="48"/>
+      <c r="E3" s="48" t="s">
+        <v>363</v>
+      </c>
+      <c r="F3" s="48"/>
+      <c r="G3" s="48"/>
+      <c r="H3" s="48"/>
+      <c r="I3" s="46"/>
     </row>
     <row r="4" spans="1:9">
-      <c r="A4" s="68">
+      <c r="A4" s="49">
         <v>3</v>
       </c>
       <c r="B4" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="C4" s="64"/>
-      <c r="D4" s="64"/>
-      <c r="E4" s="64" t="s">
-        <v>365</v>
-      </c>
-      <c r="F4" s="64"/>
-      <c r="G4" s="64"/>
-      <c r="H4" s="64"/>
-      <c r="I4" s="62"/>
+      <c r="C4" s="48"/>
+      <c r="D4" s="48"/>
+      <c r="E4" s="48" t="s">
+        <v>364</v>
+      </c>
+      <c r="F4" s="48"/>
+      <c r="G4" s="48"/>
+      <c r="H4" s="48"/>
+      <c r="I4" s="46"/>
     </row>
     <row r="5" spans="1:9">
-      <c r="A5" s="68">
+      <c r="A5" s="49">
         <v>4</v>
       </c>
       <c r="B5" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="C5" s="64"/>
-      <c r="D5" s="64"/>
-      <c r="E5" s="64" t="s">
+      <c r="C5" s="48"/>
+      <c r="D5" s="48"/>
+      <c r="E5" s="48" t="s">
         <v>42</v>
       </c>
-      <c r="F5" s="64"/>
-      <c r="G5" s="64"/>
-      <c r="H5" s="64"/>
-      <c r="I5" s="62"/>
+      <c r="F5" s="48"/>
+      <c r="G5" s="48"/>
+      <c r="H5" s="48"/>
+      <c r="I5" s="46"/>
     </row>
     <row r="6" spans="1:9">
-      <c r="A6" s="68">
+      <c r="A6" s="49">
         <v>5</v>
       </c>
       <c r="B6" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="C6" s="64"/>
-      <c r="D6" s="64"/>
-      <c r="E6" s="64" t="s">
-        <v>366</v>
-      </c>
-      <c r="F6" s="64"/>
-      <c r="G6" s="64"/>
-      <c r="H6" s="64"/>
-      <c r="I6" s="62"/>
+      <c r="C6" s="48"/>
+      <c r="D6" s="48"/>
+      <c r="E6" s="48" t="s">
+        <v>365</v>
+      </c>
+      <c r="F6" s="48"/>
+      <c r="G6" s="48"/>
+      <c r="H6" s="48"/>
+      <c r="I6" s="46"/>
     </row>
     <row r="7" spans="1:9">
-      <c r="A7" s="68">
+      <c r="A7" s="49">
         <v>6</v>
       </c>
       <c r="B7" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="C7" s="64"/>
-      <c r="D7" s="64"/>
-      <c r="E7" s="64" t="s">
+      <c r="C7" s="48"/>
+      <c r="D7" s="48"/>
+      <c r="E7" s="48" t="s">
         <v>47</v>
       </c>
-      <c r="F7" s="64"/>
-      <c r="G7" s="64"/>
-      <c r="H7" s="64"/>
-      <c r="I7" s="62"/>
+      <c r="F7" s="48"/>
+      <c r="G7" s="48"/>
+      <c r="H7" s="48"/>
+      <c r="I7" s="46"/>
     </row>
     <row r="8" spans="1:9">
-      <c r="A8" s="68">
+      <c r="A8" s="49">
         <v>7</v>
       </c>
       <c r="B8" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="C8" s="64"/>
-      <c r="D8" s="64"/>
-      <c r="E8" s="64" t="s">
+      <c r="C8" s="48"/>
+      <c r="D8" s="48"/>
+      <c r="E8" s="48" t="s">
         <v>50</v>
       </c>
-      <c r="F8" s="64"/>
-      <c r="G8" s="64"/>
-      <c r="H8" s="64"/>
-      <c r="I8" s="62"/>
+      <c r="F8" s="48"/>
+      <c r="G8" s="48"/>
+      <c r="H8" s="48"/>
+      <c r="I8" s="46"/>
     </row>
     <row r="9" spans="1:9">
-      <c r="A9" s="68">
+      <c r="A9" s="49">
         <v>8</v>
       </c>
       <c r="B9" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="C9" s="64"/>
-      <c r="D9" s="64"/>
-      <c r="E9" s="64" t="s">
+      <c r="C9" s="48"/>
+      <c r="D9" s="48"/>
+      <c r="E9" s="48" t="s">
         <v>53</v>
       </c>
-      <c r="F9" s="64"/>
-      <c r="G9" s="64"/>
-      <c r="H9" s="64"/>
-      <c r="I9" s="62"/>
+      <c r="F9" s="48"/>
+      <c r="G9" s="48"/>
+      <c r="H9" s="48"/>
+      <c r="I9" s="46"/>
     </row>
     <row r="10" spans="1:9">
-      <c r="A10" s="68">
+      <c r="A10" s="49">
         <v>9</v>
       </c>
       <c r="B10" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="C10" s="64"/>
-      <c r="D10" s="64"/>
-      <c r="E10" s="64" t="s">
+      <c r="C10" s="48"/>
+      <c r="D10" s="48"/>
+      <c r="E10" s="48" t="s">
         <v>56</v>
       </c>
-      <c r="F10" s="64"/>
-      <c r="G10" s="64"/>
-      <c r="H10" s="64"/>
-      <c r="I10" s="62"/>
+      <c r="F10" s="48"/>
+      <c r="G10" s="48"/>
+      <c r="H10" s="48"/>
+      <c r="I10" s="46"/>
     </row>
     <row r="11" spans="1:9">
-      <c r="A11" s="71">
+      <c r="A11" s="53">
         <v>10</v>
       </c>
-      <c r="B11" s="72" t="s">
+      <c r="B11" s="54" t="s">
         <v>57</v>
       </c>
-      <c r="C11" s="73"/>
-      <c r="D11" s="73"/>
-      <c r="E11" s="73" t="s">
-        <v>368</v>
-      </c>
-      <c r="F11" s="64" t="s">
-        <v>372</v>
-      </c>
-      <c r="G11" s="64" t="s">
+      <c r="C11" s="52"/>
+      <c r="D11" s="52"/>
+      <c r="E11" s="52" t="s">
+        <v>367</v>
+      </c>
+      <c r="F11" s="48" t="s">
+        <v>371</v>
+      </c>
+      <c r="G11" s="48" t="s">
+        <v>377</v>
+      </c>
+      <c r="H11" s="48" t="s">
+        <v>58</v>
+      </c>
+      <c r="I11" s="46"/>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="A12" s="53"/>
+      <c r="B12" s="54"/>
+      <c r="C12" s="52"/>
+      <c r="D12" s="52"/>
+      <c r="E12" s="52"/>
+      <c r="F12" s="48" t="s">
+        <v>371</v>
+      </c>
+      <c r="G12" s="48" t="s">
+        <v>379</v>
+      </c>
+      <c r="H12" s="48" t="s">
+        <v>376</v>
+      </c>
+      <c r="I12" s="46"/>
+    </row>
+    <row r="13" spans="1:9">
+      <c r="A13" s="53">
+        <v>11</v>
+      </c>
+      <c r="B13" s="54" t="s">
+        <v>61</v>
+      </c>
+      <c r="C13" s="52"/>
+      <c r="D13" s="52"/>
+      <c r="E13" s="52" t="s">
+        <v>366</v>
+      </c>
+      <c r="F13" s="48" t="s">
+        <v>371</v>
+      </c>
+      <c r="G13" s="48" t="s">
+        <v>377</v>
+      </c>
+      <c r="H13" s="48" t="s">
+        <v>58</v>
+      </c>
+      <c r="I13" s="46"/>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="A14" s="53"/>
+      <c r="B14" s="54"/>
+      <c r="C14" s="52"/>
+      <c r="D14" s="52"/>
+      <c r="E14" s="52"/>
+      <c r="F14" s="48" t="s">
+        <v>371</v>
+      </c>
+      <c r="G14" s="48" t="s">
         <v>378</v>
       </c>
-      <c r="H11" s="64" t="s">
-        <v>58</v>
-      </c>
-      <c r="I11" s="62"/>
-    </row>
-    <row r="12" spans="1:9">
-      <c r="A12" s="71"/>
-      <c r="B12" s="72"/>
-      <c r="C12" s="73"/>
-      <c r="D12" s="73"/>
-      <c r="E12" s="73"/>
-      <c r="F12" s="64" t="s">
-        <v>372</v>
-      </c>
-      <c r="G12" s="64" t="s">
-        <v>380</v>
-      </c>
-      <c r="H12" s="64" t="s">
-        <v>377</v>
-      </c>
-      <c r="I12" s="62"/>
-    </row>
-    <row r="13" spans="1:9">
-      <c r="A13" s="71">
-        <v>11</v>
-      </c>
-      <c r="B13" s="72" t="s">
-        <v>61</v>
-      </c>
-      <c r="C13" s="73"/>
-      <c r="D13" s="73"/>
-      <c r="E13" s="73" t="s">
-        <v>367</v>
-      </c>
-      <c r="F13" s="64" t="s">
-        <v>372</v>
-      </c>
-      <c r="G13" s="64" t="s">
-        <v>378</v>
-      </c>
-      <c r="H13" s="64" t="s">
-        <v>58</v>
-      </c>
-      <c r="I13" s="62"/>
-    </row>
-    <row r="14" spans="1:9">
-      <c r="A14" s="71"/>
-      <c r="B14" s="72"/>
-      <c r="C14" s="73"/>
-      <c r="D14" s="73"/>
-      <c r="E14" s="73"/>
-      <c r="F14" s="64" t="s">
-        <v>372</v>
-      </c>
-      <c r="G14" s="64" t="s">
-        <v>379</v>
-      </c>
-      <c r="H14" s="64" t="s">
-        <v>377</v>
-      </c>
-      <c r="I14" s="62"/>
+      <c r="H14" s="48" t="s">
+        <v>376</v>
+      </c>
+      <c r="I14" s="46"/>
     </row>
     <row r="15" spans="1:9">
-      <c r="A15" s="68">
+      <c r="A15" s="49">
         <v>12</v>
       </c>
       <c r="B15" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="C15" s="64"/>
-      <c r="D15" s="64"/>
-      <c r="E15" s="64" t="s">
+      <c r="C15" s="48"/>
+      <c r="D15" s="48"/>
+      <c r="E15" s="48" t="s">
         <v>65</v>
       </c>
-      <c r="F15" s="64"/>
-      <c r="G15" s="64"/>
-      <c r="H15" s="64"/>
-      <c r="I15" s="62"/>
+      <c r="F15" s="48"/>
+      <c r="G15" s="48"/>
+      <c r="H15" s="48"/>
+      <c r="I15" s="46"/>
     </row>
     <row r="16" spans="1:9">
-      <c r="A16" s="71">
+      <c r="A16" s="53">
         <v>13</v>
       </c>
-      <c r="B16" s="73" t="s">
+      <c r="B16" s="52" t="s">
         <v>71</v>
       </c>
-      <c r="C16" s="73"/>
-      <c r="D16" s="73"/>
-      <c r="E16" s="73" t="s">
+      <c r="C16" s="52"/>
+      <c r="D16" s="52"/>
+      <c r="E16" s="52" t="s">
+        <v>368</v>
+      </c>
+      <c r="F16" s="52" t="s">
+        <v>373</v>
+      </c>
+      <c r="G16" s="52" t="s">
+        <v>370</v>
+      </c>
+      <c r="H16" s="48" t="s">
+        <v>374</v>
+      </c>
+      <c r="I16" s="55" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
+      <c r="A17" s="53"/>
+      <c r="B17" s="52"/>
+      <c r="C17" s="52"/>
+      <c r="D17" s="52"/>
+      <c r="E17" s="52"/>
+      <c r="F17" s="52"/>
+      <c r="G17" s="52"/>
+      <c r="H17" s="48" t="s">
+        <v>375</v>
+      </c>
+      <c r="I17" s="56"/>
+    </row>
+    <row r="18" spans="1:9">
+      <c r="A18" s="53"/>
+      <c r="B18" s="52"/>
+      <c r="C18" s="52"/>
+      <c r="D18" s="52"/>
+      <c r="E18" s="52"/>
+      <c r="F18" s="52"/>
+      <c r="G18" s="52"/>
+      <c r="H18" s="48" t="s">
+        <v>376</v>
+      </c>
+      <c r="I18" s="56"/>
+    </row>
+    <row r="19" spans="1:9">
+      <c r="A19" s="53"/>
+      <c r="B19" s="52"/>
+      <c r="C19" s="52"/>
+      <c r="D19" s="52"/>
+      <c r="E19" s="52"/>
+      <c r="F19" s="52"/>
+      <c r="G19" s="52"/>
+      <c r="H19" s="48" t="s">
+        <v>58</v>
+      </c>
+      <c r="I19" s="56"/>
+    </row>
+    <row r="20" spans="1:9">
+      <c r="A20" s="53"/>
+      <c r="B20" s="52"/>
+      <c r="C20" s="52"/>
+      <c r="D20" s="52"/>
+      <c r="E20" s="52"/>
+      <c r="F20" s="52"/>
+      <c r="G20" s="52"/>
+      <c r="H20" s="48"/>
+      <c r="I20" s="46"/>
+    </row>
+    <row r="21" spans="1:9">
+      <c r="A21" s="53"/>
+      <c r="B21" s="52"/>
+      <c r="C21" s="52"/>
+      <c r="D21" s="52"/>
+      <c r="E21" s="52"/>
+      <c r="F21" s="52"/>
+      <c r="G21" s="52"/>
+      <c r="H21" s="48"/>
+      <c r="I21" s="46"/>
+    </row>
+    <row r="22" spans="1:9">
+      <c r="A22" s="49">
+        <v>15</v>
+      </c>
+      <c r="B22" s="48" t="s">
+        <v>163</v>
+      </c>
+      <c r="C22" s="48"/>
+      <c r="D22" s="48"/>
+      <c r="E22" s="48" t="s">
         <v>369</v>
       </c>
-      <c r="F16" s="73" t="s">
-        <v>374</v>
-      </c>
-      <c r="G16" s="73" t="s">
+      <c r="F22" s="48" t="s">
         <v>371</v>
       </c>
-      <c r="H16" s="64" t="s">
-        <v>375</v>
-      </c>
-      <c r="I16" s="74" t="s">
+      <c r="G22" s="48" t="s">
+        <v>372</v>
+      </c>
+      <c r="H22" s="48"/>
+      <c r="I22" s="46"/>
+    </row>
+    <row r="23" spans="1:9">
+      <c r="A23" s="49">
+        <v>16</v>
+      </c>
+      <c r="B23" s="48" t="s">
+        <v>146</v>
+      </c>
+      <c r="C23" s="48"/>
+      <c r="D23" s="48"/>
+      <c r="E23" s="48" t="s">
+        <v>369</v>
+      </c>
+      <c r="F23" s="48" t="s">
+        <v>371</v>
+      </c>
+      <c r="G23" s="48" t="s">
+        <v>372</v>
+      </c>
+      <c r="H23" s="48"/>
+      <c r="I23" s="46"/>
+    </row>
+    <row r="24" spans="1:9">
+      <c r="A24" s="49">
+        <v>17</v>
+      </c>
+      <c r="B24" s="48" t="s">
+        <v>152</v>
+      </c>
+      <c r="C24" s="48"/>
+      <c r="D24" s="48"/>
+      <c r="E24" s="48" t="s">
         <v>383</v>
       </c>
-    </row>
-    <row r="17" spans="1:9">
-      <c r="A17" s="71"/>
-      <c r="B17" s="73"/>
-      <c r="C17" s="73"/>
-      <c r="D17" s="73"/>
-      <c r="E17" s="73"/>
-      <c r="F17" s="73"/>
-      <c r="G17" s="73"/>
-      <c r="H17" s="64" t="s">
-        <v>376</v>
-      </c>
-      <c r="I17" s="67"/>
-    </row>
-    <row r="18" spans="1:9">
-      <c r="A18" s="71"/>
-      <c r="B18" s="73"/>
-      <c r="C18" s="73"/>
-      <c r="D18" s="73"/>
-      <c r="E18" s="73"/>
-      <c r="F18" s="73"/>
-      <c r="G18" s="73"/>
-      <c r="H18" s="64" t="s">
-        <v>377</v>
-      </c>
-      <c r="I18" s="67"/>
-    </row>
-    <row r="19" spans="1:9">
-      <c r="A19" s="71"/>
-      <c r="B19" s="73"/>
-      <c r="C19" s="73"/>
-      <c r="D19" s="73"/>
-      <c r="E19" s="73"/>
-      <c r="F19" s="73"/>
-      <c r="G19" s="73"/>
-      <c r="H19" s="64" t="s">
-        <v>58</v>
-      </c>
-      <c r="I19" s="67"/>
-    </row>
-    <row r="20" spans="1:9">
-      <c r="A20" s="71"/>
-      <c r="B20" s="73"/>
-      <c r="C20" s="73"/>
-      <c r="D20" s="73"/>
-      <c r="E20" s="73"/>
-      <c r="F20" s="73"/>
-      <c r="G20" s="73"/>
-      <c r="H20" s="64"/>
-      <c r="I20" s="62"/>
-    </row>
-    <row r="21" spans="1:9">
-      <c r="A21" s="71"/>
-      <c r="B21" s="73"/>
-      <c r="C21" s="73"/>
-      <c r="D21" s="73"/>
-      <c r="E21" s="73"/>
-      <c r="F21" s="73"/>
-      <c r="G21" s="73"/>
-      <c r="H21" s="64"/>
-      <c r="I21" s="62"/>
-    </row>
-    <row r="22" spans="1:9">
-      <c r="A22" s="68">
-        <v>15</v>
-      </c>
-      <c r="B22" s="64" t="s">
-        <v>164</v>
-      </c>
-      <c r="C22" s="64"/>
-      <c r="D22" s="64"/>
-      <c r="E22" s="64" t="s">
-        <v>370</v>
-      </c>
-      <c r="F22" s="64" t="s">
+      <c r="F24" s="48" t="s">
+        <v>371</v>
+      </c>
+      <c r="G24" s="48" t="s">
         <v>372</v>
       </c>
-      <c r="G22" s="64" t="s">
-        <v>373</v>
-      </c>
-      <c r="H22" s="64"/>
-      <c r="I22" s="62"/>
-    </row>
-    <row r="23" spans="1:9">
-      <c r="A23" s="68">
-        <v>16</v>
-      </c>
-      <c r="B23" s="64" t="s">
-        <v>146</v>
-      </c>
-      <c r="C23" s="64"/>
-      <c r="D23" s="64"/>
-      <c r="E23" s="64" t="s">
-        <v>370</v>
-      </c>
-      <c r="F23" s="64" t="s">
-        <v>372</v>
-      </c>
-      <c r="G23" s="64" t="s">
-        <v>373</v>
-      </c>
-      <c r="H23" s="64"/>
-      <c r="I23" s="62"/>
-    </row>
-    <row r="24" spans="1:9">
-      <c r="A24" s="68">
-        <v>17</v>
-      </c>
-      <c r="B24" s="64" t="s">
-        <v>153</v>
-      </c>
-      <c r="C24" s="64"/>
-      <c r="D24" s="64"/>
-      <c r="E24" s="64" t="s">
+      <c r="H24" s="48"/>
+      <c r="I24" s="46"/>
+    </row>
+    <row r="25" spans="1:9" s="1" customFormat="1">
+      <c r="A25" s="56">
+        <v>18</v>
+      </c>
+      <c r="B25" s="56" t="s">
+        <v>135</v>
+      </c>
+      <c r="C25" s="57"/>
+      <c r="D25" s="57"/>
+      <c r="E25" s="55" t="s">
+        <v>385</v>
+      </c>
+      <c r="F25" s="57"/>
+      <c r="G25" s="56" t="s">
         <v>384</v>
       </c>
-      <c r="F24" s="64" t="s">
-        <v>372</v>
-      </c>
-      <c r="G24" s="64" t="s">
-        <v>373</v>
-      </c>
-      <c r="H24" s="64"/>
-      <c r="I24" s="62"/>
-    </row>
-    <row r="25" spans="1:9" s="1" customFormat="1">
-      <c r="A25" s="67">
-        <v>18</v>
-      </c>
-      <c r="B25" s="67" t="s">
-        <v>135</v>
-      </c>
-      <c r="C25" s="65"/>
-      <c r="D25" s="65"/>
-      <c r="E25" s="74" t="s">
+      <c r="H25" s="48" t="s">
         <v>386</v>
       </c>
-      <c r="F25" s="65"/>
-      <c r="G25" s="67" t="s">
-        <v>385</v>
-      </c>
-      <c r="H25" s="64" t="s">
+      <c r="I25" s="59" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" s="1" customFormat="1">
+      <c r="A26" s="56"/>
+      <c r="B26" s="56"/>
+      <c r="C26" s="58"/>
+      <c r="D26" s="58"/>
+      <c r="E26" s="55"/>
+      <c r="F26" s="58"/>
+      <c r="G26" s="56"/>
+      <c r="H26" s="48" t="s">
         <v>387</v>
       </c>
-      <c r="I25" s="75" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" s="1" customFormat="1">
-      <c r="A26" s="67"/>
-      <c r="B26" s="67"/>
-      <c r="C26" s="66"/>
-      <c r="D26" s="66"/>
-      <c r="E26" s="74"/>
-      <c r="F26" s="66"/>
-      <c r="G26" s="67"/>
-      <c r="H26" s="64" t="s">
-        <v>388</v>
-      </c>
-      <c r="I26" s="66"/>
+      <c r="I26" s="58"/>
     </row>
   </sheetData>
   <mergeCells count="33">
@@ -2797,6 +2798,13 @@
     <mergeCell ref="D25:D26"/>
     <mergeCell ref="C25:C26"/>
     <mergeCell ref="I25:I26"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="G16:G19"/>
+    <mergeCell ref="F16:F19"/>
+    <mergeCell ref="E16:E19"/>
+    <mergeCell ref="B16:B19"/>
+    <mergeCell ref="A16:A19"/>
+    <mergeCell ref="D16:D19"/>
     <mergeCell ref="E13:E14"/>
     <mergeCell ref="B13:B14"/>
     <mergeCell ref="A13:A14"/>
@@ -2807,20 +2815,13 @@
     <mergeCell ref="B11:B12"/>
     <mergeCell ref="C11:C12"/>
     <mergeCell ref="D11:D12"/>
-    <mergeCell ref="A20:A21"/>
-    <mergeCell ref="G16:G19"/>
-    <mergeCell ref="F16:F19"/>
-    <mergeCell ref="E16:E19"/>
-    <mergeCell ref="B16:B19"/>
-    <mergeCell ref="A16:A19"/>
-    <mergeCell ref="D16:D19"/>
+    <mergeCell ref="B20:B21"/>
     <mergeCell ref="C16:C19"/>
     <mergeCell ref="G20:G21"/>
     <mergeCell ref="F20:F21"/>
     <mergeCell ref="E20:E21"/>
     <mergeCell ref="D20:D21"/>
     <mergeCell ref="C20:C21"/>
-    <mergeCell ref="B20:B21"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2854,2658 +2855,2658 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18">
-      <c r="A1" s="69" t="s">
+      <c r="A1" s="50" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="69" t="s">
+      <c r="B1" s="50" t="s">
         <v>11</v>
       </c>
-      <c r="C1" s="69" t="s">
+      <c r="C1" s="50" t="s">
         <v>12</v>
       </c>
-      <c r="D1" s="69" t="s">
+      <c r="D1" s="50" t="s">
         <v>13</v>
       </c>
-      <c r="E1" s="69" t="s">
+      <c r="E1" s="50" t="s">
         <v>14</v>
       </c>
-      <c r="F1" s="69" t="s">
+      <c r="F1" s="50" t="s">
         <v>15</v>
       </c>
-      <c r="G1" s="69" t="s">
+      <c r="G1" s="50" t="s">
         <v>16</v>
       </c>
-      <c r="H1" s="69" t="s">
+      <c r="H1" s="50" t="s">
         <v>17</v>
       </c>
-      <c r="I1" s="69" t="s">
+      <c r="I1" s="50" t="s">
         <v>18</v>
       </c>
-      <c r="J1" s="69" t="s">
+      <c r="J1" s="50" t="s">
         <v>19</v>
       </c>
-      <c r="K1" s="69" t="s">
+      <c r="K1" s="50" t="s">
         <v>20</v>
       </c>
-      <c r="L1" s="69" t="s">
+      <c r="L1" s="50" t="s">
         <v>21</v>
       </c>
-      <c r="M1" s="69" t="s">
+      <c r="M1" s="50" t="s">
         <v>22</v>
       </c>
-      <c r="N1" s="69" t="s">
+      <c r="N1" s="50" t="s">
         <v>23</v>
       </c>
-      <c r="O1" s="69" t="s">
+      <c r="O1" s="50" t="s">
         <v>24</v>
       </c>
-      <c r="P1" s="69" t="s">
+      <c r="P1" s="50" t="s">
         <v>25</v>
       </c>
-      <c r="Q1" s="69" t="s">
+      <c r="Q1" s="50" t="s">
         <v>26</v>
       </c>
-      <c r="R1" s="69" t="s">
+      <c r="R1" s="50" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:18">
-      <c r="A2" s="64">
-        <v>1</v>
-      </c>
-      <c r="B2" s="64" t="s">
+      <c r="A2" s="48">
+        <v>1</v>
+      </c>
+      <c r="B2" s="48" t="s">
         <v>28</v>
       </c>
-      <c r="C2" s="64" t="s">
+      <c r="C2" s="48" t="s">
         <v>29</v>
       </c>
-      <c r="D2" s="64" t="s">
+      <c r="D2" s="48" t="s">
         <v>30</v>
       </c>
-      <c r="E2" s="64" t="s">
+      <c r="E2" s="48" t="s">
         <v>31</v>
       </c>
-      <c r="F2" s="64" t="s">
+      <c r="F2" s="48" t="s">
         <v>32</v>
       </c>
-      <c r="G2" s="64" t="s">
+      <c r="G2" s="48" t="s">
         <v>33</v>
       </c>
-      <c r="H2" s="64" t="s">
+      <c r="H2" s="48" t="s">
         <v>28</v>
       </c>
-      <c r="I2" s="64" t="s">
+      <c r="I2" s="48" t="s">
         <v>34</v>
       </c>
-      <c r="J2" s="64" t="s">
+      <c r="J2" s="48" t="s">
         <v>35</v>
       </c>
-      <c r="K2" s="64">
-        <v>0</v>
-      </c>
-      <c r="L2" s="64">
+      <c r="K2" s="48">
+        <v>0</v>
+      </c>
+      <c r="L2" s="48">
         <v>100</v>
       </c>
-      <c r="M2" s="64">
-        <v>0</v>
-      </c>
-      <c r="N2" s="64">
+      <c r="M2" s="48">
+        <v>0</v>
+      </c>
+      <c r="N2" s="48">
         <v>16000</v>
       </c>
-      <c r="O2" s="64">
-        <v>0</v>
-      </c>
-      <c r="P2" s="64" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q2" s="64" t="s">
+      <c r="O2" s="48">
+        <v>0</v>
+      </c>
+      <c r="P2" s="48" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q2" s="48" t="s">
         <v>36</v>
       </c>
-      <c r="R2" s="64"/>
+      <c r="R2" s="48"/>
     </row>
     <row r="3" spans="1:18">
-      <c r="A3" s="64">
+      <c r="A3" s="48">
         <v>2</v>
       </c>
-      <c r="B3" s="64" t="s">
+      <c r="B3" s="48" t="s">
         <v>37</v>
       </c>
-      <c r="C3" s="64" t="s">
+      <c r="C3" s="48" t="s">
         <v>29</v>
       </c>
-      <c r="D3" s="64" t="s">
+      <c r="D3" s="48" t="s">
         <v>30</v>
       </c>
-      <c r="E3" s="64" t="s">
+      <c r="E3" s="48" t="s">
         <v>31</v>
       </c>
-      <c r="F3" s="64" t="s">
+      <c r="F3" s="48" t="s">
         <v>32</v>
       </c>
-      <c r="G3" s="64" t="s">
+      <c r="G3" s="48" t="s">
         <v>33</v>
       </c>
-      <c r="H3" s="64" t="s">
+      <c r="H3" s="48" t="s">
         <v>37</v>
       </c>
-      <c r="I3" s="64" t="s">
+      <c r="I3" s="48" t="s">
         <v>34</v>
       </c>
-      <c r="J3" s="64" t="s">
+      <c r="J3" s="48" t="s">
         <v>35</v>
       </c>
-      <c r="K3" s="64">
-        <v>0</v>
-      </c>
-      <c r="L3" s="64">
+      <c r="K3" s="48">
+        <v>0</v>
+      </c>
+      <c r="L3" s="48">
         <v>100</v>
       </c>
-      <c r="M3" s="64">
-        <v>0</v>
-      </c>
-      <c r="N3" s="64">
+      <c r="M3" s="48">
+        <v>0</v>
+      </c>
+      <c r="N3" s="48">
         <v>16000</v>
       </c>
-      <c r="O3" s="64">
-        <v>1</v>
-      </c>
-      <c r="P3" s="64" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q3" s="64" t="s">
+      <c r="O3" s="48">
+        <v>1</v>
+      </c>
+      <c r="P3" s="48" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q3" s="48" t="s">
         <v>38</v>
       </c>
-      <c r="R3" s="64"/>
+      <c r="R3" s="48"/>
     </row>
     <row r="4" spans="1:18">
-      <c r="A4" s="64">
+      <c r="A4" s="48">
         <v>3</v>
       </c>
-      <c r="B4" s="64" t="s">
+      <c r="B4" s="48" t="s">
         <v>39</v>
       </c>
-      <c r="C4" s="64" t="s">
+      <c r="C4" s="48" t="s">
         <v>29</v>
       </c>
-      <c r="D4" s="64" t="s">
+      <c r="D4" s="48" t="s">
         <v>30</v>
       </c>
-      <c r="E4" s="64" t="s">
+      <c r="E4" s="48" t="s">
         <v>31</v>
       </c>
-      <c r="F4" s="64" t="s">
+      <c r="F4" s="48" t="s">
         <v>32</v>
       </c>
-      <c r="G4" s="64" t="s">
+      <c r="G4" s="48" t="s">
         <v>33</v>
       </c>
-      <c r="H4" s="64" t="s">
+      <c r="H4" s="48" t="s">
         <v>39</v>
       </c>
-      <c r="I4" s="64" t="s">
+      <c r="I4" s="48" t="s">
         <v>34</v>
       </c>
-      <c r="J4" s="64" t="s">
+      <c r="J4" s="48" t="s">
         <v>35</v>
       </c>
-      <c r="K4" s="64">
-        <v>0</v>
-      </c>
-      <c r="L4" s="64">
+      <c r="K4" s="48">
+        <v>0</v>
+      </c>
+      <c r="L4" s="48">
         <v>100</v>
       </c>
-      <c r="M4" s="64">
-        <v>0</v>
-      </c>
-      <c r="N4" s="64">
+      <c r="M4" s="48">
+        <v>0</v>
+      </c>
+      <c r="N4" s="48">
         <v>16000</v>
       </c>
-      <c r="O4" s="64">
+      <c r="O4" s="48">
         <v>2</v>
       </c>
-      <c r="P4" s="64" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q4" s="64" t="s">
+      <c r="P4" s="48" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q4" s="48" t="s">
         <v>40</v>
       </c>
-      <c r="R4" s="64"/>
+      <c r="R4" s="48"/>
     </row>
     <row r="5" spans="1:18">
-      <c r="A5" s="64">
+      <c r="A5" s="48">
         <v>4</v>
       </c>
-      <c r="B5" s="64" t="s">
+      <c r="B5" s="48" t="s">
         <v>41</v>
       </c>
-      <c r="C5" s="64" t="s">
+      <c r="C5" s="48" t="s">
         <v>29</v>
       </c>
-      <c r="D5" s="64" t="s">
+      <c r="D5" s="48" t="s">
         <v>30</v>
       </c>
-      <c r="E5" s="64" t="s">
+      <c r="E5" s="48" t="s">
         <v>31</v>
       </c>
-      <c r="F5" s="64" t="s">
+      <c r="F5" s="48" t="s">
         <v>32</v>
       </c>
-      <c r="G5" s="64" t="s">
+      <c r="G5" s="48" t="s">
         <v>33</v>
       </c>
-      <c r="H5" s="64" t="s">
+      <c r="H5" s="48" t="s">
         <v>41</v>
       </c>
-      <c r="I5" s="64" t="s">
+      <c r="I5" s="48" t="s">
         <v>34</v>
       </c>
-      <c r="J5" s="64" t="s">
+      <c r="J5" s="48" t="s">
         <v>35</v>
       </c>
-      <c r="K5" s="64">
-        <v>0</v>
-      </c>
-      <c r="L5" s="64">
+      <c r="K5" s="48">
+        <v>0</v>
+      </c>
+      <c r="L5" s="48">
         <v>100</v>
       </c>
-      <c r="M5" s="64">
-        <v>0</v>
-      </c>
-      <c r="N5" s="64">
+      <c r="M5" s="48">
+        <v>0</v>
+      </c>
+      <c r="N5" s="48">
         <v>16000</v>
       </c>
-      <c r="O5" s="64">
+      <c r="O5" s="48">
         <v>3</v>
       </c>
-      <c r="P5" s="64" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q5" s="64" t="s">
+      <c r="P5" s="48" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q5" s="48" t="s">
         <v>42</v>
       </c>
-      <c r="R5" s="64"/>
+      <c r="R5" s="48"/>
     </row>
     <row r="6" spans="1:18">
-      <c r="A6" s="64">
+      <c r="A6" s="48">
         <v>5</v>
       </c>
-      <c r="B6" s="64" t="s">
+      <c r="B6" s="48" t="s">
         <v>43</v>
       </c>
-      <c r="C6" s="64" t="s">
+      <c r="C6" s="48" t="s">
         <v>29</v>
       </c>
-      <c r="D6" s="64" t="s">
+      <c r="D6" s="48" t="s">
         <v>30</v>
       </c>
-      <c r="E6" s="64" t="s">
+      <c r="E6" s="48" t="s">
         <v>31</v>
       </c>
-      <c r="F6" s="64" t="s">
+      <c r="F6" s="48" t="s">
         <v>44</v>
       </c>
-      <c r="G6" s="64" t="s">
+      <c r="G6" s="48" t="s">
         <v>33</v>
       </c>
-      <c r="H6" s="64" t="s">
+      <c r="H6" s="48" t="s">
         <v>43</v>
       </c>
-      <c r="I6" s="64" t="s">
+      <c r="I6" s="48" t="s">
         <v>34</v>
       </c>
-      <c r="J6" s="64" t="s">
+      <c r="J6" s="48" t="s">
         <v>35</v>
       </c>
-      <c r="K6" s="64">
-        <v>0</v>
-      </c>
-      <c r="L6" s="64">
+      <c r="K6" s="48">
+        <v>0</v>
+      </c>
+      <c r="L6" s="48">
         <v>100</v>
       </c>
-      <c r="M6" s="64">
-        <v>0</v>
-      </c>
-      <c r="N6" s="64">
+      <c r="M6" s="48">
+        <v>0</v>
+      </c>
+      <c r="N6" s="48">
         <v>16000</v>
       </c>
-      <c r="O6" s="64">
+      <c r="O6" s="48">
         <v>4</v>
       </c>
-      <c r="P6" s="64" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q6" s="64" t="s">
+      <c r="P6" s="48" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q6" s="48" t="s">
         <v>45</v>
       </c>
-      <c r="R6" s="64"/>
+      <c r="R6" s="48"/>
     </row>
     <row r="7" spans="1:18">
-      <c r="A7" s="64">
+      <c r="A7" s="48">
         <v>6</v>
       </c>
-      <c r="B7" s="64" t="s">
+      <c r="B7" s="48" t="s">
         <v>46</v>
       </c>
-      <c r="C7" s="64" t="s">
+      <c r="C7" s="48" t="s">
         <v>29</v>
       </c>
-      <c r="D7" s="64" t="s">
+      <c r="D7" s="48" t="s">
         <v>30</v>
       </c>
-      <c r="E7" s="64" t="s">
+      <c r="E7" s="48" t="s">
         <v>31</v>
       </c>
-      <c r="F7" s="64" t="s">
+      <c r="F7" s="48" t="s">
         <v>44</v>
       </c>
-      <c r="G7" s="64" t="s">
+      <c r="G7" s="48" t="s">
         <v>33</v>
       </c>
-      <c r="H7" s="64" t="s">
+      <c r="H7" s="48" t="s">
         <v>46</v>
       </c>
-      <c r="I7" s="64" t="s">
+      <c r="I7" s="48" t="s">
         <v>34</v>
       </c>
-      <c r="J7" s="64" t="s">
+      <c r="J7" s="48" t="s">
         <v>35</v>
       </c>
-      <c r="K7" s="64">
-        <v>0</v>
-      </c>
-      <c r="L7" s="64">
+      <c r="K7" s="48">
+        <v>0</v>
+      </c>
+      <c r="L7" s="48">
         <v>100</v>
       </c>
-      <c r="M7" s="64">
-        <v>0</v>
-      </c>
-      <c r="N7" s="64">
+      <c r="M7" s="48">
+        <v>0</v>
+      </c>
+      <c r="N7" s="48">
         <v>16000</v>
       </c>
-      <c r="O7" s="64">
+      <c r="O7" s="48">
         <v>5</v>
       </c>
-      <c r="P7" s="64" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q7" s="64" t="s">
+      <c r="P7" s="48" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="48" t="s">
         <v>47</v>
       </c>
-      <c r="R7" s="64"/>
+      <c r="R7" s="48"/>
     </row>
     <row r="8" spans="1:18">
-      <c r="A8" s="64">
+      <c r="A8" s="48">
         <v>7</v>
       </c>
-      <c r="B8" s="64" t="s">
+      <c r="B8" s="48" t="s">
         <v>48</v>
       </c>
-      <c r="C8" s="64" t="s">
+      <c r="C8" s="48" t="s">
         <v>29</v>
       </c>
-      <c r="D8" s="64" t="s">
+      <c r="D8" s="48" t="s">
         <v>30</v>
       </c>
-      <c r="E8" s="64" t="s">
+      <c r="E8" s="48" t="s">
         <v>31</v>
       </c>
-      <c r="F8" s="64" t="s">
+      <c r="F8" s="48" t="s">
         <v>44</v>
       </c>
-      <c r="G8" s="64" t="s">
+      <c r="G8" s="48" t="s">
         <v>33</v>
       </c>
-      <c r="H8" s="64" t="s">
+      <c r="H8" s="48" t="s">
         <v>48</v>
       </c>
-      <c r="I8" s="64" t="s">
+      <c r="I8" s="48" t="s">
         <v>49</v>
       </c>
-      <c r="J8" s="64" t="s">
+      <c r="J8" s="48" t="s">
         <v>35</v>
       </c>
-      <c r="K8" s="64">
-        <v>0</v>
-      </c>
-      <c r="L8" s="64">
+      <c r="K8" s="48">
+        <v>0</v>
+      </c>
+      <c r="L8" s="48">
         <v>100</v>
       </c>
-      <c r="M8" s="64">
-        <v>0</v>
-      </c>
-      <c r="N8" s="64">
+      <c r="M8" s="48">
+        <v>0</v>
+      </c>
+      <c r="N8" s="48">
         <v>16000</v>
       </c>
-      <c r="O8" s="64">
+      <c r="O8" s="48">
         <v>6</v>
       </c>
-      <c r="P8" s="64" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q8" s="64" t="s">
+      <c r="P8" s="48" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q8" s="48" t="s">
         <v>50</v>
       </c>
-      <c r="R8" s="64"/>
+      <c r="R8" s="48"/>
     </row>
     <row r="9" spans="1:18">
-      <c r="A9" s="64">
+      <c r="A9" s="48">
         <v>8</v>
       </c>
-      <c r="B9" s="64" t="s">
+      <c r="B9" s="48" t="s">
         <v>51</v>
       </c>
-      <c r="C9" s="64" t="s">
+      <c r="C9" s="48" t="s">
         <v>29</v>
       </c>
-      <c r="D9" s="64" t="s">
+      <c r="D9" s="48" t="s">
         <v>30</v>
       </c>
-      <c r="E9" s="64" t="s">
+      <c r="E9" s="48" t="s">
         <v>31</v>
       </c>
-      <c r="F9" s="64" t="s">
+      <c r="F9" s="48" t="s">
         <v>44</v>
       </c>
-      <c r="G9" s="64" t="s">
+      <c r="G9" s="48" t="s">
         <v>33</v>
       </c>
-      <c r="H9" s="64" t="s">
+      <c r="H9" s="48" t="s">
         <v>51</v>
       </c>
-      <c r="I9" s="64" t="s">
+      <c r="I9" s="48" t="s">
         <v>52</v>
       </c>
-      <c r="J9" s="64" t="s">
+      <c r="J9" s="48" t="s">
         <v>35</v>
       </c>
-      <c r="K9" s="64">
-        <v>0</v>
-      </c>
-      <c r="L9" s="64">
+      <c r="K9" s="48">
+        <v>0</v>
+      </c>
+      <c r="L9" s="48">
         <v>100</v>
       </c>
-      <c r="M9" s="64">
-        <v>0</v>
-      </c>
-      <c r="N9" s="64">
+      <c r="M9" s="48">
+        <v>0</v>
+      </c>
+      <c r="N9" s="48">
         <v>16000</v>
       </c>
-      <c r="O9" s="64">
+      <c r="O9" s="48">
         <v>7</v>
       </c>
-      <c r="P9" s="64" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q9" s="64" t="s">
+      <c r="P9" s="48" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q9" s="48" t="s">
         <v>53</v>
       </c>
-      <c r="R9" s="64"/>
+      <c r="R9" s="48"/>
     </row>
     <row r="10" spans="1:18">
-      <c r="A10" s="64">
+      <c r="A10" s="48">
         <v>9</v>
       </c>
-      <c r="B10" s="64" t="s">
+      <c r="B10" s="48" t="s">
         <v>54</v>
       </c>
-      <c r="C10" s="64" t="s">
+      <c r="C10" s="48" t="s">
         <v>29</v>
       </c>
-      <c r="D10" s="64" t="s">
+      <c r="D10" s="48" t="s">
         <v>30</v>
       </c>
-      <c r="E10" s="64" t="s">
+      <c r="E10" s="48" t="s">
         <v>31</v>
       </c>
-      <c r="F10" s="64" t="s">
+      <c r="F10" s="48" t="s">
         <v>55</v>
       </c>
-      <c r="G10" s="64" t="s">
+      <c r="G10" s="48" t="s">
         <v>33</v>
       </c>
-      <c r="H10" s="64" t="s">
+      <c r="H10" s="48" t="s">
         <v>54</v>
       </c>
-      <c r="I10" s="64" t="s">
+      <c r="I10" s="48" t="s">
         <v>52</v>
       </c>
-      <c r="J10" s="64" t="s">
+      <c r="J10" s="48" t="s">
         <v>35</v>
       </c>
-      <c r="K10" s="64">
-        <v>0</v>
-      </c>
-      <c r="L10" s="64">
+      <c r="K10" s="48">
+        <v>0</v>
+      </c>
+      <c r="L10" s="48">
         <v>100</v>
       </c>
-      <c r="M10" s="64">
-        <v>0</v>
-      </c>
-      <c r="N10" s="64">
+      <c r="M10" s="48">
+        <v>0</v>
+      </c>
+      <c r="N10" s="48">
         <v>16000</v>
       </c>
-      <c r="O10" s="64">
+      <c r="O10" s="48">
         <v>8</v>
       </c>
-      <c r="P10" s="64" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q10" s="64" t="s">
+      <c r="P10" s="48" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q10" s="48" t="s">
         <v>56</v>
       </c>
-      <c r="R10" s="64"/>
+      <c r="R10" s="48"/>
     </row>
     <row r="11" spans="1:18">
-      <c r="A11" s="64">
+      <c r="A11" s="48">
         <v>10</v>
       </c>
-      <c r="B11" s="64" t="s">
+      <c r="B11" s="48" t="s">
         <v>57</v>
       </c>
-      <c r="C11" s="64" t="s">
+      <c r="C11" s="48" t="s">
         <v>29</v>
       </c>
-      <c r="D11" s="64" t="s">
+      <c r="D11" s="48" t="s">
         <v>30</v>
       </c>
-      <c r="E11" s="64" t="s">
+      <c r="E11" s="48" t="s">
         <v>31</v>
       </c>
-      <c r="F11" s="64" t="s">
+      <c r="F11" s="48" t="s">
         <v>58</v>
       </c>
-      <c r="G11" s="64" t="s">
+      <c r="G11" s="48" t="s">
         <v>59</v>
       </c>
-      <c r="H11" s="64" t="s">
+      <c r="H11" s="48" t="s">
         <v>57</v>
       </c>
-      <c r="I11" s="64" t="s">
+      <c r="I11" s="48" t="s">
         <v>52</v>
       </c>
-      <c r="J11" s="64" t="s">
+      <c r="J11" s="48" t="s">
         <v>35</v>
       </c>
-      <c r="K11" s="64">
-        <v>0</v>
-      </c>
-      <c r="L11" s="64">
+      <c r="K11" s="48">
+        <v>0</v>
+      </c>
+      <c r="L11" s="48">
         <v>100</v>
       </c>
-      <c r="M11" s="64">
-        <v>0</v>
-      </c>
-      <c r="N11" s="64">
+      <c r="M11" s="48">
+        <v>0</v>
+      </c>
+      <c r="N11" s="48">
         <v>16000</v>
       </c>
-      <c r="O11" s="64">
+      <c r="O11" s="48">
         <v>9</v>
       </c>
-      <c r="P11" s="64" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q11" s="64" t="s">
+      <c r="P11" s="48" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q11" s="48" t="s">
         <v>60</v>
       </c>
-      <c r="R11" s="64"/>
+      <c r="R11" s="48"/>
     </row>
     <row r="12" spans="1:18">
-      <c r="A12" s="64">
+      <c r="A12" s="48">
         <v>11</v>
       </c>
-      <c r="B12" s="64" t="s">
+      <c r="B12" s="48" t="s">
         <v>61</v>
       </c>
-      <c r="C12" s="64" t="s">
+      <c r="C12" s="48" t="s">
         <v>29</v>
       </c>
-      <c r="D12" s="64" t="s">
+      <c r="D12" s="48" t="s">
         <v>30</v>
       </c>
-      <c r="E12" s="64" t="s">
+      <c r="E12" s="48" t="s">
         <v>31</v>
       </c>
-      <c r="F12" s="64" t="s">
+      <c r="F12" s="48" t="s">
         <v>58</v>
       </c>
-      <c r="G12" s="64" t="s">
+      <c r="G12" s="48" t="s">
         <v>59</v>
       </c>
-      <c r="H12" s="64" t="s">
+      <c r="H12" s="48" t="s">
         <v>61</v>
       </c>
-      <c r="I12" s="64" t="s">
+      <c r="I12" s="48" t="s">
         <v>52</v>
       </c>
-      <c r="J12" s="64" t="s">
+      <c r="J12" s="48" t="s">
         <v>35</v>
       </c>
-      <c r="K12" s="64">
-        <v>0</v>
-      </c>
-      <c r="L12" s="64">
+      <c r="K12" s="48">
+        <v>0</v>
+      </c>
+      <c r="L12" s="48">
         <v>100</v>
       </c>
-      <c r="M12" s="64">
-        <v>0</v>
-      </c>
-      <c r="N12" s="64">
+      <c r="M12" s="48">
+        <v>0</v>
+      </c>
+      <c r="N12" s="48">
         <v>16000</v>
       </c>
-      <c r="O12" s="64">
+      <c r="O12" s="48">
         <v>10</v>
       </c>
-      <c r="P12" s="64" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q12" s="64" t="s">
+      <c r="P12" s="48" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q12" s="48" t="s">
         <v>62</v>
       </c>
-      <c r="R12" s="64"/>
+      <c r="R12" s="48"/>
     </row>
     <row r="13" spans="1:18">
-      <c r="A13" s="64">
+      <c r="A13" s="48">
         <v>12</v>
       </c>
-      <c r="B13" s="64" t="s">
+      <c r="B13" s="48" t="s">
         <v>63</v>
       </c>
-      <c r="C13" s="64" t="s">
+      <c r="C13" s="48" t="s">
         <v>29</v>
       </c>
-      <c r="D13" s="64" t="s">
+      <c r="D13" s="48" t="s">
         <v>30</v>
       </c>
-      <c r="E13" s="64" t="s">
+      <c r="E13" s="48" t="s">
         <v>31</v>
       </c>
-      <c r="F13" s="64" t="s">
+      <c r="F13" s="48" t="s">
         <v>64</v>
       </c>
-      <c r="G13" s="64" t="s">
+      <c r="G13" s="48" t="s">
         <v>33</v>
       </c>
-      <c r="H13" s="64" t="s">
+      <c r="H13" s="48" t="s">
         <v>63</v>
       </c>
-      <c r="I13" s="64" t="s">
+      <c r="I13" s="48" t="s">
         <v>34</v>
       </c>
-      <c r="J13" s="64" t="s">
+      <c r="J13" s="48" t="s">
         <v>35</v>
       </c>
-      <c r="K13" s="64">
-        <v>0</v>
-      </c>
-      <c r="L13" s="64">
+      <c r="K13" s="48">
+        <v>0</v>
+      </c>
+      <c r="L13" s="48">
         <v>100</v>
       </c>
-      <c r="M13" s="64">
-        <v>0</v>
-      </c>
-      <c r="N13" s="64">
+      <c r="M13" s="48">
+        <v>0</v>
+      </c>
+      <c r="N13" s="48">
         <v>16000</v>
       </c>
-      <c r="O13" s="64">
+      <c r="O13" s="48">
         <v>11</v>
       </c>
-      <c r="P13" s="64" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q13" s="64" t="s">
+      <c r="P13" s="48" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q13" s="48" t="s">
         <v>65</v>
       </c>
-      <c r="R13" s="64"/>
+      <c r="R13" s="48"/>
     </row>
     <row r="14" spans="1:18">
-      <c r="A14" s="64">
+      <c r="A14" s="48">
         <v>13</v>
       </c>
-      <c r="B14" s="64" t="s">
+      <c r="B14" s="48" t="s">
         <v>131</v>
       </c>
-      <c r="C14" s="64" t="s">
+      <c r="C14" s="48" t="s">
         <v>29</v>
       </c>
-      <c r="D14" s="64" t="s">
+      <c r="D14" s="48" t="s">
         <v>132</v>
       </c>
-      <c r="E14" s="64"/>
-      <c r="F14" s="64" t="s">
+      <c r="E14" s="48"/>
+      <c r="F14" s="48" t="s">
         <v>133</v>
       </c>
-      <c r="G14" s="64" t="s">
+      <c r="G14" s="48" t="s">
         <v>134</v>
       </c>
-      <c r="H14" s="64" t="s">
+      <c r="H14" s="48" t="s">
         <v>135</v>
       </c>
-      <c r="I14" s="64" t="s">
+      <c r="I14" s="48" t="s">
         <v>136</v>
       </c>
-      <c r="J14" s="64" t="s">
+      <c r="J14" s="48" t="s">
         <v>137</v>
       </c>
-      <c r="K14" s="64">
-        <v>0</v>
-      </c>
-      <c r="L14" s="64">
-        <v>1</v>
-      </c>
-      <c r="M14" s="64">
-        <v>0</v>
-      </c>
-      <c r="N14" s="64">
-        <v>1</v>
-      </c>
-      <c r="O14" s="64">
+      <c r="K14" s="48">
+        <v>0</v>
+      </c>
+      <c r="L14" s="48">
+        <v>1</v>
+      </c>
+      <c r="M14" s="48">
+        <v>0</v>
+      </c>
+      <c r="N14" s="48">
+        <v>1</v>
+      </c>
+      <c r="O14" s="48">
         <v>250</v>
       </c>
-      <c r="P14" s="64" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q14" s="64" t="s">
+      <c r="P14" s="48" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q14" s="48" t="s">
         <v>138</v>
       </c>
-      <c r="R14" s="64"/>
+      <c r="R14" s="48"/>
     </row>
     <row r="15" spans="1:18">
-      <c r="A15" s="64">
+      <c r="A15" s="48">
         <v>14</v>
       </c>
-      <c r="B15" s="64" t="s">
+      <c r="B15" s="48" t="s">
         <v>139</v>
       </c>
-      <c r="C15" s="64" t="s">
+      <c r="C15" s="48" t="s">
         <v>29</v>
       </c>
-      <c r="D15" s="64" t="s">
+      <c r="D15" s="48" t="s">
         <v>132</v>
       </c>
-      <c r="E15" s="64"/>
-      <c r="F15" s="64" t="s">
+      <c r="E15" s="48"/>
+      <c r="F15" s="48" t="s">
         <v>140</v>
       </c>
-      <c r="G15" s="64" t="s">
+      <c r="G15" s="48" t="s">
         <v>134</v>
       </c>
-      <c r="H15" s="64" t="s">
+      <c r="H15" s="48" t="s">
         <v>135</v>
       </c>
-      <c r="I15" s="64" t="s">
+      <c r="I15" s="48" t="s">
         <v>136</v>
       </c>
-      <c r="J15" s="64" t="s">
+      <c r="J15" s="48" t="s">
         <v>137</v>
       </c>
-      <c r="K15" s="64">
-        <v>0</v>
-      </c>
-      <c r="L15" s="64">
-        <v>1</v>
-      </c>
-      <c r="M15" s="64">
-        <v>0</v>
-      </c>
-      <c r="N15" s="64">
-        <v>1</v>
-      </c>
-      <c r="O15" s="64">
+      <c r="K15" s="48">
+        <v>0</v>
+      </c>
+      <c r="L15" s="48">
+        <v>1</v>
+      </c>
+      <c r="M15" s="48">
+        <v>0</v>
+      </c>
+      <c r="N15" s="48">
+        <v>1</v>
+      </c>
+      <c r="O15" s="48">
         <v>251</v>
       </c>
-      <c r="P15" s="64" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q15" s="64" t="s">
+      <c r="P15" s="48" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q15" s="48" t="s">
         <v>141</v>
       </c>
-      <c r="R15" s="64"/>
+      <c r="R15" s="48"/>
     </row>
     <row r="16" spans="1:18">
-      <c r="A16" s="64">
+      <c r="A16" s="48">
         <v>15</v>
       </c>
-      <c r="B16" s="64" t="s">
+      <c r="B16" s="48" t="s">
+        <v>163</v>
+      </c>
+      <c r="C16" s="48" t="s">
+        <v>67</v>
+      </c>
+      <c r="D16" s="48" t="s">
+        <v>158</v>
+      </c>
+      <c r="E16" s="48"/>
+      <c r="F16" s="48" t="s">
         <v>164</v>
       </c>
-      <c r="C16" s="64" t="s">
+      <c r="G16" s="48" t="s">
+        <v>145</v>
+      </c>
+      <c r="H16" s="48" t="s">
+        <v>163</v>
+      </c>
+      <c r="I16" s="48" t="s">
+        <v>52</v>
+      </c>
+      <c r="J16" s="48" t="s">
+        <v>137</v>
+      </c>
+      <c r="K16" s="48">
+        <v>0</v>
+      </c>
+      <c r="L16" s="48">
+        <v>1</v>
+      </c>
+      <c r="M16" s="48">
+        <v>0</v>
+      </c>
+      <c r="N16" s="48">
+        <v>1</v>
+      </c>
+      <c r="O16" s="48">
+        <v>453</v>
+      </c>
+      <c r="P16" s="48" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q16" s="48" t="s">
+        <v>165</v>
+      </c>
+      <c r="R16" s="48"/>
+    </row>
+    <row r="17" spans="1:18">
+      <c r="A17" s="48">
+        <v>16</v>
+      </c>
+      <c r="B17" s="48" t="s">
+        <v>146</v>
+      </c>
+      <c r="C17" s="48" t="s">
         <v>67</v>
       </c>
-      <c r="D16" s="64" t="s">
+      <c r="D17" s="48" t="s">
+        <v>158</v>
+      </c>
+      <c r="E17" s="48"/>
+      <c r="F17" s="48" t="s">
+        <v>164</v>
+      </c>
+      <c r="G17" s="48" t="s">
+        <v>145</v>
+      </c>
+      <c r="H17" s="48" t="s">
+        <v>146</v>
+      </c>
+      <c r="I17" s="48" t="s">
+        <v>52</v>
+      </c>
+      <c r="J17" s="48" t="s">
+        <v>137</v>
+      </c>
+      <c r="K17" s="48">
+        <v>0</v>
+      </c>
+      <c r="L17" s="48">
+        <v>1</v>
+      </c>
+      <c r="M17" s="48">
+        <v>0</v>
+      </c>
+      <c r="N17" s="48">
+        <v>1</v>
+      </c>
+      <c r="O17" s="48">
+        <v>454</v>
+      </c>
+      <c r="P17" s="48" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q17" s="48" t="s">
+        <v>166</v>
+      </c>
+      <c r="R17" s="48"/>
+    </row>
+    <row r="18" spans="1:18">
+      <c r="A18" s="48">
+        <v>17</v>
+      </c>
+      <c r="B18" s="48" t="s">
+        <v>142</v>
+      </c>
+      <c r="C18" s="48" t="s">
+        <v>67</v>
+      </c>
+      <c r="D18" s="48" t="s">
+        <v>132</v>
+      </c>
+      <c r="E18" s="47" t="s">
+        <v>143</v>
+      </c>
+      <c r="F18" s="48" t="s">
+        <v>144</v>
+      </c>
+      <c r="G18" s="48" t="s">
+        <v>145</v>
+      </c>
+      <c r="H18" s="48" t="s">
+        <v>395</v>
+      </c>
+      <c r="I18" s="48" t="s">
+        <v>52</v>
+      </c>
+      <c r="J18" s="48" t="s">
+        <v>137</v>
+      </c>
+      <c r="K18" s="48">
+        <v>0</v>
+      </c>
+      <c r="L18" s="48">
+        <v>1</v>
+      </c>
+      <c r="M18" s="48">
+        <v>0</v>
+      </c>
+      <c r="N18" s="48">
+        <v>1</v>
+      </c>
+      <c r="O18" s="48">
+        <v>253</v>
+      </c>
+      <c r="P18" s="48" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q18" s="48" t="s">
+        <v>147</v>
+      </c>
+      <c r="R18" s="48"/>
+    </row>
+    <row r="19" spans="1:18">
+      <c r="A19" s="48">
+        <v>18</v>
+      </c>
+      <c r="B19" s="48" t="s">
+        <v>148</v>
+      </c>
+      <c r="C19" s="48" t="s">
+        <v>67</v>
+      </c>
+      <c r="D19" s="48" t="s">
+        <v>132</v>
+      </c>
+      <c r="E19" s="47" t="s">
+        <v>143</v>
+      </c>
+      <c r="F19" s="48" t="s">
+        <v>144</v>
+      </c>
+      <c r="G19" s="48" t="s">
+        <v>145</v>
+      </c>
+      <c r="H19" s="48" t="s">
+        <v>396</v>
+      </c>
+      <c r="I19" s="48" t="s">
+        <v>52</v>
+      </c>
+      <c r="J19" s="48" t="s">
+        <v>137</v>
+      </c>
+      <c r="K19" s="48">
+        <v>0</v>
+      </c>
+      <c r="L19" s="48">
+        <v>1</v>
+      </c>
+      <c r="M19" s="48">
+        <v>0</v>
+      </c>
+      <c r="N19" s="48">
+        <v>1</v>
+      </c>
+      <c r="O19" s="48">
+        <v>254</v>
+      </c>
+      <c r="P19" s="48" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q19" s="48" t="s">
+        <v>149</v>
+      </c>
+      <c r="R19" s="48"/>
+    </row>
+    <row r="20" spans="1:18">
+      <c r="A20" s="48">
+        <v>19</v>
+      </c>
+      <c r="B20" s="48" t="s">
+        <v>98</v>
+      </c>
+      <c r="C20" s="48" t="s">
+        <v>67</v>
+      </c>
+      <c r="D20" s="48" t="s">
+        <v>99</v>
+      </c>
+      <c r="E20" s="48"/>
+      <c r="F20" s="48" t="s">
+        <v>100</v>
+      </c>
+      <c r="G20" s="48" t="s">
+        <v>59</v>
+      </c>
+      <c r="H20" s="48" t="s">
+        <v>101</v>
+      </c>
+      <c r="I20" s="48" t="s">
+        <v>52</v>
+      </c>
+      <c r="J20" s="48" t="s">
+        <v>35</v>
+      </c>
+      <c r="K20" s="48">
+        <v>0</v>
+      </c>
+      <c r="L20" s="48">
+        <v>100</v>
+      </c>
+      <c r="M20" s="48">
+        <v>0</v>
+      </c>
+      <c r="N20" s="48">
+        <v>16000</v>
+      </c>
+      <c r="O20" s="48">
+        <v>30</v>
+      </c>
+      <c r="P20" s="48" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="48" t="s">
+        <v>102</v>
+      </c>
+      <c r="R20" s="48"/>
+    </row>
+    <row r="21" spans="1:18">
+      <c r="A21" s="48">
+        <v>20</v>
+      </c>
+      <c r="B21" s="48" t="s">
+        <v>103</v>
+      </c>
+      <c r="C21" s="48" t="s">
+        <v>67</v>
+      </c>
+      <c r="D21" s="48" t="s">
+        <v>99</v>
+      </c>
+      <c r="E21" s="48"/>
+      <c r="F21" s="48" t="s">
+        <v>100</v>
+      </c>
+      <c r="G21" s="48" t="s">
+        <v>59</v>
+      </c>
+      <c r="H21" s="48" t="s">
+        <v>104</v>
+      </c>
+      <c r="I21" s="48" t="s">
+        <v>52</v>
+      </c>
+      <c r="J21" s="48" t="s">
+        <v>35</v>
+      </c>
+      <c r="K21" s="48">
+        <v>0</v>
+      </c>
+      <c r="L21" s="48">
+        <v>100</v>
+      </c>
+      <c r="M21" s="48">
+        <v>0</v>
+      </c>
+      <c r="N21" s="48">
+        <v>16000</v>
+      </c>
+      <c r="O21" s="48">
+        <v>31</v>
+      </c>
+      <c r="P21" s="48" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q21" s="48" t="s">
+        <v>105</v>
+      </c>
+      <c r="R21" s="48"/>
+    </row>
+    <row r="22" spans="1:18">
+      <c r="A22" s="48">
+        <v>21</v>
+      </c>
+      <c r="B22" s="48" t="s">
+        <v>152</v>
+      </c>
+      <c r="C22" s="48" t="s">
+        <v>151</v>
+      </c>
+      <c r="D22" s="48" t="s">
+        <v>158</v>
+      </c>
+      <c r="E22" s="48"/>
+      <c r="F22" s="48" t="s">
+        <v>164</v>
+      </c>
+      <c r="G22" s="48" t="s">
+        <v>145</v>
+      </c>
+      <c r="H22" s="48" t="s">
+        <v>152</v>
+      </c>
+      <c r="I22" s="48" t="s">
+        <v>136</v>
+      </c>
+      <c r="J22" s="48" t="s">
+        <v>137</v>
+      </c>
+      <c r="K22" s="48">
+        <v>0</v>
+      </c>
+      <c r="L22" s="48">
+        <v>1</v>
+      </c>
+      <c r="M22" s="48">
+        <v>0</v>
+      </c>
+      <c r="N22" s="48">
+        <v>1</v>
+      </c>
+      <c r="O22" s="48">
+        <v>455</v>
+      </c>
+      <c r="P22" s="48" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q22" s="48" t="s">
+        <v>167</v>
+      </c>
+      <c r="R22" s="48"/>
+    </row>
+    <row r="23" spans="1:18">
+      <c r="A23" s="48">
+        <v>22</v>
+      </c>
+      <c r="B23" s="48" t="s">
+        <v>150</v>
+      </c>
+      <c r="C23" s="48" t="s">
+        <v>151</v>
+      </c>
+      <c r="D23" s="48" t="s">
+        <v>132</v>
+      </c>
+      <c r="E23" s="48"/>
+      <c r="F23" s="48" t="s">
+        <v>144</v>
+      </c>
+      <c r="G23" s="48" t="s">
+        <v>145</v>
+      </c>
+      <c r="H23" s="48" t="s">
+        <v>152</v>
+      </c>
+      <c r="I23" s="48" t="s">
+        <v>136</v>
+      </c>
+      <c r="J23" s="48" t="s">
+        <v>137</v>
+      </c>
+      <c r="K23" s="48">
+        <v>0</v>
+      </c>
+      <c r="L23" s="48">
+        <v>1</v>
+      </c>
+      <c r="M23" s="48">
+        <v>0</v>
+      </c>
+      <c r="N23" s="48">
+        <v>1</v>
+      </c>
+      <c r="O23" s="48">
+        <v>255</v>
+      </c>
+      <c r="P23" s="48" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q23" s="48" t="s">
+        <v>153</v>
+      </c>
+      <c r="R23" s="48"/>
+    </row>
+    <row r="24" spans="1:18">
+      <c r="A24" s="48">
+        <v>23</v>
+      </c>
+      <c r="B24" s="48" t="s">
+        <v>106</v>
+      </c>
+      <c r="C24" s="48" t="s">
+        <v>67</v>
+      </c>
+      <c r="D24" s="48" t="s">
+        <v>99</v>
+      </c>
+      <c r="E24" s="48"/>
+      <c r="F24" s="48" t="s">
+        <v>100</v>
+      </c>
+      <c r="G24" s="48" t="s">
+        <v>107</v>
+      </c>
+      <c r="H24" s="48" t="s">
+        <v>106</v>
+      </c>
+      <c r="I24" s="48" t="s">
+        <v>34</v>
+      </c>
+      <c r="J24" s="48" t="s">
+        <v>35</v>
+      </c>
+      <c r="K24" s="48">
+        <v>0</v>
+      </c>
+      <c r="L24" s="48">
+        <v>1</v>
+      </c>
+      <c r="M24" s="48">
+        <v>0</v>
+      </c>
+      <c r="N24" s="48">
+        <v>1</v>
+      </c>
+      <c r="O24" s="48">
+        <v>32</v>
+      </c>
+      <c r="P24" s="48" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q24" s="48" t="s">
+        <v>389</v>
+      </c>
+      <c r="R24" s="48" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" ht="32.25" customHeight="1">
+      <c r="A25" s="48">
+        <v>24</v>
+      </c>
+      <c r="B25" s="48" t="s">
+        <v>393</v>
+      </c>
+      <c r="C25" s="48" t="s">
+        <v>67</v>
+      </c>
+      <c r="D25" s="48" t="s">
+        <v>99</v>
+      </c>
+      <c r="E25" s="48"/>
+      <c r="F25" s="48" t="s">
+        <v>394</v>
+      </c>
+      <c r="G25" s="48" t="s">
+        <v>107</v>
+      </c>
+      <c r="H25" s="48" t="s">
+        <v>106</v>
+      </c>
+      <c r="I25" s="48" t="s">
+        <v>34</v>
+      </c>
+      <c r="J25" s="48" t="s">
+        <v>35</v>
+      </c>
+      <c r="K25" s="48">
+        <v>0</v>
+      </c>
+      <c r="L25" s="48">
+        <v>1</v>
+      </c>
+      <c r="M25" s="48">
+        <v>0</v>
+      </c>
+      <c r="N25" s="48">
+        <v>1</v>
+      </c>
+      <c r="O25" s="48">
+        <v>23</v>
+      </c>
+      <c r="P25" s="48" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q25" s="48" t="s">
+        <v>390</v>
+      </c>
+      <c r="R25" s="48" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" ht="33">
+      <c r="A26" s="48">
+        <v>25</v>
+      </c>
+      <c r="B26" s="48" t="s">
+        <v>119</v>
+      </c>
+      <c r="C26" s="48" t="s">
+        <v>67</v>
+      </c>
+      <c r="D26" s="48" t="s">
+        <v>99</v>
+      </c>
+      <c r="E26" s="48"/>
+      <c r="F26" s="48" t="s">
+        <v>120</v>
+      </c>
+      <c r="G26" s="48" t="s">
+        <v>70</v>
+      </c>
+      <c r="H26" s="48" t="s">
+        <v>71</v>
+      </c>
+      <c r="I26" s="48" t="s">
+        <v>49</v>
+      </c>
+      <c r="J26" s="48" t="s">
+        <v>35</v>
+      </c>
+      <c r="K26" s="48">
+        <v>0</v>
+      </c>
+      <c r="L26" s="48">
+        <v>100</v>
+      </c>
+      <c r="M26" s="48">
+        <v>0</v>
+      </c>
+      <c r="N26" s="48">
+        <v>16000</v>
+      </c>
+      <c r="O26" s="48">
+        <v>37</v>
+      </c>
+      <c r="P26" s="48" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q26" s="51" t="s">
+        <v>121</v>
+      </c>
+      <c r="R26" s="48"/>
+    </row>
+    <row r="27" spans="1:18">
+      <c r="A27" s="48">
+        <v>26</v>
+      </c>
+      <c r="B27" s="48" t="s">
+        <v>66</v>
+      </c>
+      <c r="C27" s="48" t="s">
+        <v>67</v>
+      </c>
+      <c r="D27" s="48" t="s">
+        <v>30</v>
+      </c>
+      <c r="E27" s="48" t="s">
+        <v>68</v>
+      </c>
+      <c r="F27" s="48" t="s">
+        <v>69</v>
+      </c>
+      <c r="G27" s="48" t="s">
+        <v>70</v>
+      </c>
+      <c r="H27" s="48" t="s">
+        <v>71</v>
+      </c>
+      <c r="I27" s="48" t="s">
+        <v>49</v>
+      </c>
+      <c r="J27" s="48" t="s">
+        <v>35</v>
+      </c>
+      <c r="K27" s="48">
+        <v>0</v>
+      </c>
+      <c r="L27" s="48">
+        <v>100</v>
+      </c>
+      <c r="M27" s="48">
+        <v>0</v>
+      </c>
+      <c r="N27" s="48">
+        <v>16000</v>
+      </c>
+      <c r="O27" s="48">
+        <v>13</v>
+      </c>
+      <c r="P27" s="48" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q27" s="48"/>
+      <c r="R27" s="48"/>
+    </row>
+    <row r="28" spans="1:18">
+      <c r="A28" s="48">
+        <v>27</v>
+      </c>
+      <c r="B28" s="48" t="s">
+        <v>72</v>
+      </c>
+      <c r="C28" s="48" t="s">
+        <v>67</v>
+      </c>
+      <c r="D28" s="48" t="s">
+        <v>30</v>
+      </c>
+      <c r="E28" s="48" t="s">
+        <v>31</v>
+      </c>
+      <c r="F28" s="48" t="s">
+        <v>58</v>
+      </c>
+      <c r="G28" s="48" t="s">
+        <v>70</v>
+      </c>
+      <c r="H28" s="48" t="s">
+        <v>71</v>
+      </c>
+      <c r="I28" s="48" t="s">
+        <v>49</v>
+      </c>
+      <c r="J28" s="48" t="s">
+        <v>35</v>
+      </c>
+      <c r="K28" s="48">
+        <v>0</v>
+      </c>
+      <c r="L28" s="48">
+        <v>100</v>
+      </c>
+      <c r="M28" s="48">
+        <v>0</v>
+      </c>
+      <c r="N28" s="48">
+        <v>16000</v>
+      </c>
+      <c r="O28" s="48">
+        <v>14</v>
+      </c>
+      <c r="P28" s="48" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q28" s="48"/>
+      <c r="R28" s="48"/>
+    </row>
+    <row r="29" spans="1:18">
+      <c r="A29" s="48">
+        <v>28</v>
+      </c>
+      <c r="B29" s="48" t="s">
+        <v>73</v>
+      </c>
+      <c r="C29" s="48" t="s">
+        <v>67</v>
+      </c>
+      <c r="D29" s="48" t="s">
+        <v>30</v>
+      </c>
+      <c r="E29" s="48" t="s">
+        <v>74</v>
+      </c>
+      <c r="F29" s="48" t="s">
+        <v>75</v>
+      </c>
+      <c r="G29" s="48" t="s">
+        <v>70</v>
+      </c>
+      <c r="H29" s="48" t="s">
+        <v>71</v>
+      </c>
+      <c r="I29" s="48" t="s">
+        <v>49</v>
+      </c>
+      <c r="J29" s="48" t="s">
+        <v>35</v>
+      </c>
+      <c r="K29" s="48">
+        <v>0</v>
+      </c>
+      <c r="L29" s="48">
+        <v>100</v>
+      </c>
+      <c r="M29" s="48">
+        <v>0</v>
+      </c>
+      <c r="N29" s="48">
+        <v>16000</v>
+      </c>
+      <c r="O29" s="48">
+        <v>15</v>
+      </c>
+      <c r="P29" s="48" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q29" s="48"/>
+      <c r="R29" s="48"/>
+    </row>
+    <row r="30" spans="1:18">
+      <c r="A30" s="48">
+        <v>29</v>
+      </c>
+      <c r="B30" s="48" t="s">
+        <v>76</v>
+      </c>
+      <c r="C30" s="48" t="s">
+        <v>77</v>
+      </c>
+      <c r="D30" s="48" t="s">
+        <v>30</v>
+      </c>
+      <c r="E30" s="48" t="s">
+        <v>74</v>
+      </c>
+      <c r="F30" s="48" t="s">
+        <v>78</v>
+      </c>
+      <c r="G30" s="48" t="s">
+        <v>59</v>
+      </c>
+      <c r="H30" s="48" t="s">
+        <v>57</v>
+      </c>
+      <c r="I30" s="48" t="s">
+        <v>52</v>
+      </c>
+      <c r="J30" s="48" t="s">
+        <v>35</v>
+      </c>
+      <c r="K30" s="48">
+        <v>0</v>
+      </c>
+      <c r="L30" s="48">
+        <v>100</v>
+      </c>
+      <c r="M30" s="48">
+        <v>0</v>
+      </c>
+      <c r="N30" s="48">
+        <v>16000</v>
+      </c>
+      <c r="O30" s="48">
+        <v>17</v>
+      </c>
+      <c r="P30" s="48" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q30" s="48" t="s">
+        <v>79</v>
+      </c>
+      <c r="R30" s="48"/>
+    </row>
+    <row r="31" spans="1:18">
+      <c r="A31" s="48">
+        <v>30</v>
+      </c>
+      <c r="B31" s="48" t="s">
+        <v>380</v>
+      </c>
+      <c r="C31" s="48" t="s">
+        <v>77</v>
+      </c>
+      <c r="D31" s="48" t="s">
+        <v>30</v>
+      </c>
+      <c r="E31" s="48" t="s">
+        <v>74</v>
+      </c>
+      <c r="F31" s="48" t="s">
+        <v>78</v>
+      </c>
+      <c r="G31" s="48" t="s">
+        <v>59</v>
+      </c>
+      <c r="H31" s="48" t="s">
+        <v>61</v>
+      </c>
+      <c r="I31" s="48" t="s">
+        <v>52</v>
+      </c>
+      <c r="J31" s="48" t="s">
+        <v>35</v>
+      </c>
+      <c r="K31" s="48">
+        <v>0</v>
+      </c>
+      <c r="L31" s="48">
+        <v>100</v>
+      </c>
+      <c r="M31" s="48">
+        <v>0</v>
+      </c>
+      <c r="N31" s="48">
+        <v>16000</v>
+      </c>
+      <c r="O31" s="48">
+        <v>22</v>
+      </c>
+      <c r="P31" s="48" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q31" s="48" t="s">
+        <v>381</v>
+      </c>
+      <c r="R31" s="48"/>
+    </row>
+    <row r="32" spans="1:18">
+      <c r="A32" s="48">
+        <v>31</v>
+      </c>
+      <c r="B32" s="48" t="s">
+        <v>157</v>
+      </c>
+      <c r="C32" s="48" t="s">
+        <v>81</v>
+      </c>
+      <c r="D32" s="48" t="s">
+        <v>158</v>
+      </c>
+      <c r="E32" s="48"/>
+      <c r="F32" s="48" t="s">
+        <v>83</v>
+      </c>
+      <c r="G32" s="48" t="s">
+        <v>83</v>
+      </c>
+      <c r="H32" s="48" t="s">
+        <v>81</v>
+      </c>
+      <c r="I32" s="48" t="s">
+        <v>81</v>
+      </c>
+      <c r="J32" s="48" t="s">
+        <v>155</v>
+      </c>
+      <c r="K32" s="48">
+        <v>0</v>
+      </c>
+      <c r="L32" s="48">
+        <v>1</v>
+      </c>
+      <c r="M32" s="48">
+        <v>0</v>
+      </c>
+      <c r="N32" s="48">
+        <v>1</v>
+      </c>
+      <c r="O32" s="48">
+        <v>450</v>
+      </c>
+      <c r="P32" s="48" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q32" s="48" t="s">
         <v>159</v>
       </c>
-      <c r="E16" s="64"/>
-      <c r="F16" s="64" t="s">
-        <v>165</v>
-      </c>
-      <c r="G16" s="64" t="s">
-        <v>145</v>
-      </c>
-      <c r="H16" s="64" t="s">
-        <v>164</v>
-      </c>
-      <c r="I16" s="64" t="s">
-        <v>52</v>
-      </c>
-      <c r="J16" s="64" t="s">
-        <v>137</v>
-      </c>
-      <c r="K16" s="64">
-        <v>0</v>
-      </c>
-      <c r="L16" s="64">
-        <v>1</v>
-      </c>
-      <c r="M16" s="64">
-        <v>0</v>
-      </c>
-      <c r="N16" s="64">
-        <v>1</v>
-      </c>
-      <c r="O16" s="64">
-        <v>453</v>
-      </c>
-      <c r="P16" s="64" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q16" s="64" t="s">
-        <v>166</v>
-      </c>
-      <c r="R16" s="64"/>
-    </row>
-    <row r="17" spans="1:18">
-      <c r="A17" s="64">
-        <v>16</v>
-      </c>
-      <c r="B17" s="64" t="s">
-        <v>146</v>
-      </c>
-      <c r="C17" s="64" t="s">
-        <v>67</v>
-      </c>
-      <c r="D17" s="64" t="s">
-        <v>159</v>
-      </c>
-      <c r="E17" s="64"/>
-      <c r="F17" s="64" t="s">
-        <v>165</v>
-      </c>
-      <c r="G17" s="64" t="s">
-        <v>145</v>
-      </c>
-      <c r="H17" s="64" t="s">
-        <v>146</v>
-      </c>
-      <c r="I17" s="64" t="s">
-        <v>52</v>
-      </c>
-      <c r="J17" s="64" t="s">
-        <v>137</v>
-      </c>
-      <c r="K17" s="64">
-        <v>0</v>
-      </c>
-      <c r="L17" s="64">
-        <v>1</v>
-      </c>
-      <c r="M17" s="64">
-        <v>0</v>
-      </c>
-      <c r="N17" s="64">
-        <v>1</v>
-      </c>
-      <c r="O17" s="64">
-        <v>454</v>
-      </c>
-      <c r="P17" s="64" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q17" s="64" t="s">
-        <v>167</v>
-      </c>
-      <c r="R17" s="64"/>
-    </row>
-    <row r="18" spans="1:18">
-      <c r="A18" s="64">
-        <v>17</v>
-      </c>
-      <c r="B18" s="64" t="s">
-        <v>142</v>
-      </c>
-      <c r="C18" s="64" t="s">
-        <v>67</v>
-      </c>
-      <c r="D18" s="64" t="s">
+      <c r="R32" s="48"/>
+    </row>
+    <row r="33" spans="1:18">
+      <c r="A33" s="48">
+        <v>32</v>
+      </c>
+      <c r="B33" s="48" t="s">
+        <v>154</v>
+      </c>
+      <c r="C33" s="48" t="s">
+        <v>81</v>
+      </c>
+      <c r="D33" s="48" t="s">
         <v>132</v>
       </c>
-      <c r="E18" s="63" t="s">
-        <v>143</v>
-      </c>
-      <c r="F18" s="64" t="s">
-        <v>144</v>
-      </c>
-      <c r="G18" s="64" t="s">
-        <v>145</v>
-      </c>
-      <c r="H18" s="64" t="s">
-        <v>146</v>
-      </c>
-      <c r="I18" s="64" t="s">
-        <v>52</v>
-      </c>
-      <c r="J18" s="64" t="s">
-        <v>137</v>
-      </c>
-      <c r="K18" s="64">
-        <v>0</v>
-      </c>
-      <c r="L18" s="64">
-        <v>1</v>
-      </c>
-      <c r="M18" s="64">
-        <v>0</v>
-      </c>
-      <c r="N18" s="64">
-        <v>1</v>
-      </c>
-      <c r="O18" s="64">
-        <v>253</v>
-      </c>
-      <c r="P18" s="64" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q18" s="64" t="s">
-        <v>147</v>
-      </c>
-      <c r="R18" s="64"/>
-    </row>
-    <row r="19" spans="1:18">
-      <c r="A19" s="64">
+      <c r="E33" s="48"/>
+      <c r="F33" s="48" t="s">
+        <v>83</v>
+      </c>
+      <c r="G33" s="48" t="s">
+        <v>83</v>
+      </c>
+      <c r="H33" s="48" t="s">
+        <v>81</v>
+      </c>
+      <c r="I33" s="48" t="s">
+        <v>81</v>
+      </c>
+      <c r="J33" s="48" t="s">
+        <v>155</v>
+      </c>
+      <c r="K33" s="48">
+        <v>0</v>
+      </c>
+      <c r="L33" s="48">
+        <v>1</v>
+      </c>
+      <c r="M33" s="48">
+        <v>0</v>
+      </c>
+      <c r="N33" s="48">
+        <v>1</v>
+      </c>
+      <c r="O33" s="49">
+        <v>256</v>
+      </c>
+      <c r="P33" s="48" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q33" s="48" t="s">
+        <v>156</v>
+      </c>
+      <c r="R33" s="48"/>
+    </row>
+    <row r="34" spans="1:18">
+      <c r="A34" s="48">
+        <v>33</v>
+      </c>
+      <c r="B34" s="48" t="s">
+        <v>160</v>
+      </c>
+      <c r="C34" s="48" t="s">
+        <v>81</v>
+      </c>
+      <c r="D34" s="48" t="s">
+        <v>161</v>
+      </c>
+      <c r="E34" s="48"/>
+      <c r="F34" s="48" t="s">
+        <v>83</v>
+      </c>
+      <c r="G34" s="48" t="s">
+        <v>83</v>
+      </c>
+      <c r="H34" s="48" t="s">
+        <v>81</v>
+      </c>
+      <c r="I34" s="48" t="s">
+        <v>81</v>
+      </c>
+      <c r="J34" s="48" t="s">
+        <v>155</v>
+      </c>
+      <c r="K34" s="48">
+        <v>0</v>
+      </c>
+      <c r="L34" s="48">
+        <v>1</v>
+      </c>
+      <c r="M34" s="48">
+        <v>0</v>
+      </c>
+      <c r="N34" s="48">
+        <v>1</v>
+      </c>
+      <c r="O34" s="48">
+        <v>451</v>
+      </c>
+      <c r="P34" s="48" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q34" s="48" t="s">
+        <v>162</v>
+      </c>
+      <c r="R34" s="48"/>
+    </row>
+    <row r="35" spans="1:18">
+      <c r="A35" s="48">
+        <v>34</v>
+      </c>
+      <c r="B35" s="48" t="s">
+        <v>170</v>
+      </c>
+      <c r="C35" s="48" t="s">
+        <v>81</v>
+      </c>
+      <c r="D35" s="48" t="s">
+        <v>158</v>
+      </c>
+      <c r="E35" s="48"/>
+      <c r="F35" s="48" t="s">
+        <v>171</v>
+      </c>
+      <c r="G35" s="48" t="s">
+        <v>83</v>
+      </c>
+      <c r="H35" s="48" t="s">
+        <v>84</v>
+      </c>
+      <c r="I35" s="48" t="s">
+        <v>81</v>
+      </c>
+      <c r="J35" s="48" t="s">
+        <v>155</v>
+      </c>
+      <c r="K35" s="48">
+        <v>0</v>
+      </c>
+      <c r="L35" s="48">
+        <v>1</v>
+      </c>
+      <c r="M35" s="48">
+        <v>0</v>
+      </c>
+      <c r="N35" s="48">
+        <v>1</v>
+      </c>
+      <c r="O35" s="48">
+        <v>460</v>
+      </c>
+      <c r="P35" s="48" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q35" s="51" t="s">
+        <v>172</v>
+      </c>
+      <c r="R35" s="48"/>
+    </row>
+    <row r="36" spans="1:18">
+      <c r="A36" s="48">
+        <v>35</v>
+      </c>
+      <c r="B36" s="48" t="s">
+        <v>173</v>
+      </c>
+      <c r="C36" s="48" t="s">
+        <v>81</v>
+      </c>
+      <c r="D36" s="48" t="s">
+        <v>158</v>
+      </c>
+      <c r="E36" s="48"/>
+      <c r="F36" s="48" t="s">
+        <v>174</v>
+      </c>
+      <c r="G36" s="48" t="s">
+        <v>83</v>
+      </c>
+      <c r="H36" s="48" t="s">
+        <v>88</v>
+      </c>
+      <c r="I36" s="48" t="s">
+        <v>81</v>
+      </c>
+      <c r="J36" s="48" t="s">
+        <v>155</v>
+      </c>
+      <c r="K36" s="48">
+        <v>0</v>
+      </c>
+      <c r="L36" s="48">
+        <v>1</v>
+      </c>
+      <c r="M36" s="48">
+        <v>0</v>
+      </c>
+      <c r="N36" s="48">
+        <v>1</v>
+      </c>
+      <c r="O36" s="48">
+        <v>461</v>
+      </c>
+      <c r="P36" s="48" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q36" s="51" t="s">
+        <v>175</v>
+      </c>
+      <c r="R36" s="48"/>
+    </row>
+    <row r="37" spans="1:18">
+      <c r="A37" s="48">
+        <v>36</v>
+      </c>
+      <c r="B37" s="48" t="s">
+        <v>176</v>
+      </c>
+      <c r="C37" s="48" t="s">
+        <v>81</v>
+      </c>
+      <c r="D37" s="48" t="s">
+        <v>158</v>
+      </c>
+      <c r="E37" s="48"/>
+      <c r="F37" s="48" t="s">
+        <v>177</v>
+      </c>
+      <c r="G37" s="48" t="s">
+        <v>83</v>
+      </c>
+      <c r="H37" s="48" t="s">
+        <v>92</v>
+      </c>
+      <c r="I37" s="48" t="s">
+        <v>81</v>
+      </c>
+      <c r="J37" s="48" t="s">
+        <v>155</v>
+      </c>
+      <c r="K37" s="48">
+        <v>0</v>
+      </c>
+      <c r="L37" s="48">
+        <v>1</v>
+      </c>
+      <c r="M37" s="48">
+        <v>0</v>
+      </c>
+      <c r="N37" s="48">
+        <v>1</v>
+      </c>
+      <c r="O37" s="48">
+        <v>462</v>
+      </c>
+      <c r="P37" s="48" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q37" s="51" t="s">
+        <v>178</v>
+      </c>
+      <c r="R37" s="48"/>
+    </row>
+    <row r="38" spans="1:18">
+      <c r="A38" s="48">
+        <v>37</v>
+      </c>
+      <c r="B38" s="48" t="s">
+        <v>80</v>
+      </c>
+      <c r="C38" s="48" t="s">
+        <v>81</v>
+      </c>
+      <c r="D38" s="48" t="s">
+        <v>30</v>
+      </c>
+      <c r="E38" s="48"/>
+      <c r="F38" s="48" t="s">
+        <v>82</v>
+      </c>
+      <c r="G38" s="48" t="s">
+        <v>83</v>
+      </c>
+      <c r="H38" s="48" t="s">
+        <v>84</v>
+      </c>
+      <c r="I38" s="48" t="s">
+        <v>81</v>
+      </c>
+      <c r="J38" s="48" t="s">
+        <v>35</v>
+      </c>
+      <c r="K38" s="48">
+        <v>0</v>
+      </c>
+      <c r="L38" s="48">
+        <v>1</v>
+      </c>
+      <c r="M38" s="48">
+        <v>0</v>
+      </c>
+      <c r="N38" s="48">
+        <v>1</v>
+      </c>
+      <c r="O38" s="48">
         <v>18</v>
       </c>
-      <c r="B19" s="64" t="s">
-        <v>148</v>
-      </c>
-      <c r="C19" s="64" t="s">
-        <v>67</v>
-      </c>
-      <c r="D19" s="64" t="s">
-        <v>132</v>
-      </c>
-      <c r="E19" s="63" t="s">
-        <v>143</v>
-      </c>
-      <c r="F19" s="64" t="s">
-        <v>144</v>
-      </c>
-      <c r="G19" s="64" t="s">
-        <v>145</v>
-      </c>
-      <c r="H19" s="64" t="s">
-        <v>149</v>
-      </c>
-      <c r="I19" s="64" t="s">
-        <v>52</v>
-      </c>
-      <c r="J19" s="64" t="s">
-        <v>137</v>
-      </c>
-      <c r="K19" s="64">
-        <v>0</v>
-      </c>
-      <c r="L19" s="64">
-        <v>1</v>
-      </c>
-      <c r="M19" s="64">
-        <v>0</v>
-      </c>
-      <c r="N19" s="64">
-        <v>1</v>
-      </c>
-      <c r="O19" s="64">
-        <v>254</v>
-      </c>
-      <c r="P19" s="64" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q19" s="64" t="s">
-        <v>150</v>
-      </c>
-      <c r="R19" s="64"/>
-    </row>
-    <row r="20" spans="1:18">
-      <c r="A20" s="64">
+      <c r="P38" s="48" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q38" s="48" t="s">
+        <v>85</v>
+      </c>
+      <c r="R38" s="48"/>
+    </row>
+    <row r="39" spans="1:18">
+      <c r="A39" s="48">
+        <v>38</v>
+      </c>
+      <c r="B39" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="C39" s="48" t="s">
+        <v>81</v>
+      </c>
+      <c r="D39" s="48" t="s">
+        <v>30</v>
+      </c>
+      <c r="E39" s="48"/>
+      <c r="F39" s="48" t="s">
+        <v>87</v>
+      </c>
+      <c r="G39" s="48" t="s">
+        <v>83</v>
+      </c>
+      <c r="H39" s="48" t="s">
+        <v>88</v>
+      </c>
+      <c r="I39" s="48" t="s">
+        <v>81</v>
+      </c>
+      <c r="J39" s="48" t="s">
+        <v>35</v>
+      </c>
+      <c r="K39" s="48">
+        <v>0</v>
+      </c>
+      <c r="L39" s="48">
+        <v>1</v>
+      </c>
+      <c r="M39" s="48">
+        <v>0</v>
+      </c>
+      <c r="N39" s="48">
+        <v>1</v>
+      </c>
+      <c r="O39" s="48">
         <v>19</v>
       </c>
-      <c r="B20" s="64" t="s">
-        <v>98</v>
-      </c>
-      <c r="C20" s="64" t="s">
-        <v>67</v>
-      </c>
-      <c r="D20" s="64" t="s">
-        <v>99</v>
-      </c>
-      <c r="E20" s="64"/>
-      <c r="F20" s="64" t="s">
-        <v>100</v>
-      </c>
-      <c r="G20" s="64" t="s">
-        <v>59</v>
-      </c>
-      <c r="H20" s="64" t="s">
-        <v>101</v>
-      </c>
-      <c r="I20" s="64" t="s">
-        <v>52</v>
-      </c>
-      <c r="J20" s="64" t="s">
+      <c r="P39" s="48" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q39" s="48" t="s">
+        <v>89</v>
+      </c>
+      <c r="R39" s="48"/>
+    </row>
+    <row r="40" spans="1:18">
+      <c r="A40" s="48">
+        <v>39</v>
+      </c>
+      <c r="B40" s="48" t="s">
+        <v>90</v>
+      </c>
+      <c r="C40" s="48" t="s">
+        <v>81</v>
+      </c>
+      <c r="D40" s="48" t="s">
+        <v>30</v>
+      </c>
+      <c r="E40" s="48"/>
+      <c r="F40" s="48" t="s">
+        <v>91</v>
+      </c>
+      <c r="G40" s="48" t="s">
+        <v>83</v>
+      </c>
+      <c r="H40" s="48" t="s">
+        <v>92</v>
+      </c>
+      <c r="I40" s="48" t="s">
+        <v>81</v>
+      </c>
+      <c r="J40" s="48" t="s">
         <v>35</v>
       </c>
-      <c r="K20" s="64">
-        <v>0</v>
-      </c>
-      <c r="L20" s="64">
-        <v>100</v>
-      </c>
-      <c r="M20" s="64">
-        <v>0</v>
-      </c>
-      <c r="N20" s="64">
-        <v>16000</v>
-      </c>
-      <c r="O20" s="64">
+      <c r="K40" s="48">
+        <v>0</v>
+      </c>
+      <c r="L40" s="48">
+        <v>1</v>
+      </c>
+      <c r="M40" s="48">
+        <v>0</v>
+      </c>
+      <c r="N40" s="48">
+        <v>1</v>
+      </c>
+      <c r="O40" s="48">
+        <v>20</v>
+      </c>
+      <c r="P40" s="48" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q40" s="48" t="s">
+        <v>93</v>
+      </c>
+      <c r="R40" s="48"/>
+    </row>
+    <row r="41" spans="1:18">
+      <c r="A41" s="48">
+        <v>40</v>
+      </c>
+      <c r="B41" s="48" t="s">
+        <v>94</v>
+      </c>
+      <c r="C41" s="48" t="s">
+        <v>81</v>
+      </c>
+      <c r="D41" s="48" t="s">
         <v>30</v>
       </c>
-      <c r="P20" s="64" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q20" s="64" t="s">
-        <v>102</v>
-      </c>
-      <c r="R20" s="64"/>
-    </row>
-    <row r="21" spans="1:18">
-      <c r="A21" s="64">
-        <v>20</v>
-      </c>
-      <c r="B21" s="64" t="s">
-        <v>103</v>
-      </c>
-      <c r="C21" s="64" t="s">
-        <v>67</v>
-      </c>
-      <c r="D21" s="64" t="s">
-        <v>99</v>
-      </c>
-      <c r="E21" s="64"/>
-      <c r="F21" s="64" t="s">
-        <v>100</v>
-      </c>
-      <c r="G21" s="64" t="s">
-        <v>59</v>
-      </c>
-      <c r="H21" s="64" t="s">
-        <v>104</v>
-      </c>
-      <c r="I21" s="64" t="s">
-        <v>52</v>
-      </c>
-      <c r="J21" s="64" t="s">
+      <c r="E41" s="48"/>
+      <c r="F41" s="48" t="s">
+        <v>95</v>
+      </c>
+      <c r="G41" s="48" t="s">
+        <v>83</v>
+      </c>
+      <c r="H41" s="48" t="s">
+        <v>96</v>
+      </c>
+      <c r="I41" s="48" t="s">
+        <v>81</v>
+      </c>
+      <c r="J41" s="48" t="s">
         <v>35</v>
       </c>
-      <c r="K21" s="64">
-        <v>0</v>
-      </c>
-      <c r="L21" s="64">
-        <v>100</v>
-      </c>
-      <c r="M21" s="64">
-        <v>0</v>
-      </c>
-      <c r="N21" s="64">
-        <v>16000</v>
-      </c>
-      <c r="O21" s="64">
-        <v>31</v>
-      </c>
-      <c r="P21" s="64" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q21" s="64" t="s">
-        <v>105</v>
-      </c>
-      <c r="R21" s="64"/>
-    </row>
-    <row r="22" spans="1:18">
-      <c r="A22" s="64">
+      <c r="K41" s="48">
+        <v>0</v>
+      </c>
+      <c r="L41" s="48">
+        <v>1</v>
+      </c>
+      <c r="M41" s="48">
+        <v>0</v>
+      </c>
+      <c r="N41" s="48">
+        <v>1</v>
+      </c>
+      <c r="O41" s="48">
         <v>21</v>
       </c>
-      <c r="B22" s="64" t="s">
-        <v>153</v>
-      </c>
-      <c r="C22" s="64" t="s">
-        <v>152</v>
-      </c>
-      <c r="D22" s="64" t="s">
-        <v>159</v>
-      </c>
-      <c r="E22" s="64"/>
-      <c r="F22" s="64" t="s">
-        <v>165</v>
-      </c>
-      <c r="G22" s="64" t="s">
-        <v>145</v>
-      </c>
-      <c r="H22" s="64" t="s">
-        <v>153</v>
-      </c>
-      <c r="I22" s="64" t="s">
-        <v>136</v>
-      </c>
-      <c r="J22" s="64" t="s">
-        <v>137</v>
-      </c>
-      <c r="K22" s="64">
-        <v>0</v>
-      </c>
-      <c r="L22" s="64">
-        <v>1</v>
-      </c>
-      <c r="M22" s="64">
-        <v>0</v>
-      </c>
-      <c r="N22" s="64">
-        <v>1</v>
-      </c>
-      <c r="O22" s="64">
-        <v>455</v>
-      </c>
-      <c r="P22" s="64" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q22" s="64" t="s">
+      <c r="P41" s="48" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q41" s="48" t="s">
+        <v>97</v>
+      </c>
+      <c r="R41" s="48"/>
+    </row>
+    <row r="42" spans="1:18">
+      <c r="A42" s="48">
+        <v>41</v>
+      </c>
+      <c r="B42" s="48" t="s">
+        <v>108</v>
+      </c>
+      <c r="C42" s="48" t="s">
+        <v>81</v>
+      </c>
+      <c r="D42" s="48" t="s">
+        <v>109</v>
+      </c>
+      <c r="E42" s="48"/>
+      <c r="F42" s="48" t="s">
+        <v>110</v>
+      </c>
+      <c r="G42" s="48" t="s">
+        <v>83</v>
+      </c>
+      <c r="H42" s="48" t="s">
+        <v>81</v>
+      </c>
+      <c r="I42" s="48" t="s">
+        <v>81</v>
+      </c>
+      <c r="J42" s="48" t="s">
+        <v>35</v>
+      </c>
+      <c r="K42" s="48">
+        <v>0</v>
+      </c>
+      <c r="L42" s="48">
+        <v>1</v>
+      </c>
+      <c r="M42" s="48">
+        <v>0</v>
+      </c>
+      <c r="N42" s="48">
+        <v>1</v>
+      </c>
+      <c r="O42" s="48">
+        <v>34</v>
+      </c>
+      <c r="P42" s="48" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="48" t="s">
+        <v>111</v>
+      </c>
+      <c r="R42" s="48" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="43" spans="1:18">
+      <c r="A43" s="48">
+        <v>42</v>
+      </c>
+      <c r="B43" s="48" t="s">
+        <v>113</v>
+      </c>
+      <c r="C43" s="48" t="s">
+        <v>81</v>
+      </c>
+      <c r="D43" s="48" t="s">
+        <v>109</v>
+      </c>
+      <c r="E43" s="48"/>
+      <c r="F43" s="48" t="s">
+        <v>114</v>
+      </c>
+      <c r="G43" s="48" t="s">
+        <v>83</v>
+      </c>
+      <c r="H43" s="48" t="s">
+        <v>81</v>
+      </c>
+      <c r="I43" s="48" t="s">
+        <v>81</v>
+      </c>
+      <c r="J43" s="48" t="s">
+        <v>35</v>
+      </c>
+      <c r="K43" s="48">
+        <v>0</v>
+      </c>
+      <c r="L43" s="48">
+        <v>1</v>
+      </c>
+      <c r="M43" s="48">
+        <v>0</v>
+      </c>
+      <c r="N43" s="48">
+        <v>1</v>
+      </c>
+      <c r="O43" s="48">
+        <v>35</v>
+      </c>
+      <c r="P43" s="48" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q43" s="48" t="s">
+        <v>115</v>
+      </c>
+      <c r="R43" s="48" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="44" spans="1:18">
+      <c r="A44" s="48">
+        <v>43</v>
+      </c>
+      <c r="B44" s="48" t="s">
+        <v>116</v>
+      </c>
+      <c r="C44" s="48" t="s">
+        <v>81</v>
+      </c>
+      <c r="D44" s="48" t="s">
+        <v>109</v>
+      </c>
+      <c r="E44" s="48"/>
+      <c r="F44" s="48" t="s">
+        <v>117</v>
+      </c>
+      <c r="G44" s="48" t="s">
+        <v>83</v>
+      </c>
+      <c r="H44" s="48" t="s">
+        <v>81</v>
+      </c>
+      <c r="I44" s="48" t="s">
+        <v>81</v>
+      </c>
+      <c r="J44" s="48" t="s">
+        <v>35</v>
+      </c>
+      <c r="K44" s="48">
+        <v>0</v>
+      </c>
+      <c r="L44" s="48">
+        <v>1</v>
+      </c>
+      <c r="M44" s="48">
+        <v>0</v>
+      </c>
+      <c r="N44" s="48">
+        <v>1</v>
+      </c>
+      <c r="O44" s="48">
+        <v>36</v>
+      </c>
+      <c r="P44" s="48" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q44" s="48" t="s">
+        <v>118</v>
+      </c>
+      <c r="R44" s="48" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="45" spans="1:18">
+      <c r="A45" s="48">
+        <v>44</v>
+      </c>
+      <c r="B45" s="48" t="s">
+        <v>122</v>
+      </c>
+      <c r="C45" s="48" t="s">
+        <v>81</v>
+      </c>
+      <c r="D45" s="48" t="s">
+        <v>109</v>
+      </c>
+      <c r="E45" s="48"/>
+      <c r="F45" s="48" t="s">
+        <v>123</v>
+      </c>
+      <c r="G45" s="48" t="s">
+        <v>83</v>
+      </c>
+      <c r="H45" s="48" t="s">
+        <v>81</v>
+      </c>
+      <c r="I45" s="48" t="s">
+        <v>81</v>
+      </c>
+      <c r="J45" s="48" t="s">
+        <v>35</v>
+      </c>
+      <c r="K45" s="48">
+        <v>0</v>
+      </c>
+      <c r="L45" s="48">
+        <v>1</v>
+      </c>
+      <c r="M45" s="48">
+        <v>0</v>
+      </c>
+      <c r="N45" s="48">
+        <v>1</v>
+      </c>
+      <c r="O45" s="48">
+        <v>40</v>
+      </c>
+      <c r="P45" s="48" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q45" s="48" t="s">
+        <v>124</v>
+      </c>
+      <c r="R45" s="48" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="46" spans="1:18">
+      <c r="A46" s="48">
+        <v>45</v>
+      </c>
+      <c r="B46" s="48" t="s">
+        <v>125</v>
+      </c>
+      <c r="C46" s="48" t="s">
+        <v>81</v>
+      </c>
+      <c r="D46" s="48" t="s">
+        <v>109</v>
+      </c>
+      <c r="E46" s="48"/>
+      <c r="F46" s="48" t="s">
+        <v>126</v>
+      </c>
+      <c r="G46" s="48" t="s">
+        <v>83</v>
+      </c>
+      <c r="H46" s="48" t="s">
+        <v>81</v>
+      </c>
+      <c r="I46" s="48" t="s">
+        <v>81</v>
+      </c>
+      <c r="J46" s="48" t="s">
+        <v>35</v>
+      </c>
+      <c r="K46" s="48">
+        <v>0</v>
+      </c>
+      <c r="L46" s="48">
+        <v>1</v>
+      </c>
+      <c r="M46" s="48">
+        <v>0</v>
+      </c>
+      <c r="N46" s="48">
+        <v>1</v>
+      </c>
+      <c r="O46" s="48">
+        <v>41</v>
+      </c>
+      <c r="P46" s="48" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q46" s="48" t="s">
+        <v>127</v>
+      </c>
+      <c r="R46" s="48" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="47" spans="1:18">
+      <c r="A47" s="48">
+        <v>46</v>
+      </c>
+      <c r="B47" s="48" t="s">
+        <v>128</v>
+      </c>
+      <c r="C47" s="48" t="s">
+        <v>81</v>
+      </c>
+      <c r="D47" s="48" t="s">
+        <v>109</v>
+      </c>
+      <c r="E47" s="48"/>
+      <c r="F47" s="48" t="s">
+        <v>129</v>
+      </c>
+      <c r="G47" s="48" t="s">
+        <v>83</v>
+      </c>
+      <c r="H47" s="48" t="s">
+        <v>81</v>
+      </c>
+      <c r="I47" s="48" t="s">
+        <v>81</v>
+      </c>
+      <c r="J47" s="48" t="s">
+        <v>35</v>
+      </c>
+      <c r="K47" s="48">
+        <v>0</v>
+      </c>
+      <c r="L47" s="48">
+        <v>1</v>
+      </c>
+      <c r="M47" s="48">
+        <v>0</v>
+      </c>
+      <c r="N47" s="48">
+        <v>1</v>
+      </c>
+      <c r="O47" s="48">
+        <v>42</v>
+      </c>
+      <c r="P47" s="48" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q47" s="48" t="s">
+        <v>130</v>
+      </c>
+      <c r="R47" s="48" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="48" spans="1:18">
+      <c r="A48" s="48">
+        <v>47</v>
+      </c>
+      <c r="B48" s="48" t="s">
+        <v>179</v>
+      </c>
+      <c r="C48" s="48" t="s">
+        <v>81</v>
+      </c>
+      <c r="D48" s="48" t="s">
+        <v>161</v>
+      </c>
+      <c r="E48" s="48"/>
+      <c r="F48" s="48" t="s">
+        <v>180</v>
+      </c>
+      <c r="G48" s="48" t="s">
+        <v>83</v>
+      </c>
+      <c r="H48" s="48" t="s">
+        <v>81</v>
+      </c>
+      <c r="I48" s="48" t="s">
+        <v>81</v>
+      </c>
+      <c r="J48" s="48" t="s">
+        <v>155</v>
+      </c>
+      <c r="K48" s="48">
+        <v>0</v>
+      </c>
+      <c r="L48" s="48">
+        <v>1</v>
+      </c>
+      <c r="M48" s="48">
+        <v>0</v>
+      </c>
+      <c r="N48" s="48">
+        <v>1</v>
+      </c>
+      <c r="O48" s="48">
+        <v>470</v>
+      </c>
+      <c r="P48" s="48" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q48" s="48" t="s">
+        <v>181</v>
+      </c>
+      <c r="R48" s="48" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="49" spans="1:18">
+      <c r="A49" s="48">
+        <v>48</v>
+      </c>
+      <c r="B49" s="48" t="s">
+        <v>183</v>
+      </c>
+      <c r="C49" s="48" t="s">
+        <v>81</v>
+      </c>
+      <c r="D49" s="48" t="s">
+        <v>161</v>
+      </c>
+      <c r="E49" s="48"/>
+      <c r="F49" s="48" t="s">
+        <v>184</v>
+      </c>
+      <c r="G49" s="48" t="s">
+        <v>83</v>
+      </c>
+      <c r="H49" s="48" t="s">
+        <v>81</v>
+      </c>
+      <c r="I49" s="48" t="s">
+        <v>81</v>
+      </c>
+      <c r="J49" s="48" t="s">
+        <v>155</v>
+      </c>
+      <c r="K49" s="48">
+        <v>0</v>
+      </c>
+      <c r="L49" s="48">
+        <v>1</v>
+      </c>
+      <c r="M49" s="48">
+        <v>0</v>
+      </c>
+      <c r="N49" s="48">
+        <v>1</v>
+      </c>
+      <c r="O49" s="48">
+        <v>471</v>
+      </c>
+      <c r="P49" s="48" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q49" s="48" t="s">
+        <v>185</v>
+      </c>
+      <c r="R49" s="48" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="50" spans="1:18">
+      <c r="A50" s="48">
+        <v>49</v>
+      </c>
+      <c r="B50" s="48" t="s">
         <v>168</v>
       </c>
-      <c r="R22" s="64"/>
-    </row>
-    <row r="23" spans="1:18">
-      <c r="A23" s="64">
-        <v>22</v>
-      </c>
-      <c r="B23" s="64" t="s">
-        <v>151</v>
-      </c>
-      <c r="C23" s="64" t="s">
-        <v>152</v>
-      </c>
-      <c r="D23" s="64" t="s">
-        <v>132</v>
-      </c>
-      <c r="E23" s="64"/>
-      <c r="F23" s="64" t="s">
-        <v>144</v>
-      </c>
-      <c r="G23" s="64" t="s">
-        <v>145</v>
-      </c>
-      <c r="H23" s="64" t="s">
-        <v>153</v>
-      </c>
-      <c r="I23" s="64" t="s">
-        <v>136</v>
-      </c>
-      <c r="J23" s="64" t="s">
-        <v>137</v>
-      </c>
-      <c r="K23" s="64">
-        <v>0</v>
-      </c>
-      <c r="L23" s="64">
-        <v>1</v>
-      </c>
-      <c r="M23" s="64">
-        <v>0</v>
-      </c>
-      <c r="N23" s="64">
-        <v>1</v>
-      </c>
-      <c r="O23" s="64">
-        <v>255</v>
-      </c>
-      <c r="P23" s="64" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q23" s="64" t="s">
-        <v>154</v>
-      </c>
-      <c r="R23" s="64"/>
-    </row>
-    <row r="24" spans="1:18">
-      <c r="A24" s="64">
-        <v>23</v>
-      </c>
-      <c r="B24" s="64" t="s">
-        <v>106</v>
-      </c>
-      <c r="C24" s="64" t="s">
-        <v>67</v>
-      </c>
-      <c r="D24" s="64" t="s">
-        <v>99</v>
-      </c>
-      <c r="E24" s="64"/>
-      <c r="F24" s="64" t="s">
-        <v>100</v>
-      </c>
-      <c r="G24" s="64" t="s">
-        <v>107</v>
-      </c>
-      <c r="H24" s="64" t="s">
-        <v>106</v>
-      </c>
-      <c r="I24" s="64" t="s">
-        <v>34</v>
-      </c>
-      <c r="J24" s="64" t="s">
-        <v>35</v>
-      </c>
-      <c r="K24" s="64">
-        <v>0</v>
-      </c>
-      <c r="L24" s="64">
-        <v>1</v>
-      </c>
-      <c r="M24" s="64">
-        <v>0</v>
-      </c>
-      <c r="N24" s="64">
-        <v>1</v>
-      </c>
-      <c r="O24" s="64">
-        <v>32</v>
-      </c>
-      <c r="P24" s="64" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q24" s="64" t="s">
-        <v>390</v>
-      </c>
-      <c r="R24" s="64" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="25" spans="1:18" ht="32.25" customHeight="1">
-      <c r="A25" s="64">
-        <v>24</v>
-      </c>
-      <c r="B25" s="64" t="s">
-        <v>394</v>
-      </c>
-      <c r="C25" s="64" t="s">
-        <v>67</v>
-      </c>
-      <c r="D25" s="64" t="s">
-        <v>99</v>
-      </c>
-      <c r="E25" s="64"/>
-      <c r="F25" s="64" t="s">
-        <v>395</v>
-      </c>
-      <c r="G25" s="64" t="s">
-        <v>107</v>
-      </c>
-      <c r="H25" s="64" t="s">
-        <v>106</v>
-      </c>
-      <c r="I25" s="64" t="s">
-        <v>34</v>
-      </c>
-      <c r="J25" s="64" t="s">
-        <v>35</v>
-      </c>
-      <c r="K25" s="64">
-        <v>0</v>
-      </c>
-      <c r="L25" s="64">
-        <v>1</v>
-      </c>
-      <c r="M25" s="64">
-        <v>0</v>
-      </c>
-      <c r="N25" s="64">
-        <v>1</v>
-      </c>
-      <c r="O25" s="64">
-        <v>23</v>
-      </c>
-      <c r="P25" s="64" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q25" s="64" t="s">
-        <v>391</v>
-      </c>
-      <c r="R25" s="64" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="26" spans="1:18" ht="33">
-      <c r="A26" s="64">
-        <v>25</v>
-      </c>
-      <c r="B26" s="64" t="s">
-        <v>119</v>
-      </c>
-      <c r="C26" s="64" t="s">
-        <v>67</v>
-      </c>
-      <c r="D26" s="64" t="s">
-        <v>99</v>
-      </c>
-      <c r="E26" s="64"/>
-      <c r="F26" s="64" t="s">
-        <v>120</v>
-      </c>
-      <c r="G26" s="64" t="s">
-        <v>70</v>
-      </c>
-      <c r="H26" s="64" t="s">
-        <v>71</v>
-      </c>
-      <c r="I26" s="64" t="s">
-        <v>49</v>
-      </c>
-      <c r="J26" s="64" t="s">
-        <v>35</v>
-      </c>
-      <c r="K26" s="64">
-        <v>0</v>
-      </c>
-      <c r="L26" s="64">
-        <v>100</v>
-      </c>
-      <c r="M26" s="64">
-        <v>0</v>
-      </c>
-      <c r="N26" s="64">
-        <v>16000</v>
-      </c>
-      <c r="O26" s="64">
-        <v>37</v>
-      </c>
-      <c r="P26" s="64" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q26" s="70" t="s">
-        <v>121</v>
-      </c>
-      <c r="R26" s="64"/>
-    </row>
-    <row r="27" spans="1:18">
-      <c r="A27" s="64">
-        <v>26</v>
-      </c>
-      <c r="B27" s="64" t="s">
-        <v>66</v>
-      </c>
-      <c r="C27" s="64" t="s">
-        <v>67</v>
-      </c>
-      <c r="D27" s="64" t="s">
-        <v>30</v>
-      </c>
-      <c r="E27" s="64" t="s">
-        <v>68</v>
-      </c>
-      <c r="F27" s="64" t="s">
-        <v>69</v>
-      </c>
-      <c r="G27" s="64" t="s">
-        <v>70</v>
-      </c>
-      <c r="H27" s="64" t="s">
-        <v>71</v>
-      </c>
-      <c r="I27" s="64" t="s">
-        <v>49</v>
-      </c>
-      <c r="J27" s="64" t="s">
-        <v>35</v>
-      </c>
-      <c r="K27" s="64">
-        <v>0</v>
-      </c>
-      <c r="L27" s="64">
-        <v>100</v>
-      </c>
-      <c r="M27" s="64">
-        <v>0</v>
-      </c>
-      <c r="N27" s="64">
-        <v>16000</v>
-      </c>
-      <c r="O27" s="64">
-        <v>13</v>
-      </c>
-      <c r="P27" s="64" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q27" s="64"/>
-      <c r="R27" s="64"/>
-    </row>
-    <row r="28" spans="1:18">
-      <c r="A28" s="64">
-        <v>27</v>
-      </c>
-      <c r="B28" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="C28" s="64" t="s">
-        <v>67</v>
-      </c>
-      <c r="D28" s="64" t="s">
-        <v>30</v>
-      </c>
-      <c r="E28" s="64" t="s">
-        <v>31</v>
-      </c>
-      <c r="F28" s="64" t="s">
-        <v>58</v>
-      </c>
-      <c r="G28" s="64" t="s">
-        <v>70</v>
-      </c>
-      <c r="H28" s="64" t="s">
-        <v>71</v>
-      </c>
-      <c r="I28" s="64" t="s">
-        <v>49</v>
-      </c>
-      <c r="J28" s="64" t="s">
-        <v>35</v>
-      </c>
-      <c r="K28" s="64">
-        <v>0</v>
-      </c>
-      <c r="L28" s="64">
-        <v>100</v>
-      </c>
-      <c r="M28" s="64">
-        <v>0</v>
-      </c>
-      <c r="N28" s="64">
-        <v>16000</v>
-      </c>
-      <c r="O28" s="64">
-        <v>14</v>
-      </c>
-      <c r="P28" s="64" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q28" s="64"/>
-      <c r="R28" s="64"/>
-    </row>
-    <row r="29" spans="1:18">
-      <c r="A29" s="64">
-        <v>28</v>
-      </c>
-      <c r="B29" s="64" t="s">
-        <v>73</v>
-      </c>
-      <c r="C29" s="64" t="s">
-        <v>67</v>
-      </c>
-      <c r="D29" s="64" t="s">
-        <v>30</v>
-      </c>
-      <c r="E29" s="64" t="s">
-        <v>74</v>
-      </c>
-      <c r="F29" s="64" t="s">
-        <v>75</v>
-      </c>
-      <c r="G29" s="64" t="s">
-        <v>70</v>
-      </c>
-      <c r="H29" s="64" t="s">
-        <v>71</v>
-      </c>
-      <c r="I29" s="64" t="s">
-        <v>49</v>
-      </c>
-      <c r="J29" s="64" t="s">
-        <v>35</v>
-      </c>
-      <c r="K29" s="64">
-        <v>0</v>
-      </c>
-      <c r="L29" s="64">
-        <v>100</v>
-      </c>
-      <c r="M29" s="64">
-        <v>0</v>
-      </c>
-      <c r="N29" s="64">
-        <v>16000</v>
-      </c>
-      <c r="O29" s="64">
-        <v>15</v>
-      </c>
-      <c r="P29" s="64" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q29" s="64"/>
-      <c r="R29" s="64"/>
-    </row>
-    <row r="30" spans="1:18">
-      <c r="A30" s="64">
-        <v>29</v>
-      </c>
-      <c r="B30" s="64" t="s">
-        <v>76</v>
-      </c>
-      <c r="C30" s="64" t="s">
-        <v>77</v>
-      </c>
-      <c r="D30" s="64" t="s">
-        <v>30</v>
-      </c>
-      <c r="E30" s="64" t="s">
-        <v>74</v>
-      </c>
-      <c r="F30" s="64" t="s">
-        <v>78</v>
-      </c>
-      <c r="G30" s="64" t="s">
-        <v>59</v>
-      </c>
-      <c r="H30" s="64" t="s">
-        <v>57</v>
-      </c>
-      <c r="I30" s="64" t="s">
-        <v>52</v>
-      </c>
-      <c r="J30" s="64" t="s">
-        <v>35</v>
-      </c>
-      <c r="K30" s="64">
-        <v>0</v>
-      </c>
-      <c r="L30" s="64">
-        <v>100</v>
-      </c>
-      <c r="M30" s="64">
-        <v>0</v>
-      </c>
-      <c r="N30" s="64">
-        <v>16000</v>
-      </c>
-      <c r="O30" s="64">
-        <v>17</v>
-      </c>
-      <c r="P30" s="64" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q30" s="64" t="s">
-        <v>79</v>
-      </c>
-      <c r="R30" s="64"/>
-    </row>
-    <row r="31" spans="1:18">
-      <c r="A31" s="64">
-        <v>30</v>
-      </c>
-      <c r="B31" s="64" t="s">
-        <v>381</v>
-      </c>
-      <c r="C31" s="64" t="s">
-        <v>77</v>
-      </c>
-      <c r="D31" s="64" t="s">
-        <v>30</v>
-      </c>
-      <c r="E31" s="64" t="s">
-        <v>74</v>
-      </c>
-      <c r="F31" s="64" t="s">
-        <v>78</v>
-      </c>
-      <c r="G31" s="64" t="s">
-        <v>59</v>
-      </c>
-      <c r="H31" s="64" t="s">
-        <v>61</v>
-      </c>
-      <c r="I31" s="64" t="s">
-        <v>52</v>
-      </c>
-      <c r="J31" s="64" t="s">
-        <v>35</v>
-      </c>
-      <c r="K31" s="64">
-        <v>0</v>
-      </c>
-      <c r="L31" s="64">
-        <v>100</v>
-      </c>
-      <c r="M31" s="64">
-        <v>0</v>
-      </c>
-      <c r="N31" s="64">
-        <v>16000</v>
-      </c>
-      <c r="O31" s="64">
-        <v>22</v>
-      </c>
-      <c r="P31" s="64" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q31" s="64" t="s">
-        <v>382</v>
-      </c>
-      <c r="R31" s="64"/>
-    </row>
-    <row r="32" spans="1:18">
-      <c r="A32" s="64">
-        <v>31</v>
-      </c>
-      <c r="B32" s="64" t="s">
-        <v>158</v>
-      </c>
-      <c r="C32" s="64" t="s">
+      <c r="C50" s="48" t="s">
         <v>81</v>
       </c>
-      <c r="D32" s="64" t="s">
-        <v>159</v>
-      </c>
-      <c r="E32" s="64"/>
-      <c r="F32" s="64" t="s">
+      <c r="D50" s="48" t="s">
+        <v>161</v>
+      </c>
+      <c r="E50" s="48"/>
+      <c r="F50" s="48"/>
+      <c r="G50" s="48" t="s">
         <v>83</v>
       </c>
-      <c r="G32" s="64" t="s">
-        <v>83</v>
-      </c>
-      <c r="H32" s="64" t="s">
+      <c r="H50" s="48" t="s">
         <v>81</v>
       </c>
-      <c r="I32" s="64" t="s">
+      <c r="I50" s="48" t="s">
         <v>81</v>
       </c>
-      <c r="J32" s="64" t="s">
-        <v>156</v>
-      </c>
-      <c r="K32" s="64">
-        <v>0</v>
-      </c>
-      <c r="L32" s="64">
-        <v>1</v>
-      </c>
-      <c r="M32" s="64">
-        <v>0</v>
-      </c>
-      <c r="N32" s="64">
-        <v>1</v>
-      </c>
-      <c r="O32" s="64">
-        <v>450</v>
-      </c>
-      <c r="P32" s="64" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q32" s="64" t="s">
-        <v>160</v>
-      </c>
-      <c r="R32" s="64"/>
-    </row>
-    <row r="33" spans="1:18">
-      <c r="A33" s="64">
-        <v>32</v>
-      </c>
-      <c r="B33" s="64" t="s">
+      <c r="J50" s="48" t="s">
         <v>155</v>
       </c>
-      <c r="C33" s="64" t="s">
-        <v>81</v>
-      </c>
-      <c r="D33" s="64" t="s">
-        <v>132</v>
-      </c>
-      <c r="E33" s="64"/>
-      <c r="F33" s="64" t="s">
-        <v>83</v>
-      </c>
-      <c r="G33" s="64" t="s">
-        <v>83</v>
-      </c>
-      <c r="H33" s="64" t="s">
-        <v>81</v>
-      </c>
-      <c r="I33" s="64" t="s">
-        <v>81</v>
-      </c>
-      <c r="J33" s="64" t="s">
-        <v>156</v>
-      </c>
-      <c r="K33" s="64">
-        <v>0</v>
-      </c>
-      <c r="L33" s="64">
-        <v>1</v>
-      </c>
-      <c r="M33" s="64">
-        <v>0</v>
-      </c>
-      <c r="N33" s="64">
-        <v>1</v>
-      </c>
-      <c r="O33" s="68">
-        <v>256</v>
-      </c>
-      <c r="P33" s="64" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q33" s="64" t="s">
-        <v>157</v>
-      </c>
-      <c r="R33" s="64"/>
-    </row>
-    <row r="34" spans="1:18">
-      <c r="A34" s="64">
-        <v>33</v>
-      </c>
-      <c r="B34" s="64" t="s">
-        <v>161</v>
-      </c>
-      <c r="C34" s="64" t="s">
-        <v>81</v>
-      </c>
-      <c r="D34" s="64" t="s">
-        <v>162</v>
-      </c>
-      <c r="E34" s="64"/>
-      <c r="F34" s="64" t="s">
-        <v>83</v>
-      </c>
-      <c r="G34" s="64" t="s">
-        <v>83</v>
-      </c>
-      <c r="H34" s="64" t="s">
-        <v>81</v>
-      </c>
-      <c r="I34" s="64" t="s">
-        <v>81</v>
-      </c>
-      <c r="J34" s="64" t="s">
-        <v>156</v>
-      </c>
-      <c r="K34" s="64">
-        <v>0</v>
-      </c>
-      <c r="L34" s="64">
-        <v>1</v>
-      </c>
-      <c r="M34" s="64">
-        <v>0</v>
-      </c>
-      <c r="N34" s="64">
-        <v>1</v>
-      </c>
-      <c r="O34" s="64">
-        <v>451</v>
-      </c>
-      <c r="P34" s="64" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q34" s="64" t="s">
-        <v>163</v>
-      </c>
-      <c r="R34" s="64"/>
-    </row>
-    <row r="35" spans="1:18">
-      <c r="A35" s="64">
-        <v>34</v>
-      </c>
-      <c r="B35" s="64" t="s">
-        <v>171</v>
-      </c>
-      <c r="C35" s="64" t="s">
-        <v>81</v>
-      </c>
-      <c r="D35" s="64" t="s">
-        <v>159</v>
-      </c>
-      <c r="E35" s="64"/>
-      <c r="F35" s="64" t="s">
-        <v>172</v>
-      </c>
-      <c r="G35" s="64" t="s">
-        <v>83</v>
-      </c>
-      <c r="H35" s="64" t="s">
-        <v>84</v>
-      </c>
-      <c r="I35" s="64" t="s">
-        <v>81</v>
-      </c>
-      <c r="J35" s="64" t="s">
-        <v>156</v>
-      </c>
-      <c r="K35" s="64">
-        <v>0</v>
-      </c>
-      <c r="L35" s="64">
-        <v>1</v>
-      </c>
-      <c r="M35" s="64">
-        <v>0</v>
-      </c>
-      <c r="N35" s="64">
-        <v>1</v>
-      </c>
-      <c r="O35" s="64">
-        <v>460</v>
-      </c>
-      <c r="P35" s="64" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q35" s="70" t="s">
-        <v>173</v>
-      </c>
-      <c r="R35" s="64"/>
-    </row>
-    <row r="36" spans="1:18">
-      <c r="A36" s="64">
-        <v>35</v>
-      </c>
-      <c r="B36" s="64" t="s">
-        <v>174</v>
-      </c>
-      <c r="C36" s="64" t="s">
-        <v>81</v>
-      </c>
-      <c r="D36" s="64" t="s">
-        <v>159</v>
-      </c>
-      <c r="E36" s="64"/>
-      <c r="F36" s="64" t="s">
-        <v>175</v>
-      </c>
-      <c r="G36" s="64" t="s">
-        <v>83</v>
-      </c>
-      <c r="H36" s="64" t="s">
-        <v>88</v>
-      </c>
-      <c r="I36" s="64" t="s">
-        <v>81</v>
-      </c>
-      <c r="J36" s="64" t="s">
-        <v>156</v>
-      </c>
-      <c r="K36" s="64">
-        <v>0</v>
-      </c>
-      <c r="L36" s="64">
-        <v>1</v>
-      </c>
-      <c r="M36" s="64">
-        <v>0</v>
-      </c>
-      <c r="N36" s="64">
-        <v>1</v>
-      </c>
-      <c r="O36" s="64">
-        <v>461</v>
-      </c>
-      <c r="P36" s="64" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q36" s="70" t="s">
-        <v>176</v>
-      </c>
-      <c r="R36" s="64"/>
-    </row>
-    <row r="37" spans="1:18">
-      <c r="A37" s="64">
-        <v>36</v>
-      </c>
-      <c r="B37" s="64" t="s">
-        <v>177</v>
-      </c>
-      <c r="C37" s="64" t="s">
-        <v>81</v>
-      </c>
-      <c r="D37" s="64" t="s">
-        <v>159</v>
-      </c>
-      <c r="E37" s="64"/>
-      <c r="F37" s="64" t="s">
-        <v>178</v>
-      </c>
-      <c r="G37" s="64" t="s">
-        <v>83</v>
-      </c>
-      <c r="H37" s="64" t="s">
-        <v>92</v>
-      </c>
-      <c r="I37" s="64" t="s">
-        <v>81</v>
-      </c>
-      <c r="J37" s="64" t="s">
-        <v>156</v>
-      </c>
-      <c r="K37" s="64">
-        <v>0</v>
-      </c>
-      <c r="L37" s="64">
-        <v>1</v>
-      </c>
-      <c r="M37" s="64">
-        <v>0</v>
-      </c>
-      <c r="N37" s="64">
-        <v>1</v>
-      </c>
-      <c r="O37" s="64">
-        <v>462</v>
-      </c>
-      <c r="P37" s="64" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q37" s="70" t="s">
-        <v>179</v>
-      </c>
-      <c r="R37" s="64"/>
-    </row>
-    <row r="38" spans="1:18">
-      <c r="A38" s="64">
-        <v>37</v>
-      </c>
-      <c r="B38" s="64" t="s">
-        <v>80</v>
-      </c>
-      <c r="C38" s="64" t="s">
-        <v>81</v>
-      </c>
-      <c r="D38" s="64" t="s">
-        <v>30</v>
-      </c>
-      <c r="E38" s="64"/>
-      <c r="F38" s="64" t="s">
-        <v>82</v>
-      </c>
-      <c r="G38" s="64" t="s">
-        <v>83</v>
-      </c>
-      <c r="H38" s="64" t="s">
-        <v>84</v>
-      </c>
-      <c r="I38" s="64" t="s">
-        <v>81</v>
-      </c>
-      <c r="J38" s="64" t="s">
-        <v>35</v>
-      </c>
-      <c r="K38" s="64">
-        <v>0</v>
-      </c>
-      <c r="L38" s="64">
-        <v>1</v>
-      </c>
-      <c r="M38" s="64">
-        <v>0</v>
-      </c>
-      <c r="N38" s="64">
-        <v>1</v>
-      </c>
-      <c r="O38" s="64">
-        <v>18</v>
-      </c>
-      <c r="P38" s="64" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q38" s="64" t="s">
-        <v>85</v>
-      </c>
-      <c r="R38" s="64"/>
-    </row>
-    <row r="39" spans="1:18">
-      <c r="A39" s="64">
-        <v>38</v>
-      </c>
-      <c r="B39" s="64" t="s">
-        <v>86</v>
-      </c>
-      <c r="C39" s="64" t="s">
-        <v>81</v>
-      </c>
-      <c r="D39" s="64" t="s">
-        <v>30</v>
-      </c>
-      <c r="E39" s="64"/>
-      <c r="F39" s="64" t="s">
-        <v>87</v>
-      </c>
-      <c r="G39" s="64" t="s">
-        <v>83</v>
-      </c>
-      <c r="H39" s="64" t="s">
-        <v>88</v>
-      </c>
-      <c r="I39" s="64" t="s">
-        <v>81</v>
-      </c>
-      <c r="J39" s="64" t="s">
-        <v>35</v>
-      </c>
-      <c r="K39" s="64">
-        <v>0</v>
-      </c>
-      <c r="L39" s="64">
-        <v>1</v>
-      </c>
-      <c r="M39" s="64">
-        <v>0</v>
-      </c>
-      <c r="N39" s="64">
-        <v>1</v>
-      </c>
-      <c r="O39" s="64">
-        <v>19</v>
-      </c>
-      <c r="P39" s="64" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q39" s="64" t="s">
-        <v>89</v>
-      </c>
-      <c r="R39" s="64"/>
-    </row>
-    <row r="40" spans="1:18">
-      <c r="A40" s="64">
-        <v>39</v>
-      </c>
-      <c r="B40" s="64" t="s">
-        <v>90</v>
-      </c>
-      <c r="C40" s="64" t="s">
-        <v>81</v>
-      </c>
-      <c r="D40" s="64" t="s">
-        <v>30</v>
-      </c>
-      <c r="E40" s="64"/>
-      <c r="F40" s="64" t="s">
-        <v>91</v>
-      </c>
-      <c r="G40" s="64" t="s">
-        <v>83</v>
-      </c>
-      <c r="H40" s="64" t="s">
-        <v>92</v>
-      </c>
-      <c r="I40" s="64" t="s">
-        <v>81</v>
-      </c>
-      <c r="J40" s="64" t="s">
-        <v>35</v>
-      </c>
-      <c r="K40" s="64">
-        <v>0</v>
-      </c>
-      <c r="L40" s="64">
-        <v>1</v>
-      </c>
-      <c r="M40" s="64">
-        <v>0</v>
-      </c>
-      <c r="N40" s="64">
-        <v>1</v>
-      </c>
-      <c r="O40" s="64">
-        <v>20</v>
-      </c>
-      <c r="P40" s="64" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q40" s="64" t="s">
-        <v>93</v>
-      </c>
-      <c r="R40" s="64"/>
-    </row>
-    <row r="41" spans="1:18">
-      <c r="A41" s="64">
-        <v>40</v>
-      </c>
-      <c r="B41" s="64" t="s">
-        <v>94</v>
-      </c>
-      <c r="C41" s="64" t="s">
-        <v>81</v>
-      </c>
-      <c r="D41" s="64" t="s">
-        <v>30</v>
-      </c>
-      <c r="E41" s="64"/>
-      <c r="F41" s="64" t="s">
-        <v>95</v>
-      </c>
-      <c r="G41" s="64" t="s">
-        <v>83</v>
-      </c>
-      <c r="H41" s="64" t="s">
-        <v>96</v>
-      </c>
-      <c r="I41" s="64" t="s">
-        <v>81</v>
-      </c>
-      <c r="J41" s="64" t="s">
-        <v>35</v>
-      </c>
-      <c r="K41" s="64">
-        <v>0</v>
-      </c>
-      <c r="L41" s="64">
-        <v>1</v>
-      </c>
-      <c r="M41" s="64">
-        <v>0</v>
-      </c>
-      <c r="N41" s="64">
-        <v>1</v>
-      </c>
-      <c r="O41" s="64">
-        <v>21</v>
-      </c>
-      <c r="P41" s="64" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q41" s="64" t="s">
-        <v>97</v>
-      </c>
-      <c r="R41" s="64"/>
-    </row>
-    <row r="42" spans="1:18">
-      <c r="A42" s="64">
-        <v>41</v>
-      </c>
-      <c r="B42" s="64" t="s">
-        <v>108</v>
-      </c>
-      <c r="C42" s="64" t="s">
-        <v>81</v>
-      </c>
-      <c r="D42" s="64" t="s">
-        <v>109</v>
-      </c>
-      <c r="E42" s="64"/>
-      <c r="F42" s="64" t="s">
-        <v>110</v>
-      </c>
-      <c r="G42" s="64" t="s">
-        <v>83</v>
-      </c>
-      <c r="H42" s="64" t="s">
-        <v>81</v>
-      </c>
-      <c r="I42" s="64" t="s">
-        <v>81</v>
-      </c>
-      <c r="J42" s="64" t="s">
-        <v>35</v>
-      </c>
-      <c r="K42" s="64">
-        <v>0</v>
-      </c>
-      <c r="L42" s="64">
-        <v>1</v>
-      </c>
-      <c r="M42" s="64">
-        <v>0</v>
-      </c>
-      <c r="N42" s="64">
-        <v>1</v>
-      </c>
-      <c r="O42" s="64">
-        <v>34</v>
-      </c>
-      <c r="P42" s="64" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q42" s="64" t="s">
-        <v>111</v>
-      </c>
-      <c r="R42" s="64" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="43" spans="1:18">
-      <c r="A43" s="64">
-        <v>42</v>
-      </c>
-      <c r="B43" s="64" t="s">
-        <v>113</v>
-      </c>
-      <c r="C43" s="64" t="s">
-        <v>81</v>
-      </c>
-      <c r="D43" s="64" t="s">
-        <v>109</v>
-      </c>
-      <c r="E43" s="64"/>
-      <c r="F43" s="64" t="s">
-        <v>114</v>
-      </c>
-      <c r="G43" s="64" t="s">
-        <v>83</v>
-      </c>
-      <c r="H43" s="64" t="s">
-        <v>81</v>
-      </c>
-      <c r="I43" s="64" t="s">
-        <v>81</v>
-      </c>
-      <c r="J43" s="64" t="s">
-        <v>35</v>
-      </c>
-      <c r="K43" s="64">
-        <v>0</v>
-      </c>
-      <c r="L43" s="64">
-        <v>1</v>
-      </c>
-      <c r="M43" s="64">
-        <v>0</v>
-      </c>
-      <c r="N43" s="64">
-        <v>1</v>
-      </c>
-      <c r="O43" s="64">
-        <v>35</v>
-      </c>
-      <c r="P43" s="64" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q43" s="64" t="s">
-        <v>115</v>
-      </c>
-      <c r="R43" s="64" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="44" spans="1:18">
-      <c r="A44" s="64">
-        <v>43</v>
-      </c>
-      <c r="B44" s="64" t="s">
-        <v>116</v>
-      </c>
-      <c r="C44" s="64" t="s">
-        <v>81</v>
-      </c>
-      <c r="D44" s="64" t="s">
-        <v>109</v>
-      </c>
-      <c r="E44" s="64"/>
-      <c r="F44" s="64" t="s">
-        <v>117</v>
-      </c>
-      <c r="G44" s="64" t="s">
-        <v>83</v>
-      </c>
-      <c r="H44" s="64" t="s">
-        <v>81</v>
-      </c>
-      <c r="I44" s="64" t="s">
-        <v>81</v>
-      </c>
-      <c r="J44" s="64" t="s">
-        <v>35</v>
-      </c>
-      <c r="K44" s="64">
-        <v>0</v>
-      </c>
-      <c r="L44" s="64">
-        <v>1</v>
-      </c>
-      <c r="M44" s="64">
-        <v>0</v>
-      </c>
-      <c r="N44" s="64">
-        <v>1</v>
-      </c>
-      <c r="O44" s="64">
-        <v>36</v>
-      </c>
-      <c r="P44" s="64" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q44" s="64" t="s">
-        <v>118</v>
-      </c>
-      <c r="R44" s="64" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="45" spans="1:18">
-      <c r="A45" s="64">
-        <v>44</v>
-      </c>
-      <c r="B45" s="64" t="s">
-        <v>122</v>
-      </c>
-      <c r="C45" s="64" t="s">
-        <v>81</v>
-      </c>
-      <c r="D45" s="64" t="s">
-        <v>109</v>
-      </c>
-      <c r="E45" s="64"/>
-      <c r="F45" s="64" t="s">
-        <v>123</v>
-      </c>
-      <c r="G45" s="64" t="s">
-        <v>83</v>
-      </c>
-      <c r="H45" s="64" t="s">
-        <v>81</v>
-      </c>
-      <c r="I45" s="64" t="s">
-        <v>81</v>
-      </c>
-      <c r="J45" s="64" t="s">
-        <v>35</v>
-      </c>
-      <c r="K45" s="64">
-        <v>0</v>
-      </c>
-      <c r="L45" s="64">
-        <v>1</v>
-      </c>
-      <c r="M45" s="64">
-        <v>0</v>
-      </c>
-      <c r="N45" s="64">
-        <v>1</v>
-      </c>
-      <c r="O45" s="64">
-        <v>40</v>
-      </c>
-      <c r="P45" s="64" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q45" s="64" t="s">
-        <v>124</v>
-      </c>
-      <c r="R45" s="64" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="46" spans="1:18">
-      <c r="A46" s="64">
-        <v>45</v>
-      </c>
-      <c r="B46" s="64" t="s">
-        <v>125</v>
-      </c>
-      <c r="C46" s="64" t="s">
-        <v>81</v>
-      </c>
-      <c r="D46" s="64" t="s">
-        <v>109</v>
-      </c>
-      <c r="E46" s="64"/>
-      <c r="F46" s="64" t="s">
-        <v>126</v>
-      </c>
-      <c r="G46" s="64" t="s">
-        <v>83</v>
-      </c>
-      <c r="H46" s="64" t="s">
-        <v>81</v>
-      </c>
-      <c r="I46" s="64" t="s">
-        <v>81</v>
-      </c>
-      <c r="J46" s="64" t="s">
-        <v>35</v>
-      </c>
-      <c r="K46" s="64">
-        <v>0</v>
-      </c>
-      <c r="L46" s="64">
-        <v>1</v>
-      </c>
-      <c r="M46" s="64">
-        <v>0</v>
-      </c>
-      <c r="N46" s="64">
-        <v>1</v>
-      </c>
-      <c r="O46" s="64">
-        <v>41</v>
-      </c>
-      <c r="P46" s="64" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q46" s="64" t="s">
-        <v>127</v>
-      </c>
-      <c r="R46" s="64" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="47" spans="1:18">
-      <c r="A47" s="64">
-        <v>46</v>
-      </c>
-      <c r="B47" s="64" t="s">
-        <v>128</v>
-      </c>
-      <c r="C47" s="64" t="s">
-        <v>81</v>
-      </c>
-      <c r="D47" s="64" t="s">
-        <v>109</v>
-      </c>
-      <c r="E47" s="64"/>
-      <c r="F47" s="64" t="s">
-        <v>129</v>
-      </c>
-      <c r="G47" s="64" t="s">
-        <v>83</v>
-      </c>
-      <c r="H47" s="64" t="s">
-        <v>81</v>
-      </c>
-      <c r="I47" s="64" t="s">
-        <v>81</v>
-      </c>
-      <c r="J47" s="64" t="s">
-        <v>35</v>
-      </c>
-      <c r="K47" s="64">
-        <v>0</v>
-      </c>
-      <c r="L47" s="64">
-        <v>1</v>
-      </c>
-      <c r="M47" s="64">
-        <v>0</v>
-      </c>
-      <c r="N47" s="64">
-        <v>1</v>
-      </c>
-      <c r="O47" s="64">
-        <v>42</v>
-      </c>
-      <c r="P47" s="64" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q47" s="64" t="s">
-        <v>130</v>
-      </c>
-      <c r="R47" s="64" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="48" spans="1:18">
-      <c r="A48" s="64">
-        <v>47</v>
-      </c>
-      <c r="B48" s="64" t="s">
-        <v>180</v>
-      </c>
-      <c r="C48" s="64" t="s">
-        <v>81</v>
-      </c>
-      <c r="D48" s="64" t="s">
-        <v>162</v>
-      </c>
-      <c r="E48" s="64"/>
-      <c r="F48" s="64" t="s">
-        <v>181</v>
-      </c>
-      <c r="G48" s="64" t="s">
-        <v>83</v>
-      </c>
-      <c r="H48" s="64" t="s">
-        <v>81</v>
-      </c>
-      <c r="I48" s="64" t="s">
-        <v>81</v>
-      </c>
-      <c r="J48" s="64" t="s">
-        <v>156</v>
-      </c>
-      <c r="K48" s="64">
-        <v>0</v>
-      </c>
-      <c r="L48" s="64">
-        <v>1</v>
-      </c>
-      <c r="M48" s="64">
-        <v>0</v>
-      </c>
-      <c r="N48" s="64">
-        <v>1</v>
-      </c>
-      <c r="O48" s="64">
-        <v>470</v>
-      </c>
-      <c r="P48" s="64" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q48" s="64" t="s">
-        <v>182</v>
-      </c>
-      <c r="R48" s="64" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="49" spans="1:18">
-      <c r="A49" s="64">
-        <v>48</v>
-      </c>
-      <c r="B49" s="64" t="s">
-        <v>184</v>
-      </c>
-      <c r="C49" s="64" t="s">
-        <v>81</v>
-      </c>
-      <c r="D49" s="64" t="s">
-        <v>162</v>
-      </c>
-      <c r="E49" s="64"/>
-      <c r="F49" s="64" t="s">
-        <v>185</v>
-      </c>
-      <c r="G49" s="64" t="s">
-        <v>83</v>
-      </c>
-      <c r="H49" s="64" t="s">
-        <v>81</v>
-      </c>
-      <c r="I49" s="64" t="s">
-        <v>81</v>
-      </c>
-      <c r="J49" s="64" t="s">
-        <v>156</v>
-      </c>
-      <c r="K49" s="64">
-        <v>0</v>
-      </c>
-      <c r="L49" s="64">
-        <v>1</v>
-      </c>
-      <c r="M49" s="64">
-        <v>0</v>
-      </c>
-      <c r="N49" s="64">
-        <v>1</v>
-      </c>
-      <c r="O49" s="64">
-        <v>471</v>
-      </c>
-      <c r="P49" s="64" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q49" s="64" t="s">
-        <v>186</v>
-      </c>
-      <c r="R49" s="64" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="50" spans="1:18">
-      <c r="A50" s="64">
-        <v>49</v>
-      </c>
-      <c r="B50" s="64" t="s">
+      <c r="K50" s="48">
+        <v>0</v>
+      </c>
+      <c r="L50" s="48">
+        <v>1</v>
+      </c>
+      <c r="M50" s="48">
+        <v>0</v>
+      </c>
+      <c r="N50" s="48">
+        <v>1</v>
+      </c>
+      <c r="O50" s="48">
+        <v>456</v>
+      </c>
+      <c r="P50" s="48" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q50" s="48" t="s">
         <v>169</v>
       </c>
-      <c r="C50" s="64" t="s">
-        <v>81</v>
-      </c>
-      <c r="D50" s="64" t="s">
-        <v>162</v>
-      </c>
-      <c r="E50" s="64"/>
-      <c r="F50" s="64"/>
-      <c r="G50" s="64" t="s">
-        <v>83</v>
-      </c>
-      <c r="H50" s="64" t="s">
-        <v>81</v>
-      </c>
-      <c r="I50" s="64" t="s">
-        <v>81</v>
-      </c>
-      <c r="J50" s="64" t="s">
-        <v>156</v>
-      </c>
-      <c r="K50" s="64">
-        <v>0</v>
-      </c>
-      <c r="L50" s="64">
-        <v>1</v>
-      </c>
-      <c r="M50" s="64">
-        <v>0</v>
-      </c>
-      <c r="N50" s="64">
-        <v>1</v>
-      </c>
-      <c r="O50" s="64">
-        <v>456</v>
-      </c>
-      <c r="P50" s="64" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q50" s="64" t="s">
-        <v>170</v>
-      </c>
-      <c r="R50" s="64"/>
+      <c r="R50" s="48"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:R1" xr:uid="{7C485614-A5BE-4FB7-B2E6-807540769775}">
@@ -5532,7 +5533,7 @@
         <v>17</v>
       </c>
       <c r="B1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -5589,10 +5590,10 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>188</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>189</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>17</v>
@@ -5601,7 +5602,7 @@
         <v>26</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>11</v>
@@ -5610,7 +5611,7 @@
         <v>143</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -5618,19 +5619,19 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>84</v>
       </c>
       <c r="D2" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F2" s="11" t="s">
         <v>193</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="F2" s="11" t="s">
-        <v>194</v>
       </c>
       <c r="G2" s="1">
         <v>16000</v>
@@ -5644,19 +5645,19 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>84</v>
       </c>
       <c r="D3" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>196</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>197</v>
       </c>
       <c r="G3" s="1">
         <v>100</v>
@@ -5670,19 +5671,19 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>84</v>
       </c>
       <c r="D4" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>199</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>200</v>
       </c>
       <c r="G4" s="1">
         <v>100</v>
@@ -5696,16 +5697,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>84</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>116</v>
@@ -5722,13 +5723,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>84</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>125</v>
@@ -5745,16 +5746,16 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>84</v>
       </c>
       <c r="E7" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="F7" s="1" t="s">
         <v>205</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>206</v>
       </c>
       <c r="G7" s="1">
         <v>3</v>
@@ -5768,13 +5769,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>84</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>128</v>
@@ -5791,7 +5792,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>84</v>
@@ -5808,13 +5809,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>96</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>83</v>
@@ -5828,13 +5829,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>96</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>83</v>
@@ -5848,19 +5849,19 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>96</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="G12" s="1">
         <v>1000</v>
@@ -5874,19 +5875,19 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>96</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E13" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="F13" s="1" t="s">
         <v>205</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>206</v>
       </c>
       <c r="G13" s="1">
         <v>3</v>
@@ -5900,16 +5901,16 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>96</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>125</v>
@@ -5926,19 +5927,19 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>96</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E15" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="F15" s="1" t="s">
         <v>205</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>206</v>
       </c>
       <c r="G15" s="1">
         <v>0</v>
@@ -5952,16 +5953,16 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>96</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>128</v>
@@ -5975,7 +5976,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>96</v>
@@ -6007,16 +6008,16 @@
   <sheetData>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B2" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C2" t="s">
         <v>17</v>
       </c>
       <c r="D2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
   </sheetData>
@@ -6040,25 +6041,25 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="3" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>14</v>
       </c>
       <c r="C1" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>225</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>226</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="5" t="s">
         <v>227</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="G1" s="3" t="s">
         <v>228</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>229</v>
       </c>
       <c r="H1" s="3" t="s">
         <v>26</v>
@@ -6069,360 +6070,360 @@
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="C2" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>233</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>234</v>
       </c>
       <c r="F2" s="6">
         <f>175241*4</f>
         <v>700964</v>
       </c>
       <c r="G2" s="7" t="s">
+        <v>234</v>
+      </c>
+      <c r="H2" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>236</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>237</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>238</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>239</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>240</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>241</v>
       </c>
       <c r="F3" s="6">
         <v>237420</v>
       </c>
       <c r="G3" s="8" t="s">
+        <v>241</v>
+      </c>
+      <c r="H3" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="H3" s="1" t="s">
-        <v>243</v>
-      </c>
       <c r="I3" s="1" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="1" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>231</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>232</v>
       </c>
       <c r="D4" s="1"/>
       <c r="E4" s="1" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F4" s="6">
         <v>509000</v>
       </c>
       <c r="G4" s="8" t="s">
+        <v>245</v>
+      </c>
+      <c r="H4" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="H4" s="1" t="s">
-        <v>247</v>
-      </c>
       <c r="I4" s="1" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>231</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>232</v>
       </c>
       <c r="D5" s="1"/>
       <c r="E5" s="1" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F5" s="6"/>
       <c r="G5" s="1"/>
       <c r="H5" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="I5" s="1" t="s">
         <v>249</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>250</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="33">
       <c r="A6" s="1" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B6" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>231</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>232</v>
       </c>
       <c r="D6" s="1"/>
       <c r="E6" s="1" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="F6" s="6"/>
       <c r="G6" s="1"/>
       <c r="H6" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="I6" s="2" t="s">
         <v>253</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>254</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="1" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B7" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>231</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>232</v>
       </c>
       <c r="D7" s="1"/>
       <c r="E7" s="1" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="F7" s="6"/>
       <c r="G7" s="1"/>
       <c r="H7" s="1" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="I7" s="1"/>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B8" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="C8" s="1" t="s">
         <v>231</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>232</v>
       </c>
       <c r="D8" s="1"/>
       <c r="E8" s="1" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="F8" s="6">
         <v>85000</v>
       </c>
       <c r="G8" s="9" t="s">
+        <v>258</v>
+      </c>
+      <c r="H8" s="1" t="s">
         <v>259</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>260</v>
       </c>
       <c r="I8" s="1"/>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="1" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B9" s="1"/>
       <c r="C9" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D9" s="1"/>
       <c r="E9" s="1" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="F9" s="6">
         <v>55200</v>
       </c>
       <c r="G9" s="8" t="s">
+        <v>262</v>
+      </c>
+      <c r="H9" s="1" t="s">
         <v>263</v>
-      </c>
-      <c r="H9" s="1" t="s">
-        <v>264</v>
       </c>
       <c r="I9" s="1"/>
     </row>
     <row r="10" spans="1:9" ht="33">
       <c r="A10" s="1" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
       <c r="E10" s="1" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="F10" s="6"/>
       <c r="G10" s="1"/>
       <c r="H10" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="I10" s="2" t="s">
         <v>266</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>267</v>
       </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="C11" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="D11" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="D11" s="1" t="s">
-        <v>271</v>
-      </c>
       <c r="E11" s="1" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="F11" s="6"/>
       <c r="G11" s="8" t="s">
+        <v>271</v>
+      </c>
+      <c r="H11" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="H11" s="1" t="s">
+      <c r="I11" s="1" t="s">
         <v>273</v>
-      </c>
-      <c r="I11" s="1" t="s">
-        <v>274</v>
       </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="B12" s="10" t="s">
         <v>275</v>
       </c>
-      <c r="B12" s="10" t="s">
+      <c r="C12" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="C12" s="1" t="s">
+      <c r="D12" s="1" t="s">
         <v>277</v>
       </c>
-      <c r="D12" s="1" t="s">
-        <v>278</v>
-      </c>
       <c r="E12" s="1" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F12" s="6">
         <f>6700*4</f>
         <v>26800</v>
       </c>
       <c r="G12" s="7" t="s">
+        <v>278</v>
+      </c>
+      <c r="H12" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="H12" s="1" t="s">
-        <v>280</v>
-      </c>
       <c r="I12" s="1" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="B13" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="C13" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="D13" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="D13" s="1" t="s">
-        <v>284</v>
-      </c>
       <c r="E13" s="1" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="F13" s="6">
         <v>2464000</v>
       </c>
       <c r="G13" s="8" t="s">
+        <v>284</v>
+      </c>
+      <c r="H13" s="1" t="s">
         <v>285</v>
-      </c>
-      <c r="H13" s="1" t="s">
-        <v>286</v>
       </c>
       <c r="I13" s="1"/>
     </row>
     <row r="14" spans="1:9" ht="33">
       <c r="A14" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="B14" s="2" t="s">
         <v>287</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>288</v>
       </c>
       <c r="C14" s="1"/>
       <c r="D14" s="1" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="F14" s="6">
         <v>230989</v>
       </c>
       <c r="G14" s="8" t="s">
+        <v>289</v>
+      </c>
+      <c r="H14" s="1" t="s">
         <v>290</v>
-      </c>
-      <c r="H14" s="1" t="s">
-        <v>291</v>
       </c>
       <c r="I14" s="1"/>
     </row>
     <row r="16" spans="1:9">
       <c r="D16" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="18" spans="1:9">
       <c r="A18" t="s">
+        <v>292</v>
+      </c>
+      <c r="C18" t="s">
         <v>293</v>
       </c>
-      <c r="C18" t="s">
+      <c r="D18" s="12" t="s">
         <v>294</v>
       </c>
-      <c r="D18" s="12" t="s">
-        <v>295</v>
-      </c>
       <c r="E18" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="F18" s="4">
         <v>311300</v>
       </c>
       <c r="G18" s="13" t="s">
+        <v>295</v>
+      </c>
+      <c r="H18" t="s">
         <v>296</v>
       </c>
-      <c r="H18" t="s">
+      <c r="I18" t="s">
         <v>297</v>
-      </c>
-      <c r="I18" t="s">
-        <v>298</v>
       </c>
     </row>
   </sheetData>
@@ -6455,505 +6456,505 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="41" t="s">
+        <v>298</v>
+      </c>
+      <c r="B1" s="42" t="s">
         <v>299</v>
       </c>
-      <c r="B1" s="42" t="s">
+      <c r="C1" s="43" t="s">
         <v>300</v>
       </c>
-      <c r="C1" s="43" t="s">
+      <c r="D1" s="44" t="s">
         <v>301</v>
       </c>
-      <c r="D1" s="44" t="s">
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="62" t="s">
         <v>302</v>
       </c>
-    </row>
-    <row r="2" spans="1:4">
-      <c r="A2" s="48" t="s">
+      <c r="B2" s="14" t="s">
         <v>303</v>
-      </c>
-      <c r="B2" s="14" t="s">
-        <v>304</v>
       </c>
       <c r="C2" s="15">
         <v>10000000</v>
       </c>
-      <c r="D2" s="49">
+      <c r="D2" s="63">
         <v>18960000</v>
       </c>
     </row>
     <row r="3" spans="1:4">
-      <c r="A3" s="48"/>
+      <c r="A3" s="62"/>
       <c r="B3" s="16" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C3" s="17">
         <v>2000000</v>
       </c>
-      <c r="D3" s="50"/>
+      <c r="D3" s="64"/>
     </row>
     <row r="4" spans="1:4">
-      <c r="A4" s="48"/>
+      <c r="A4" s="62"/>
       <c r="B4" s="16" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C4" s="17">
         <v>1200000</v>
       </c>
-      <c r="D4" s="50"/>
+      <c r="D4" s="64"/>
     </row>
     <row r="5" spans="1:4">
-      <c r="A5" s="48"/>
+      <c r="A5" s="62"/>
       <c r="B5" s="16" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C5" s="17">
         <v>800000</v>
       </c>
-      <c r="D5" s="50"/>
+      <c r="D5" s="64"/>
     </row>
     <row r="6" spans="1:4">
-      <c r="A6" s="48"/>
+      <c r="A6" s="62"/>
       <c r="B6" s="16" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C6" s="17">
         <v>400000</v>
       </c>
-      <c r="D6" s="50"/>
+      <c r="D6" s="64"/>
     </row>
     <row r="7" spans="1:4">
-      <c r="A7" s="48"/>
+      <c r="A7" s="62"/>
       <c r="B7" s="16" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C7" s="17">
         <v>1000000</v>
       </c>
-      <c r="D7" s="50"/>
+      <c r="D7" s="64"/>
     </row>
     <row r="8" spans="1:4">
-      <c r="A8" s="48"/>
+      <c r="A8" s="62"/>
       <c r="B8" s="16" t="s">
+        <v>309</v>
+      </c>
+      <c r="C8" s="18" t="s">
         <v>310</v>
       </c>
-      <c r="C8" s="18" t="s">
+      <c r="D8" s="64"/>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="62"/>
+      <c r="B9" s="16" t="s">
         <v>311</v>
-      </c>
-      <c r="D8" s="50"/>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9" s="48"/>
-      <c r="B9" s="16" t="s">
-        <v>312</v>
       </c>
       <c r="C9" s="17">
         <v>3500000</v>
       </c>
-      <c r="D9" s="50"/>
+      <c r="D9" s="64"/>
     </row>
     <row r="10" spans="1:4">
-      <c r="A10" s="48"/>
+      <c r="A10" s="62"/>
       <c r="B10" s="16" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C10" s="17">
         <v>60000</v>
       </c>
-      <c r="D10" s="50"/>
+      <c r="D10" s="64"/>
     </row>
     <row r="11" spans="1:4">
-      <c r="A11" s="51" t="s">
+      <c r="A11" s="65" t="s">
+        <v>313</v>
+      </c>
+      <c r="B11" s="14" t="s">
         <v>314</v>
-      </c>
-      <c r="B11" s="14" t="s">
-        <v>315</v>
       </c>
       <c r="C11" s="19">
         <v>200000</v>
       </c>
-      <c r="D11" s="49">
+      <c r="D11" s="63">
         <v>4380000</v>
       </c>
     </row>
     <row r="12" spans="1:4">
-      <c r="A12" s="48"/>
+      <c r="A12" s="62"/>
       <c r="B12" s="16" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C12" s="17">
         <v>200000</v>
       </c>
-      <c r="D12" s="50"/>
+      <c r="D12" s="64"/>
     </row>
     <row r="13" spans="1:4">
-      <c r="A13" s="48"/>
+      <c r="A13" s="62"/>
       <c r="B13" s="16" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C13" s="17">
         <v>500000</v>
       </c>
-      <c r="D13" s="50"/>
+      <c r="D13" s="64"/>
     </row>
     <row r="14" spans="1:4">
-      <c r="A14" s="48"/>
+      <c r="A14" s="62"/>
       <c r="B14" s="16" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C14" s="20">
         <v>500000</v>
       </c>
-      <c r="D14" s="50"/>
+      <c r="D14" s="64"/>
     </row>
     <row r="15" spans="1:4">
-      <c r="A15" s="48"/>
+      <c r="A15" s="62"/>
       <c r="B15" s="16" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C15" s="20">
         <v>1000000</v>
       </c>
-      <c r="D15" s="50"/>
+      <c r="D15" s="64"/>
     </row>
     <row r="16" spans="1:4">
-      <c r="A16" s="48"/>
+      <c r="A16" s="62"/>
       <c r="B16" s="16" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C16" s="20">
         <v>1000000</v>
       </c>
-      <c r="D16" s="50"/>
+      <c r="D16" s="64"/>
     </row>
     <row r="17" spans="1:4">
-      <c r="A17" s="48"/>
+      <c r="A17" s="62"/>
       <c r="B17" s="16" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C17" s="20">
         <v>1850000</v>
       </c>
-      <c r="D17" s="50"/>
+      <c r="D17" s="64"/>
     </row>
     <row r="18" spans="1:4">
-      <c r="A18" s="48"/>
+      <c r="A18" s="62"/>
       <c r="B18" s="16" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C18" s="20">
         <v>300000</v>
       </c>
-      <c r="D18" s="50"/>
+      <c r="D18" s="64"/>
     </row>
     <row r="19" spans="1:4">
-      <c r="A19" s="48"/>
+      <c r="A19" s="62"/>
       <c r="B19" s="16" t="s">
+        <v>322</v>
+      </c>
+      <c r="C19" s="21" t="s">
         <v>323</v>
       </c>
-      <c r="C19" s="21" t="s">
+      <c r="D19" s="64"/>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20" s="62"/>
+      <c r="B20" s="16" t="s">
         <v>324</v>
-      </c>
-      <c r="D19" s="50"/>
-    </row>
-    <row r="20" spans="1:4">
-      <c r="A20" s="48"/>
-      <c r="B20" s="16" t="s">
-        <v>325</v>
       </c>
       <c r="C20" s="17">
         <v>200000</v>
       </c>
-      <c r="D20" s="50"/>
+      <c r="D20" s="64"/>
     </row>
     <row r="21" spans="1:4">
-      <c r="A21" s="48"/>
+      <c r="A21" s="62"/>
       <c r="B21" s="16" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C21" s="17">
         <v>1200000</v>
       </c>
-      <c r="D21" s="50"/>
+      <c r="D21" s="64"/>
     </row>
     <row r="22" spans="1:4">
-      <c r="A22" s="48"/>
+      <c r="A22" s="62"/>
       <c r="B22" s="16" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C22" s="17">
         <v>30000</v>
       </c>
-      <c r="D22" s="50"/>
+      <c r="D22" s="64"/>
     </row>
     <row r="23" spans="1:4">
-      <c r="A23" s="48"/>
+      <c r="A23" s="62"/>
       <c r="B23" s="16" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C23" s="17">
         <v>450000</v>
       </c>
-      <c r="D23" s="50"/>
+      <c r="D23" s="64"/>
     </row>
     <row r="24" spans="1:4">
-      <c r="A24" s="48"/>
+      <c r="A24" s="62"/>
       <c r="B24" s="16" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C24" s="17">
         <v>450000</v>
       </c>
-      <c r="D24" s="50"/>
+      <c r="D24" s="64"/>
     </row>
     <row r="25" spans="1:4">
-      <c r="A25" s="48"/>
+      <c r="A25" s="62"/>
       <c r="B25" s="16" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C25" s="17">
         <v>50000</v>
       </c>
-      <c r="D25" s="50"/>
+      <c r="D25" s="64"/>
     </row>
     <row r="26" spans="1:4">
-      <c r="A26" s="48"/>
+      <c r="A26" s="62"/>
       <c r="B26" s="16" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C26" s="17">
         <v>100000</v>
       </c>
-      <c r="D26" s="50"/>
+      <c r="D26" s="64"/>
     </row>
     <row r="27" spans="1:4">
-      <c r="A27" s="48"/>
+      <c r="A27" s="62"/>
       <c r="B27" s="16" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C27" s="17">
         <v>500000</v>
       </c>
-      <c r="D27" s="50"/>
+      <c r="D27" s="64"/>
     </row>
     <row r="28" spans="1:4">
-      <c r="A28" s="52"/>
+      <c r="A28" s="66"/>
       <c r="B28" s="22" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C28" s="23">
         <v>700000</v>
       </c>
-      <c r="D28" s="53"/>
+      <c r="D28" s="67"/>
     </row>
     <row r="29" spans="1:4">
-      <c r="A29" s="51" t="s">
+      <c r="A29" s="65" t="s">
+        <v>333</v>
+      </c>
+      <c r="B29" s="16" t="s">
         <v>334</v>
-      </c>
-      <c r="B29" s="16" t="s">
-        <v>335</v>
       </c>
       <c r="C29" s="17">
         <v>1200000</v>
       </c>
-      <c r="D29" s="54">
+      <c r="D29" s="68">
         <v>6900000</v>
       </c>
     </row>
     <row r="30" spans="1:4">
-      <c r="A30" s="48"/>
+      <c r="A30" s="62"/>
       <c r="B30" s="16" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C30" s="17">
         <v>550000</v>
       </c>
-      <c r="D30" s="50"/>
+      <c r="D30" s="64"/>
     </row>
     <row r="31" spans="1:4">
-      <c r="A31" s="48"/>
+      <c r="A31" s="62"/>
       <c r="B31" s="16" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C31" s="17">
         <v>1200000</v>
       </c>
-      <c r="D31" s="50"/>
+      <c r="D31" s="64"/>
     </row>
     <row r="32" spans="1:4">
-      <c r="A32" s="48"/>
+      <c r="A32" s="62"/>
       <c r="B32" s="16" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C32" s="17">
         <v>450000</v>
       </c>
-      <c r="D32" s="50"/>
+      <c r="D32" s="64"/>
     </row>
     <row r="33" spans="1:8">
-      <c r="A33" s="48"/>
+      <c r="A33" s="62"/>
       <c r="B33" s="16" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C33" s="17">
         <v>3500000</v>
       </c>
-      <c r="D33" s="50"/>
+      <c r="D33" s="64"/>
     </row>
     <row r="34" spans="1:8">
-      <c r="A34" s="48"/>
+      <c r="A34" s="62"/>
       <c r="B34" s="16" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C34" s="24">
         <v>300000</v>
       </c>
-      <c r="D34" s="50"/>
+      <c r="D34" s="64"/>
     </row>
     <row r="35" spans="1:8">
-      <c r="A35" s="48"/>
+      <c r="A35" s="62"/>
       <c r="B35" s="16" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C35" s="24">
         <v>30000</v>
       </c>
-      <c r="D35" s="50"/>
+      <c r="D35" s="64"/>
     </row>
     <row r="36" spans="1:8">
-      <c r="A36" s="52"/>
+      <c r="A36" s="66"/>
       <c r="B36" s="22" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C36" s="25" t="s">
-        <v>324</v>
-      </c>
-      <c r="D36" s="53"/>
+        <v>323</v>
+      </c>
+      <c r="D36" s="67"/>
     </row>
     <row r="37" spans="1:8">
-      <c r="A37" s="55" t="s">
-        <v>341</v>
+      <c r="A37" s="69" t="s">
+        <v>340</v>
       </c>
       <c r="B37" s="26" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C37" s="27" t="s">
-        <v>324</v>
-      </c>
-      <c r="D37" s="58" t="s">
-        <v>324</v>
+        <v>323</v>
+      </c>
+      <c r="D37" s="72" t="s">
+        <v>323</v>
       </c>
     </row>
     <row r="38" spans="1:8">
-      <c r="A38" s="56"/>
+      <c r="A38" s="70"/>
       <c r="B38" s="26"/>
       <c r="C38" s="27" t="s">
-        <v>324</v>
-      </c>
-      <c r="D38" s="58"/>
+        <v>323</v>
+      </c>
+      <c r="D38" s="72"/>
     </row>
     <row r="39" spans="1:8">
-      <c r="A39" s="56"/>
+      <c r="A39" s="70"/>
       <c r="B39" s="26"/>
       <c r="C39" s="27" t="s">
-        <v>324</v>
-      </c>
-      <c r="D39" s="58"/>
+        <v>323</v>
+      </c>
+      <c r="D39" s="72"/>
     </row>
     <row r="40" spans="1:8">
-      <c r="A40" s="56"/>
+      <c r="A40" s="70"/>
       <c r="B40" s="26"/>
       <c r="C40" s="27" t="s">
-        <v>324</v>
-      </c>
-      <c r="D40" s="58"/>
+        <v>323</v>
+      </c>
+      <c r="D40" s="72"/>
     </row>
     <row r="41" spans="1:8">
-      <c r="A41" s="56"/>
+      <c r="A41" s="70"/>
       <c r="B41" s="26"/>
       <c r="C41" s="27" t="s">
-        <v>324</v>
-      </c>
-      <c r="D41" s="58"/>
+        <v>323</v>
+      </c>
+      <c r="D41" s="72"/>
     </row>
     <row r="42" spans="1:8">
-      <c r="A42" s="57"/>
+      <c r="A42" s="71"/>
       <c r="B42" s="28" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C42" s="29" t="s">
-        <v>324</v>
-      </c>
-      <c r="D42" s="59"/>
+        <v>323</v>
+      </c>
+      <c r="D42" s="73"/>
     </row>
     <row r="43" spans="1:8">
-      <c r="A43" s="51" t="s">
+      <c r="A43" s="65" t="s">
+        <v>341</v>
+      </c>
+      <c r="B43" s="16" t="s">
         <v>342</v>
       </c>
-      <c r="B43" s="16" t="s">
+      <c r="C43" s="18" t="s">
+        <v>323</v>
+      </c>
+      <c r="D43" s="68">
+        <v>7630000</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8">
+      <c r="A44" s="62"/>
+      <c r="B44" s="26" t="s">
         <v>343</v>
-      </c>
-      <c r="C43" s="18" t="s">
-        <v>324</v>
-      </c>
-      <c r="D43" s="54">
-        <v>7630000</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8">
-      <c r="A44" s="48"/>
-      <c r="B44" s="26" t="s">
-        <v>344</v>
       </c>
       <c r="C44" s="17">
         <v>1600000</v>
       </c>
-      <c r="D44" s="50"/>
+      <c r="D44" s="64"/>
     </row>
     <row r="45" spans="1:8">
-      <c r="A45" s="48"/>
+      <c r="A45" s="62"/>
       <c r="B45" s="26" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C45" s="30">
         <v>5000000</v>
       </c>
-      <c r="D45" s="50"/>
+      <c r="D45" s="64"/>
     </row>
     <row r="46" spans="1:8">
-      <c r="A46" s="48"/>
+      <c r="A46" s="62"/>
       <c r="B46" s="16" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C46" s="17">
         <v>1000000</v>
       </c>
-      <c r="D46" s="50"/>
+      <c r="D46" s="64"/>
       <c r="F46" t="s">
+        <v>345</v>
+      </c>
+      <c r="H46" s="45" t="s">
         <v>346</v>
       </c>
-      <c r="H46" s="45" t="s">
-        <v>347</v>
-      </c>
     </row>
     <row r="47" spans="1:8">
-      <c r="A47" s="52"/>
+      <c r="A47" s="66"/>
       <c r="B47" s="22" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C47" s="23">
         <v>30000</v>
       </c>
-      <c r="D47" s="53"/>
+      <c r="D47" s="67"/>
       <c r="H47" s="45" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="48" spans="1:8">
       <c r="A48" s="31" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B48" s="22" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C48" s="23">
         <v>1000000</v>
@@ -6962,94 +6963,94 @@
         <v>1000000</v>
       </c>
       <c r="H48" s="45" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="49" spans="1:4">
       <c r="A49" s="31" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B49" s="22" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C49" s="33" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="D49" s="34" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="50" spans="1:4">
       <c r="A50" s="31" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B50" s="22" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C50" s="25" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="D50" s="34" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="51" spans="1:4">
       <c r="A51" s="31" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B51" s="22" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C51" s="25" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="D51" s="34" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="52" spans="1:4">
       <c r="A52" s="31" t="s">
+        <v>353</v>
+      </c>
+      <c r="B52" s="22" t="s">
+        <v>323</v>
+      </c>
+      <c r="C52" s="35" t="s">
+        <v>323</v>
+      </c>
+      <c r="D52" s="34" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4">
+      <c r="A53" s="60" t="s">
+        <v>323</v>
+      </c>
+      <c r="B53" s="74"/>
+      <c r="C53" s="74"/>
+      <c r="D53" s="75"/>
+    </row>
+    <row r="54" spans="1:4">
+      <c r="A54" s="60" t="s">
+        <v>323</v>
+      </c>
+      <c r="B54" s="36" t="s">
         <v>354</v>
       </c>
-      <c r="B52" s="22" t="s">
-        <v>324</v>
-      </c>
-      <c r="C52" s="35" t="s">
-        <v>324</v>
-      </c>
-      <c r="D52" s="34" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4">
-      <c r="A53" s="46" t="s">
-        <v>324</v>
-      </c>
-      <c r="B53" s="60"/>
-      <c r="C53" s="60"/>
-      <c r="D53" s="61"/>
-    </row>
-    <row r="54" spans="1:4">
-      <c r="A54" s="46" t="s">
-        <v>324</v>
-      </c>
-      <c r="B54" s="36" t="s">
+      <c r="C54" s="14" t="s">
         <v>355</v>
-      </c>
-      <c r="C54" s="14" t="s">
-        <v>356</v>
       </c>
       <c r="D54" s="37">
         <v>38870000</v>
       </c>
     </row>
     <row r="55" spans="1:4">
-      <c r="A55" s="47"/>
+      <c r="A55" s="61"/>
       <c r="B55" s="38" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C55" s="39" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="D55" s="40">
         <v>38870000</v>

--- a/Assets/StreamingAssets/DataTable.xlsx
+++ b/Assets/StreamingAssets/DataTable.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SWProject\My project\Assets\StreamingAssets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB2AAA6A-47EA-4A30-8F50-DE4BFB7952AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83EBC745-F59D-4136-8641-600DCA1652F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="690" yWindow="690" windowWidth="28800" windowHeight="15435" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="암모니아 실험 개요" sheetId="1" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="845" uniqueCount="397">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="847" uniqueCount="397">
   <si>
     <t>개요</t>
   </si>
@@ -4043,7 +4043,9 @@
       <c r="D23" s="48" t="s">
         <v>132</v>
       </c>
-      <c r="E23" s="48"/>
+      <c r="E23" s="47" t="s">
+        <v>143</v>
+      </c>
       <c r="F23" s="48" t="s">
         <v>144</v>
       </c>
@@ -4124,7 +4126,7 @@
         <v>1</v>
       </c>
       <c r="O24" s="48">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="P24" s="48" t="b">
         <v>1</v>
@@ -4149,7 +4151,9 @@
       <c r="D25" s="48" t="s">
         <v>99</v>
       </c>
-      <c r="E25" s="48"/>
+      <c r="E25" s="48" t="s">
+        <v>68</v>
+      </c>
       <c r="F25" s="48" t="s">
         <v>394</v>
       </c>
@@ -4178,7 +4182,7 @@
         <v>1</v>
       </c>
       <c r="O25" s="48">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="P25" s="48" t="b">
         <v>1</v>
@@ -4203,7 +4207,9 @@
       <c r="D26" s="48" t="s">
         <v>99</v>
       </c>
-      <c r="E26" s="48"/>
+      <c r="E26" s="48" t="s">
+        <v>68</v>
+      </c>
       <c r="F26" s="48" t="s">
         <v>120</v>
       </c>
@@ -4255,9 +4261,7 @@
       <c r="D27" s="48" t="s">
         <v>30</v>
       </c>
-      <c r="E27" s="48" t="s">
-        <v>68</v>
-      </c>
+      <c r="E27" s="48"/>
       <c r="F27" s="48" t="s">
         <v>69</v>
       </c>
@@ -7082,6 +7086,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="문서" ma:contentTypeID="0x01010001DD19DE52280940B3AAA5F241D6761B" ma:contentTypeVersion="4" ma:contentTypeDescription="새 문서를 만듭니다." ma:contentTypeScope="" ma:versionID="e9eb13fb4618761134bcbf92bbe04a85">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="68c09c20-cf94-447c-8c86-a27e8b975351" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="39da59c9f0b9e3f02c0d4affa15a324d" ns2:_="">
     <xsd:import namespace="68c09c20-cf94-447c-8c86-a27e8b975351"/>
@@ -7225,22 +7244,31 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0ECA5C0A-123A-482D-9740-A5FEEB670C26}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="68c09c20-cf94-447c-8c86-a27e8b975351"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{21529231-6B89-4ED0-BD3A-09A6E1C3C7BC}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{96212AED-2B2E-4A37-B17B-B5E79697714B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -7256,28 +7284,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0ECA5C0A-123A-482D-9740-A5FEEB670C26}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="68c09c20-cf94-447c-8c86-a27e8b975351"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{21529231-6B89-4ED0-BD3A-09A6E1C3C7BC}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>